--- a/artfynd/A 49804-2025 artfynd.xlsx
+++ b/artfynd/A 49804-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY51"/>
+  <dimension ref="A1:AY116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6948,6 +6948,7324 @@
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>129702610</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>457417</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6677423</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>129700821</v>
+      </c>
+      <c r="B53" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>457486</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6677569</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>129711613</v>
+      </c>
+      <c r="B54" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>St. Mörtsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>457300</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6678044</v>
+      </c>
+      <c r="S54" t="n">
+        <v>15</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Barkflagning</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>129699502</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>457280</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6678039</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>På tall.</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>129703897</v>
+      </c>
+      <c r="B56" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>457306</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6677088</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>129711614</v>
+      </c>
+      <c r="B57" t="n">
+        <v>57732</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>St. Mörtsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>457280</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6678029</v>
+      </c>
+      <c r="S57" t="n">
+        <v>15</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Färskt födosök av spillkråka i björk stubbe.</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>129700360</v>
+      </c>
+      <c r="B58" t="n">
+        <v>91551</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>457345</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6677677</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>129701074</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>457397</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6677548</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>129711612</v>
+      </c>
+      <c r="B60" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>St. Mörtsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>457358</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6677489</v>
+      </c>
+      <c r="S60" t="n">
+        <v>15</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Möjligt början på bohål i år/fjolåret.</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>129701963</v>
+      </c>
+      <c r="B61" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>457294</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6677481</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>129699824</v>
+      </c>
+      <c r="B62" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>457346</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6677881</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>129700848</v>
+      </c>
+      <c r="B63" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>457492</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6677562</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>129703670</v>
+      </c>
+      <c r="B64" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>457385</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6677038</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>129703378</v>
+      </c>
+      <c r="B65" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>457407</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6677144</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>På tall.</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>129711616</v>
+      </c>
+      <c r="B66" t="n">
+        <v>78832</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>St. Mörtsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>457305</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6677449</v>
+      </c>
+      <c r="S66" t="n">
+        <v>15</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>129703525</v>
+      </c>
+      <c r="B67" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>457433</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6677123</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Rikligt på tall.</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>129702120</v>
+      </c>
+      <c r="B68" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>457299</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6677464</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>129711615</v>
+      </c>
+      <c r="B69" t="n">
+        <v>91571</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>4660</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Rävticka</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Inocutis rheades</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>St. Mörtsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>457423</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6677421</v>
+      </c>
+      <c r="S69" t="n">
+        <v>15</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>10-15 fk på stående mindre asp.</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>129704842</v>
+      </c>
+      <c r="B70" t="n">
+        <v>78833</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>457230</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6677594</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Lite osäker men rätt säker.</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>129702970</v>
+      </c>
+      <c r="B71" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>457390</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6677240</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>På tall.</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>129704395</v>
+      </c>
+      <c r="B72" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>457267</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6677342</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>129711617</v>
+      </c>
+      <c r="B73" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>St. Mörtsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>457423</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6677206</v>
+      </c>
+      <c r="S73" t="n">
+        <v>15</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>På tallstam</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>129704249</v>
+      </c>
+      <c r="B74" t="n">
+        <v>97014</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>53</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>457311</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6677235</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>129704181</v>
+      </c>
+      <c r="B75" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>457325</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6677219</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>129702657</v>
+      </c>
+      <c r="B76" t="n">
+        <v>91551</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>457420</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6677417</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>129699484</v>
+      </c>
+      <c r="B77" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>457246</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6678032</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>129700400</v>
+      </c>
+      <c r="B78" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>457345</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6677660</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>129702998</v>
+      </c>
+      <c r="B79" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>457371</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6677246</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>På tall.</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>129703222</v>
+      </c>
+      <c r="B80" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>457409</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6677172</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>129703164</v>
+      </c>
+      <c r="B81" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>457394</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6677203</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>129700616</v>
+      </c>
+      <c r="B82" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>457384</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6677586</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>129702050</v>
+      </c>
+      <c r="B83" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>457274</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6677446</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>129701018</v>
+      </c>
+      <c r="B84" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>457426</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6677541</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>129700434</v>
+      </c>
+      <c r="B85" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>457349</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6677657</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>129700950</v>
+      </c>
+      <c r="B86" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>457431</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6677513</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>129703077</v>
+      </c>
+      <c r="B87" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>457393</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6677229</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>129704366</v>
+      </c>
+      <c r="B88" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>457288</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6677333</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>På tall.</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>129711618</v>
+      </c>
+      <c r="B89" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>St. Mörtsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>457392</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6677547</v>
+      </c>
+      <c r="S89" t="n">
+        <v>15</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>129702495</v>
+      </c>
+      <c r="B90" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>457432</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6677419</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>129700968</v>
+      </c>
+      <c r="B91" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>457428</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6677512</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>129699765</v>
+      </c>
+      <c r="B92" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>457317</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6677895</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>129701101</v>
+      </c>
+      <c r="B93" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>457396</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6677546</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Inte super färska.</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>129703817</v>
+      </c>
+      <c r="B94" t="n">
+        <v>78832</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>457337</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6677076</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>129700098</v>
+      </c>
+      <c r="B95" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>457355</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6677771</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Inte jätte färska med syns sav fortfarande.</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>129703127</v>
+      </c>
+      <c r="B96" t="n">
+        <v>78832</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>457391</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6677213</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>129717970</v>
+      </c>
+      <c r="B97" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>457534</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6676132</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, hyfsat färska.</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>129722077</v>
+      </c>
+      <c r="B98" t="n">
+        <v>91607</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>457452</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6676554</v>
+      </c>
+      <c r="S98" t="n">
+        <v>5</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Fler fruktkroppar.</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>129722173</v>
+      </c>
+      <c r="B99" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>457418</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6676575</v>
+      </c>
+      <c r="S99" t="n">
+        <v>5</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>129722296</v>
+      </c>
+      <c r="B100" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>457348</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6676704</v>
+      </c>
+      <c r="S100" t="n">
+        <v>5</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Lite färskare och äldre.</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>129722043</v>
+      </c>
+      <c r="B101" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>457469</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6676536</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>129704065</v>
+      </c>
+      <c r="B102" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>457293</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6677157</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF102" t="inlineStr"/>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>129721585</v>
+      </c>
+      <c r="B103" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Lagalamm, Lagalamm, Dlr</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>457426</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6676070</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>129722392</v>
+      </c>
+      <c r="B104" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>457336</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6676787</v>
+      </c>
+      <c r="S104" t="n">
+        <v>5</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Rikligt.</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>129722198</v>
+      </c>
+      <c r="B105" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>457434</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6676600</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>129717396</v>
+      </c>
+      <c r="B106" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>457284</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6677370</v>
+      </c>
+      <c r="S106" t="n">
+        <v>5</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>129721773</v>
+      </c>
+      <c r="B107" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>457411</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6676290</v>
+      </c>
+      <c r="S107" t="n">
+        <v>5</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>129722095</v>
+      </c>
+      <c r="B108" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>457440</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6676555</v>
+      </c>
+      <c r="S108" t="n">
+        <v>5</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Ganska hänlavs rikt.</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>129699541</v>
+      </c>
+      <c r="B109" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>457267</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6678042</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF109" t="inlineStr"/>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>129717610</v>
+      </c>
+      <c r="B110" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>457387</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6677155</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>129722523</v>
+      </c>
+      <c r="B111" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>457223</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6676922</v>
+      </c>
+      <c r="S111" t="n">
+        <v>5</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, mycket färska.</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>129721616</v>
+      </c>
+      <c r="B112" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Lagalamm, Lagalamm, Dlr</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>457429</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6676074</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>129722486</v>
+      </c>
+      <c r="B113" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>457247</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6676846</v>
+      </c>
+      <c r="S113" t="n">
+        <v>5</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>På flera tallar.</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>129717654</v>
+      </c>
+      <c r="B114" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>457556</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6676911</v>
+      </c>
+      <c r="S114" t="n">
+        <v>5</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>På tall.</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>129722420</v>
+      </c>
+      <c r="B115" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>457309</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6676816</v>
+      </c>
+      <c r="S115" t="n">
+        <v>5</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>129722346</v>
+      </c>
+      <c r="B116" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>457349</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6676758</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, mycket färska.</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49804-2025 artfynd.xlsx
+++ b/artfynd/A 49804-2025 artfynd.xlsx
@@ -6953,7 +6953,7 @@
         <v>129702610</v>
       </c>
       <c r="B52" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7057,10 +7057,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129700821</v>
+        <v>129699502</v>
       </c>
       <c r="B53" t="n">
-        <v>57735</v>
+        <v>79076</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7068,39 +7068,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>457486</v>
+        <v>457280</v>
       </c>
       <c r="R53" t="n">
-        <v>6677569</v>
+        <v>6678039</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7132,7 +7127,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7142,12 +7137,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7177,7 +7172,7 @@
         <v>129711613</v>
       </c>
       <c r="B54" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7284,10 +7279,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129699502</v>
+        <v>129700821</v>
       </c>
       <c r="B55" t="n">
-        <v>79075</v>
+        <v>57736</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7295,34 +7290,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>457280</v>
+        <v>457486</v>
       </c>
       <c r="R55" t="n">
-        <v>6678039</v>
+        <v>6677569</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7354,7 +7354,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7399,7 +7399,7 @@
         <v>129703897</v>
       </c>
       <c r="B56" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7513,10 +7513,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129711614</v>
+        <v>129701074</v>
       </c>
       <c r="B57" t="n">
-        <v>57732</v>
+        <v>79076</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7524,37 +7524,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>457280</v>
+        <v>457397</v>
       </c>
       <c r="R57" t="n">
-        <v>6678029</v>
+        <v>6677548</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7581,14 +7581,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Färskt födosök av spillkråka i björk stubbe.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7603,12 +7613,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -7618,7 +7628,7 @@
         <v>129700360</v>
       </c>
       <c r="B58" t="n">
-        <v>91551</v>
+        <v>91552</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7722,10 +7732,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129701074</v>
+        <v>129711614</v>
       </c>
       <c r="B59" t="n">
-        <v>79075</v>
+        <v>57733</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7733,37 +7743,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>457397</v>
+        <v>457280</v>
       </c>
       <c r="R59" t="n">
-        <v>6677548</v>
+        <v>6678029</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7790,24 +7800,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Färskt födosök av spillkråka i björk stubbe.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7822,22 +7822,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129711612</v>
+        <v>129701963</v>
       </c>
       <c r="B60" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7863,27 +7863,24 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>457358</v>
+        <v>457294</v>
       </c>
       <c r="R60" t="n">
-        <v>6677489</v>
+        <v>6677481</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7910,14 +7907,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Möjligt början på bohål i år/fjolåret.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7932,22 +7939,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129701963</v>
+        <v>129711612</v>
       </c>
       <c r="B61" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7973,24 +7980,27 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>457294</v>
+        <v>457358</v>
       </c>
       <c r="R61" t="n">
-        <v>6677481</v>
+        <v>6677489</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8017,24 +8027,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>12:43</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>12:43</t>
-        </is>
-      </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Möjligt början på bohål i år/fjolåret.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8049,12 +8049,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -8064,7 +8064,7 @@
         <v>129699824</v>
       </c>
       <c r="B62" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         <v>129700848</v>
       </c>
       <c r="B63" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>129703670</v>
       </c>
       <c r="B64" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>129703378</v>
       </c>
       <c r="B65" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8524,45 +8524,56 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129711616</v>
+        <v>129711615</v>
       </c>
       <c r="B66" t="n">
-        <v>78832</v>
+        <v>91572</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>4660</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>457305</v>
+        <v>457423</v>
       </c>
       <c r="R66" t="n">
-        <v>6677449</v>
+        <v>6677421</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -8597,12 +8608,18 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>10-15 fk på stående mindre asp.</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -8621,10 +8638,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129703525</v>
+        <v>129711616</v>
       </c>
       <c r="B67" t="n">
-        <v>57735</v>
+        <v>78833</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8632,42 +8649,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>457433</v>
+        <v>457305</v>
       </c>
       <c r="R67" t="n">
-        <v>6677123</v>
+        <v>6677449</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8694,24 +8706,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>13:41</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>13:41</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Rikligt på tall.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8726,22 +8723,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129702120</v>
+        <v>129703525</v>
       </c>
       <c r="B68" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8769,19 +8766,19 @@
       <c r="I68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>457299</v>
+        <v>457433</v>
       </c>
       <c r="R68" t="n">
-        <v>6677464</v>
+        <v>6677123</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8813,7 +8810,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8823,7 +8820,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Rikligt på tall.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8850,59 +8852,53 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129711615</v>
+        <v>129702120</v>
       </c>
       <c r="B69" t="n">
-        <v>91571</v>
+        <v>57736</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4660</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>457423</v>
+        <v>457299</v>
       </c>
       <c r="R69" t="n">
-        <v>6677421</v>
+        <v>6677464</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8929,14 +8925,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>10-15 fk på stående mindre asp.</t>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8945,19 +8946,18 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -8967,7 +8967,7 @@
         <v>129704842</v>
       </c>
       <c r="B70" t="n">
-        <v>78833</v>
+        <v>78834</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         <v>129702970</v>
       </c>
       <c r="B71" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         <v>129704395</v>
       </c>
       <c r="B72" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9305,10 +9305,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129711617</v>
+        <v>129704249</v>
       </c>
       <c r="B73" t="n">
-        <v>79075</v>
+        <v>97015</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9316,37 +9316,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>457423</v>
+        <v>457311</v>
       </c>
       <c r="R73" t="n">
-        <v>6677206</v>
+        <v>6677235</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9373,14 +9373,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>På tallstam</t>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9395,22 +9400,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129704249</v>
+        <v>129711617</v>
       </c>
       <c r="B74" t="n">
-        <v>97014</v>
+        <v>79076</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9418,37 +9423,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>457311</v>
+        <v>457423</v>
       </c>
       <c r="R74" t="n">
-        <v>6677235</v>
+        <v>6677206</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9475,19 +9480,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>14:11</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>14:11</t>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>På tallstam</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9502,62 +9502,57 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129704181</v>
+        <v>129702657</v>
       </c>
       <c r="B75" t="n">
-        <v>57735</v>
+        <v>91552</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>457325</v>
+        <v>457420</v>
       </c>
       <c r="R75" t="n">
-        <v>6677219</v>
+        <v>6677417</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9589,7 +9584,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9599,12 +9594,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9631,45 +9621,50 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129702657</v>
+        <v>129704181</v>
       </c>
       <c r="B76" t="n">
-        <v>91551</v>
+        <v>57736</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>457420</v>
+        <v>457325</v>
       </c>
       <c r="R76" t="n">
-        <v>6677417</v>
+        <v>6677219</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9701,7 +9696,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9711,7 +9706,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9738,10 +9738,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129699484</v>
+        <v>129700400</v>
       </c>
       <c r="B77" t="n">
-        <v>57735</v>
+        <v>79076</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9749,39 +9749,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>457246</v>
+        <v>457345</v>
       </c>
       <c r="R77" t="n">
-        <v>6678032</v>
+        <v>6677660</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9813,7 +9808,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9823,12 +9818,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9855,10 +9850,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129700400</v>
+        <v>129699484</v>
       </c>
       <c r="B78" t="n">
-        <v>79075</v>
+        <v>57736</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9866,34 +9861,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>457345</v>
+        <v>457246</v>
       </c>
       <c r="R78" t="n">
-        <v>6677660</v>
+        <v>6678032</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9925,7 +9925,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9970,7 +9970,7 @@
         <v>129702998</v>
       </c>
       <c r="B79" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10082,7 +10082,7 @@
         <v>129703222</v>
       </c>
       <c r="B80" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10199,7 +10199,7 @@
         <v>129703164</v>
       </c>
       <c r="B81" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10306,7 +10306,7 @@
         <v>129700616</v>
       </c>
       <c r="B82" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10415,10 +10415,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129702050</v>
+        <v>129701018</v>
       </c>
       <c r="B83" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10446,7 +10446,7 @@
       <c r="I83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -10455,10 +10455,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>457274</v>
+        <v>457426</v>
       </c>
       <c r="R83" t="n">
-        <v>6677446</v>
+        <v>6677541</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10490,7 +10490,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
@@ -10532,10 +10532,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129701018</v>
+        <v>129702050</v>
       </c>
       <c r="B84" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10563,7 +10563,7 @@
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -10572,10 +10572,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>457426</v>
+        <v>457274</v>
       </c>
       <c r="R84" t="n">
-        <v>6677541</v>
+        <v>6677446</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10607,7 +10607,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10617,7 +10617,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
@@ -10652,7 +10652,7 @@
         <v>129700434</v>
       </c>
       <c r="B85" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10766,10 +10766,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129700950</v>
+        <v>129702495</v>
       </c>
       <c r="B86" t="n">
-        <v>79075</v>
+        <v>57736</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10777,34 +10777,39 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>457431</v>
+        <v>457432</v>
       </c>
       <c r="R86" t="n">
-        <v>6677513</v>
+        <v>6677419</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10836,7 +10841,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10846,12 +10851,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10878,10 +10883,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129703077</v>
+        <v>129700968</v>
       </c>
       <c r="B87" t="n">
-        <v>79075</v>
+        <v>57736</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10889,34 +10894,39 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>457393</v>
+        <v>457428</v>
       </c>
       <c r="R87" t="n">
-        <v>6677229</v>
+        <v>6677512</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10948,7 +10958,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10958,12 +10968,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10990,10 +11000,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129704366</v>
+        <v>129700950</v>
       </c>
       <c r="B88" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11021,14 +11031,14 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>457288</v>
+        <v>457431</v>
       </c>
       <c r="R88" t="n">
-        <v>6677333</v>
+        <v>6677513</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11060,7 +11070,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11070,12 +11080,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11102,10 +11112,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129711618</v>
+        <v>129703077</v>
       </c>
       <c r="B89" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11133,17 +11143,17 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>457392</v>
+        <v>457393</v>
       </c>
       <c r="R89" t="n">
-        <v>6677547</v>
+        <v>6677229</v>
       </c>
       <c r="S89" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11170,9 +11180,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11187,22 +11212,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129702495</v>
+        <v>129704366</v>
       </c>
       <c r="B90" t="n">
-        <v>57735</v>
+        <v>79076</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11210,39 +11235,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>457432</v>
+        <v>457288</v>
       </c>
       <c r="R90" t="n">
-        <v>6677419</v>
+        <v>6677333</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11274,7 +11294,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11284,12 +11304,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11316,10 +11336,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129700968</v>
+        <v>129711618</v>
       </c>
       <c r="B91" t="n">
-        <v>57735</v>
+        <v>79076</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11327,42 +11347,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>457428</v>
+        <v>457392</v>
       </c>
       <c r="R91" t="n">
-        <v>6677512</v>
+        <v>6677547</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11389,24 +11404,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>11:56</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>11:56</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11421,12 +11421,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -11436,7 +11436,7 @@
         <v>129699765</v>
       </c>
       <c r="B92" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11550,10 +11550,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129701101</v>
+        <v>129703817</v>
       </c>
       <c r="B93" t="n">
-        <v>57735</v>
+        <v>78833</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11561,39 +11561,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>457396</v>
+        <v>457337</v>
       </c>
       <c r="R93" t="n">
-        <v>6677546</v>
+        <v>6677076</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11625,7 +11620,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11635,12 +11630,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:03</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Inte super färska.</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11667,10 +11657,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129703817</v>
+        <v>129701101</v>
       </c>
       <c r="B94" t="n">
-        <v>78832</v>
+        <v>57736</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11678,34 +11668,39 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>457337</v>
+        <v>457396</v>
       </c>
       <c r="R94" t="n">
-        <v>6677076</v>
+        <v>6677546</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11737,7 +11732,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11747,7 +11742,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Inte super färska.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11774,10 +11774,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129700098</v>
+        <v>129703127</v>
       </c>
       <c r="B95" t="n">
-        <v>57735</v>
+        <v>78833</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11785,39 +11785,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>457355</v>
+        <v>457391</v>
       </c>
       <c r="R95" t="n">
-        <v>6677771</v>
+        <v>6677213</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11849,7 +11844,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11859,12 +11854,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Inte jätte färska med syns sav fortfarande.</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11891,10 +11881,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129703127</v>
+        <v>129700098</v>
       </c>
       <c r="B96" t="n">
-        <v>78832</v>
+        <v>57736</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11902,34 +11892,39 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>457391</v>
+        <v>457355</v>
       </c>
       <c r="R96" t="n">
-        <v>6677213</v>
+        <v>6677771</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11961,7 +11956,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11971,7 +11966,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Inte jätte färska med syns sav fortfarande.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11998,10 +11998,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129717970</v>
+        <v>129722077</v>
       </c>
       <c r="B97" t="n">
-        <v>57735</v>
+        <v>91608</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12009,42 +12009,33 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>457534</v>
+        <v>457452</v>
       </c>
       <c r="R97" t="n">
-        <v>6676132</v>
+        <v>6676554</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -12073,7 +12064,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12083,12 +12074,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Ringhack på tall, hyfsat färska.</t>
+          <t>Fler fruktkroppar.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12115,10 +12106,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129722077</v>
+        <v>129717970</v>
       </c>
       <c r="B98" t="n">
-        <v>91607</v>
+        <v>57736</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12126,33 +12117,42 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>457452</v>
+        <v>457534</v>
       </c>
       <c r="R98" t="n">
-        <v>6676554</v>
+        <v>6676132</v>
       </c>
       <c r="S98" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -12181,7 +12181,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12191,12 +12191,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Fler fruktkroppar.</t>
+          <t>Ringhack på tall, hyfsat färska.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12226,7 +12226,7 @@
         <v>129722173</v>
       </c>
       <c r="B99" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12343,7 +12343,7 @@
         <v>129722296</v>
       </c>
       <c r="B100" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>129722043</v>
       </c>
       <c r="B101" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12567,7 +12567,7 @@
         <v>129704065</v>
       </c>
       <c r="B102" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12686,7 +12686,7 @@
         <v>129721585</v>
       </c>
       <c r="B103" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12793,7 +12793,7 @@
         <v>129722392</v>
       </c>
       <c r="B104" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         <v>129722198</v>
       </c>
       <c r="B105" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13027,7 +13027,7 @@
         <v>129717396</v>
       </c>
       <c r="B106" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13144,7 +13144,7 @@
         <v>129721773</v>
       </c>
       <c r="B107" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13251,7 +13251,7 @@
         <v>129722095</v>
       </c>
       <c r="B108" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13363,7 +13363,7 @@
         <v>129699541</v>
       </c>
       <c r="B109" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13479,10 +13479,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129717610</v>
+        <v>129722523</v>
       </c>
       <c r="B110" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
       <c r="I110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -13519,13 +13519,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>457387</v>
+        <v>457223</v>
       </c>
       <c r="R110" t="n">
-        <v>6677155</v>
+        <v>6676922</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -13554,7 +13554,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -13564,12 +13564,12 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack på tall, mycket färska.</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13596,10 +13596,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129722523</v>
+        <v>129717610</v>
       </c>
       <c r="B111" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13627,7 +13627,7 @@
       <c r="I111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -13636,13 +13636,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>457223</v>
+        <v>457387</v>
       </c>
       <c r="R111" t="n">
-        <v>6676922</v>
+        <v>6677155</v>
       </c>
       <c r="S111" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13671,7 +13671,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -13681,12 +13681,12 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Ringhack på tall, mycket färska.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13716,7 +13716,7 @@
         <v>129721616</v>
       </c>
       <c r="B112" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>129722486</v>
       </c>
       <c r="B113" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13935,7 +13935,7 @@
         <v>129717654</v>
       </c>
       <c r="B114" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14047,7 +14047,7 @@
         <v>129722420</v>
       </c>
       <c r="B115" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14154,7 +14154,7 @@
         <v>129722346</v>
       </c>
       <c r="B116" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>

--- a/artfynd/A 49804-2025 artfynd.xlsx
+++ b/artfynd/A 49804-2025 artfynd.xlsx
@@ -10196,7 +10196,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129703164</v>
+        <v>129700616</v>
       </c>
       <c r="B81" t="n">
         <v>79076</v>
@@ -10227,14 +10227,14 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>457394</v>
+        <v>457384</v>
       </c>
       <c r="R81" t="n">
-        <v>6677203</v>
+        <v>6677586</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10266,7 +10266,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10276,7 +10276,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10303,10 +10308,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129700616</v>
+        <v>129701018</v>
       </c>
       <c r="B82" t="n">
-        <v>79076</v>
+        <v>57736</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10314,34 +10319,39 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>457384</v>
+        <v>457426</v>
       </c>
       <c r="R82" t="n">
-        <v>6677586</v>
+        <v>6677541</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10373,7 +10383,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10383,12 +10393,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10415,7 +10425,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129701018</v>
+        <v>129702050</v>
       </c>
       <c r="B83" t="n">
         <v>57736</v>
@@ -10446,7 +10456,7 @@
       <c r="I83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -10455,10 +10465,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>457426</v>
+        <v>457274</v>
       </c>
       <c r="R83" t="n">
-        <v>6677541</v>
+        <v>6677446</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10490,7 +10500,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10500,7 +10510,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
@@ -10532,10 +10542,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129702050</v>
+        <v>129703164</v>
       </c>
       <c r="B84" t="n">
-        <v>57736</v>
+        <v>79076</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10543,39 +10553,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>457274</v>
+        <v>457394</v>
       </c>
       <c r="R84" t="n">
-        <v>6677446</v>
+        <v>6677203</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10607,7 +10612,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10617,12 +10622,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:46</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -12457,45 +12457,56 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129722043</v>
+        <v>129704065</v>
       </c>
       <c r="B101" t="n">
-        <v>79076</v>
+        <v>92870</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>457469</v>
+        <v>457293</v>
       </c>
       <c r="R101" t="n">
-        <v>6676536</v>
+        <v>6677157</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12522,22 +12533,22 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12546,6 +12557,7 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -12564,56 +12576,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129704065</v>
+        <v>129722043</v>
       </c>
       <c r="B102" t="n">
-        <v>92870</v>
+        <v>79076</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>457293</v>
+        <v>457469</v>
       </c>
       <c r="R102" t="n">
-        <v>6677157</v>
+        <v>6676536</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12640,22 +12641,22 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12664,7 +12665,6 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49804-2025 artfynd.xlsx
+++ b/artfynd/A 49804-2025 artfynd.xlsx
@@ -6953,7 +6953,7 @@
         <v>129702610</v>
       </c>
       <c r="B52" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
         <v>129699502</v>
       </c>
       <c r="B53" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7513,10 +7513,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129701074</v>
+        <v>129699824</v>
       </c>
       <c r="B57" t="n">
-        <v>79076</v>
+        <v>57736</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7524,34 +7524,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>457397</v>
+        <v>457346</v>
       </c>
       <c r="R57" t="n">
-        <v>6677548</v>
+        <v>6677881</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7583,7 +7588,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7593,12 +7598,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7628,7 +7633,7 @@
         <v>129700360</v>
       </c>
       <c r="B58" t="n">
-        <v>91552</v>
+        <v>91557</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7732,10 +7737,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129711614</v>
+        <v>129701963</v>
       </c>
       <c r="B59" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7743,16 +7748,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -7761,19 +7766,24 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>457280</v>
+        <v>457294</v>
       </c>
       <c r="R59" t="n">
-        <v>6678029</v>
+        <v>6677481</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7800,14 +7810,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Färskt födosök av spillkråka i björk stubbe.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7822,19 +7842,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129701963</v>
+        <v>129711612</v>
       </c>
       <c r="B60" t="n">
         <v>57736</v>
@@ -7863,24 +7883,27 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>457294</v>
+        <v>457358</v>
       </c>
       <c r="R60" t="n">
-        <v>6677481</v>
+        <v>6677489</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7907,24 +7930,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>12:43</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>12:43</t>
-        </is>
-      </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Möjligt början på bohål i år/fjolåret.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7939,22 +7952,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129711612</v>
+        <v>129711614</v>
       </c>
       <c r="B61" t="n">
-        <v>57736</v>
+        <v>57733</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7962,16 +7975,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -7980,24 +7993,16 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>457358</v>
+        <v>457280</v>
       </c>
       <c r="R61" t="n">
-        <v>6677489</v>
+        <v>6678029</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -8034,7 +8039,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Möjligt början på bohål i år/fjolåret.</t>
+          <t>Färskt födosök av spillkråka i björk stubbe.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8061,10 +8066,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129699824</v>
+        <v>129701074</v>
       </c>
       <c r="B62" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8072,39 +8077,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>457346</v>
+        <v>457397</v>
       </c>
       <c r="R62" t="n">
-        <v>6677881</v>
+        <v>6677548</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8136,7 +8136,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8412,48 +8412,59 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129703378</v>
+        <v>129711615</v>
       </c>
       <c r="B65" t="n">
-        <v>79076</v>
+        <v>91577</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>4660</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>457407</v>
+        <v>457423</v>
       </c>
       <c r="R65" t="n">
-        <v>6677144</v>
+        <v>6677421</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8480,24 +8491,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>10-15 fk på stående mindre asp.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8506,77 +8507,67 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129711615</v>
+        <v>129703378</v>
       </c>
       <c r="B66" t="n">
-        <v>91572</v>
+        <v>79081</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4660</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>457423</v>
+        <v>457407</v>
       </c>
       <c r="R66" t="n">
-        <v>6677421</v>
+        <v>6677144</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8603,14 +8594,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>10-15 fk på stående mindre asp.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8619,19 +8620,18 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -8641,7 +8641,7 @@
         <v>129711616</v>
       </c>
       <c r="B67" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8735,10 +8735,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129703525</v>
+        <v>129704842</v>
       </c>
       <c r="B68" t="n">
-        <v>57736</v>
+        <v>78839</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8746,39 +8746,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>457433</v>
+        <v>457230</v>
       </c>
       <c r="R68" t="n">
-        <v>6677123</v>
+        <v>6677594</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8810,7 +8805,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8820,12 +8815,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Rikligt på tall.</t>
+          <t>Lite osäker men rätt säker.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8852,7 +8847,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129702120</v>
+        <v>129703525</v>
       </c>
       <c r="B69" t="n">
         <v>57736</v>
@@ -8883,19 +8878,19 @@
       <c r="I69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>457299</v>
+        <v>457433</v>
       </c>
       <c r="R69" t="n">
-        <v>6677464</v>
+        <v>6677123</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8927,7 +8922,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8937,7 +8932,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Rikligt på tall.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8964,10 +8964,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129704842</v>
+        <v>129702120</v>
       </c>
       <c r="B70" t="n">
-        <v>78834</v>
+        <v>57736</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8975,34 +8975,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>457230</v>
+        <v>457299</v>
       </c>
       <c r="R70" t="n">
-        <v>6677594</v>
+        <v>6677464</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9034,7 +9039,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9044,12 +9049,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:36</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Lite osäker men rätt säker.</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9079,7 +9079,7 @@
         <v>129702970</v>
       </c>
       <c r="B71" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9308,7 +9308,7 @@
         <v>129704249</v>
       </c>
       <c r="B73" t="n">
-        <v>97015</v>
+        <v>97020</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
         <v>129711617</v>
       </c>
       <c r="B74" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9517,7 +9517,7 @@
         <v>129702657</v>
       </c>
       <c r="B75" t="n">
-        <v>91552</v>
+        <v>91557</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9741,7 +9741,7 @@
         <v>129700400</v>
       </c>
       <c r="B77" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>129702998</v>
       </c>
       <c r="B79" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10196,10 +10196,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129700616</v>
+        <v>129703164</v>
       </c>
       <c r="B81" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10227,14 +10227,14 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>457384</v>
+        <v>457394</v>
       </c>
       <c r="R81" t="n">
-        <v>6677586</v>
+        <v>6677203</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10266,7 +10266,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10276,12 +10276,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:40</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10308,10 +10303,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129701018</v>
+        <v>129700616</v>
       </c>
       <c r="B82" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10319,39 +10314,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>457426</v>
+        <v>457384</v>
       </c>
       <c r="R82" t="n">
-        <v>6677541</v>
+        <v>6677586</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10383,7 +10373,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10393,12 +10383,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10425,7 +10415,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129702050</v>
+        <v>129701018</v>
       </c>
       <c r="B83" t="n">
         <v>57736</v>
@@ -10456,7 +10446,7 @@
       <c r="I83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -10465,10 +10455,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>457274</v>
+        <v>457426</v>
       </c>
       <c r="R83" t="n">
-        <v>6677446</v>
+        <v>6677541</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10500,7 +10490,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10510,7 +10500,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
@@ -10542,10 +10532,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129703164</v>
+        <v>129702050</v>
       </c>
       <c r="B84" t="n">
-        <v>79076</v>
+        <v>57736</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10553,34 +10543,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>457394</v>
+        <v>457274</v>
       </c>
       <c r="R84" t="n">
-        <v>6677203</v>
+        <v>6677446</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10612,7 +10607,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10622,7 +10617,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10766,10 +10766,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129702495</v>
+        <v>129700950</v>
       </c>
       <c r="B86" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10777,39 +10777,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>457432</v>
+        <v>457431</v>
       </c>
       <c r="R86" t="n">
-        <v>6677419</v>
+        <v>6677513</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10841,7 +10836,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10851,12 +10846,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10883,10 +10878,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129700968</v>
+        <v>129703077</v>
       </c>
       <c r="B87" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10894,39 +10889,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>457428</v>
+        <v>457393</v>
       </c>
       <c r="R87" t="n">
-        <v>6677512</v>
+        <v>6677229</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10958,7 +10948,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10968,12 +10958,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11000,10 +10990,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129700950</v>
+        <v>129704366</v>
       </c>
       <c r="B88" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11031,14 +11021,14 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>457431</v>
+        <v>457288</v>
       </c>
       <c r="R88" t="n">
-        <v>6677513</v>
+        <v>6677333</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11070,7 +11060,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11080,12 +11070,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11112,10 +11102,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129703077</v>
+        <v>129711618</v>
       </c>
       <c r="B89" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11143,17 +11133,17 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>457393</v>
+        <v>457392</v>
       </c>
       <c r="R89" t="n">
-        <v>6677229</v>
+        <v>6677547</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11180,24 +11170,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>På gran.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11212,22 +11187,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129704366</v>
+        <v>129702495</v>
       </c>
       <c r="B90" t="n">
-        <v>79076</v>
+        <v>57736</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11235,34 +11210,39 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>457288</v>
+        <v>457432</v>
       </c>
       <c r="R90" t="n">
-        <v>6677333</v>
+        <v>6677419</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11294,7 +11274,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11304,12 +11284,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11336,10 +11316,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129711618</v>
+        <v>129700968</v>
       </c>
       <c r="B91" t="n">
-        <v>79076</v>
+        <v>57736</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11347,37 +11327,42 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>457392</v>
+        <v>457428</v>
       </c>
       <c r="R91" t="n">
-        <v>6677547</v>
+        <v>6677512</v>
       </c>
       <c r="S91" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11404,9 +11389,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11421,22 +11421,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129699765</v>
+        <v>129703817</v>
       </c>
       <c r="B92" t="n">
-        <v>57736</v>
+        <v>78838</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11444,39 +11444,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>457317</v>
+        <v>457337</v>
       </c>
       <c r="R92" t="n">
-        <v>6677895</v>
+        <v>6677076</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11508,7 +11503,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11518,12 +11513,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11550,10 +11540,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129703817</v>
+        <v>129701101</v>
       </c>
       <c r="B93" t="n">
-        <v>78833</v>
+        <v>57736</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11561,34 +11551,39 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>457337</v>
+        <v>457396</v>
       </c>
       <c r="R93" t="n">
-        <v>6677076</v>
+        <v>6677546</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11620,7 +11615,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11630,7 +11625,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Inte super färska.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11657,7 +11657,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129701101</v>
+        <v>129699765</v>
       </c>
       <c r="B94" t="n">
         <v>57736</v>
@@ -11688,7 +11688,7 @@
       <c r="I94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -11697,10 +11697,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>457396</v>
+        <v>457317</v>
       </c>
       <c r="R94" t="n">
-        <v>6677546</v>
+        <v>6677895</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11732,7 +11732,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11742,12 +11742,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Inte super färska.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11777,7 +11777,7 @@
         <v>129703127</v>
       </c>
       <c r="B95" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11998,10 +11998,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129722077</v>
+        <v>129717970</v>
       </c>
       <c r="B97" t="n">
-        <v>91608</v>
+        <v>57736</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12009,33 +12009,42 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>457452</v>
+        <v>457534</v>
       </c>
       <c r="R97" t="n">
-        <v>6676554</v>
+        <v>6676132</v>
       </c>
       <c r="S97" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -12064,7 +12073,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12074,12 +12083,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Fler fruktkroppar.</t>
+          <t>Ringhack på tall, hyfsat färska.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12106,10 +12115,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129717970</v>
+        <v>129722077</v>
       </c>
       <c r="B98" t="n">
-        <v>57736</v>
+        <v>91613</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12117,42 +12126,33 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>457534</v>
+        <v>457452</v>
       </c>
       <c r="R98" t="n">
-        <v>6676132</v>
+        <v>6676554</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -12181,7 +12181,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12191,12 +12191,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Ringhack på tall, hyfsat färska.</t>
+          <t>Fler fruktkroppar.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12460,7 +12460,7 @@
         <v>129704065</v>
       </c>
       <c r="B101" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12579,7 +12579,7 @@
         <v>129722043</v>
       </c>
       <c r="B102" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12686,7 +12686,7 @@
         <v>129721585</v>
       </c>
       <c r="B103" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13144,7 +13144,7 @@
         <v>129721773</v>
       </c>
       <c r="B107" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13248,48 +13248,59 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129722095</v>
+        <v>129699541</v>
       </c>
       <c r="B108" t="n">
-        <v>79076</v>
+        <v>92875</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
+          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>457440</v>
+        <v>457267</v>
       </c>
       <c r="R108" t="n">
-        <v>6676555</v>
+        <v>6678042</v>
       </c>
       <c r="S108" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -13313,27 +13324,22 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>15:19</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Ganska hänlavs rikt.</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13342,6 +13348,7 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -13360,59 +13367,48 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129699541</v>
+        <v>129722095</v>
       </c>
       <c r="B109" t="n">
-        <v>92870</v>
+        <v>79081</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
+          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>457267</v>
+        <v>457440</v>
       </c>
       <c r="R109" t="n">
-        <v>6678042</v>
+        <v>6676555</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -13436,22 +13432,27 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Ganska hänlavs rikt.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13460,7 +13461,6 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
@@ -13716,7 +13716,7 @@
         <v>129721616</v>
       </c>
       <c r="B112" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>129722486</v>
       </c>
       <c r="B113" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13935,7 +13935,7 @@
         <v>129717654</v>
       </c>
       <c r="B114" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14047,7 +14047,7 @@
         <v>129722420</v>
       </c>
       <c r="B115" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>

--- a/artfynd/A 49804-2025 artfynd.xlsx
+++ b/artfynd/A 49804-2025 artfynd.xlsx
@@ -7057,10 +7057,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129699502</v>
+        <v>129711613</v>
       </c>
       <c r="B53" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7068,37 +7068,45 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>457280</v>
+        <v>457300</v>
       </c>
       <c r="R53" t="n">
-        <v>6678039</v>
+        <v>6678044</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7125,24 +7133,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Barkflagning</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7157,19 +7155,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129711613</v>
+        <v>129700821</v>
       </c>
       <c r="B54" t="n">
         <v>57736</v>
@@ -7198,27 +7196,24 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>457300</v>
+        <v>457486</v>
       </c>
       <c r="R54" t="n">
-        <v>6678044</v>
+        <v>6677569</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7245,14 +7240,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Barkflagning</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7267,22 +7272,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129700821</v>
+        <v>129699502</v>
       </c>
       <c r="B55" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7290,39 +7295,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>457486</v>
+        <v>457280</v>
       </c>
       <c r="R55" t="n">
-        <v>6677569</v>
+        <v>6678039</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7354,7 +7354,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7513,50 +7513,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129699824</v>
+        <v>129700360</v>
       </c>
       <c r="B57" t="n">
-        <v>57736</v>
+        <v>91557</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>457346</v>
+        <v>457345</v>
       </c>
       <c r="R57" t="n">
-        <v>6677881</v>
+        <v>6677677</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7588,7 +7583,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7598,12 +7593,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:04</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7630,48 +7620,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129700360</v>
+        <v>129711614</v>
       </c>
       <c r="B58" t="n">
-        <v>91557</v>
+        <v>57733</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>457345</v>
+        <v>457280</v>
       </c>
       <c r="R58" t="n">
-        <v>6677677</v>
+        <v>6678029</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7698,19 +7688,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>11:26</t>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Färskt födosök av spillkråka i björk stubbe.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7725,22 +7710,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129701963</v>
+        <v>129701074</v>
       </c>
       <c r="B59" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7748,39 +7733,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>457294</v>
+        <v>457397</v>
       </c>
       <c r="R59" t="n">
-        <v>6677481</v>
+        <v>6677548</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7812,7 +7792,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7822,12 +7802,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7854,7 +7834,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129711612</v>
+        <v>129701963</v>
       </c>
       <c r="B60" t="n">
         <v>57736</v>
@@ -7883,27 +7863,24 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>457358</v>
+        <v>457294</v>
       </c>
       <c r="R60" t="n">
-        <v>6677489</v>
+        <v>6677481</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7930,14 +7907,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Möjligt början på bohål i år/fjolåret.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7952,22 +7939,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129711614</v>
+        <v>129711612</v>
       </c>
       <c r="B61" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7975,16 +7962,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -7993,16 +7980,24 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>457280</v>
+        <v>457358</v>
       </c>
       <c r="R61" t="n">
-        <v>6678029</v>
+        <v>6677489</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -8039,7 +8034,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Färskt födosök av spillkråka i björk stubbe.</t>
+          <t>Möjligt början på bohål i år/fjolåret.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8066,10 +8061,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129701074</v>
+        <v>129699824</v>
       </c>
       <c r="B62" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8077,34 +8072,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>457397</v>
+        <v>457346</v>
       </c>
       <c r="R62" t="n">
-        <v>6677548</v>
+        <v>6677881</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8136,7 +8136,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8526,10 +8526,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129703378</v>
+        <v>129703525</v>
       </c>
       <c r="B66" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8537,34 +8537,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>457407</v>
+        <v>457433</v>
       </c>
       <c r="R66" t="n">
-        <v>6677144</v>
+        <v>6677123</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8596,7 +8601,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8606,12 +8611,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Rikligt på tall.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8638,10 +8643,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129711616</v>
+        <v>129702120</v>
       </c>
       <c r="B67" t="n">
-        <v>78838</v>
+        <v>57736</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8649,37 +8654,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>457305</v>
+        <v>457299</v>
       </c>
       <c r="R67" t="n">
-        <v>6677449</v>
+        <v>6677464</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8706,9 +8716,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8723,22 +8743,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129704842</v>
+        <v>129703378</v>
       </c>
       <c r="B68" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8746,34 +8766,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>457230</v>
+        <v>457407</v>
       </c>
       <c r="R68" t="n">
-        <v>6677594</v>
+        <v>6677144</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8805,7 +8825,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8815,12 +8835,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Lite osäker men rätt säker.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8847,10 +8867,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129703525</v>
+        <v>129711616</v>
       </c>
       <c r="B69" t="n">
-        <v>57736</v>
+        <v>78838</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8858,42 +8878,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>457433</v>
+        <v>457305</v>
       </c>
       <c r="R69" t="n">
-        <v>6677123</v>
+        <v>6677449</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8920,24 +8935,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>13:41</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>13:41</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Rikligt på tall.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8952,22 +8952,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129702120</v>
+        <v>129704842</v>
       </c>
       <c r="B70" t="n">
-        <v>57736</v>
+        <v>78839</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8975,39 +8975,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>457299</v>
+        <v>457230</v>
       </c>
       <c r="R70" t="n">
-        <v>6677464</v>
+        <v>6677594</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9039,7 +9034,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9049,7 +9044,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Lite osäker men rätt säker.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9076,10 +9076,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129702970</v>
+        <v>129704395</v>
       </c>
       <c r="B71" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9087,34 +9087,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>457390</v>
+        <v>457267</v>
       </c>
       <c r="R71" t="n">
-        <v>6677240</v>
+        <v>6677342</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9146,7 +9151,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9156,12 +9161,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9188,10 +9193,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129704395</v>
+        <v>129702970</v>
       </c>
       <c r="B72" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9199,39 +9204,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>457267</v>
+        <v>457390</v>
       </c>
       <c r="R72" t="n">
-        <v>6677342</v>
+        <v>6677240</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9263,7 +9263,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9273,12 +9273,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9738,10 +9738,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129700400</v>
+        <v>129699484</v>
       </c>
       <c r="B77" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9749,34 +9749,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>457345</v>
+        <v>457246</v>
       </c>
       <c r="R77" t="n">
-        <v>6677660</v>
+        <v>6678032</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9808,7 +9813,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9818,12 +9823,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9850,10 +9855,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129699484</v>
+        <v>129700400</v>
       </c>
       <c r="B78" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9861,39 +9866,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>457246</v>
+        <v>457345</v>
       </c>
       <c r="R78" t="n">
-        <v>6678032</v>
+        <v>6677660</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9925,7 +9925,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -11540,7 +11540,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129701101</v>
+        <v>129699765</v>
       </c>
       <c r="B93" t="n">
         <v>57736</v>
@@ -11571,7 +11571,7 @@
       <c r="I93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -11580,10 +11580,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>457396</v>
+        <v>457317</v>
       </c>
       <c r="R93" t="n">
-        <v>6677546</v>
+        <v>6677895</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11615,7 +11615,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11625,12 +11625,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Inte super färska.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11657,7 +11657,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129699765</v>
+        <v>129701101</v>
       </c>
       <c r="B94" t="n">
         <v>57736</v>
@@ -11688,7 +11688,7 @@
       <c r="I94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -11697,10 +11697,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>457317</v>
+        <v>457396</v>
       </c>
       <c r="R94" t="n">
-        <v>6677895</v>
+        <v>6677546</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11732,7 +11732,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11742,12 +11742,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Inte super färska.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11998,10 +11998,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129717970</v>
+        <v>129722077</v>
       </c>
       <c r="B97" t="n">
-        <v>57736</v>
+        <v>91613</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12009,42 +12009,33 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>457534</v>
+        <v>457452</v>
       </c>
       <c r="R97" t="n">
-        <v>6676132</v>
+        <v>6676554</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -12073,7 +12064,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12083,12 +12074,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Ringhack på tall, hyfsat färska.</t>
+          <t>Fler fruktkroppar.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12115,10 +12106,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129722077</v>
+        <v>129717970</v>
       </c>
       <c r="B98" t="n">
-        <v>91613</v>
+        <v>57736</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12126,33 +12117,42 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>457452</v>
+        <v>457534</v>
       </c>
       <c r="R98" t="n">
-        <v>6676554</v>
+        <v>6676132</v>
       </c>
       <c r="S98" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -12181,7 +12181,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12191,12 +12191,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Fler fruktkroppar.</t>
+          <t>Ringhack på tall, hyfsat färska.</t>
         </is>
       </c>
       <c r="AD98" t="b">

--- a/artfynd/A 49804-2025 artfynd.xlsx
+++ b/artfynd/A 49804-2025 artfynd.xlsx
@@ -6950,7 +6950,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129702610</v>
+        <v>129699502</v>
       </c>
       <c r="B52" t="n">
         <v>79081</v>
@@ -6981,14 +6981,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>457417</v>
+        <v>457280</v>
       </c>
       <c r="R52" t="n">
-        <v>6677423</v>
+        <v>6678039</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7030,7 +7030,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7057,10 +7062,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129711613</v>
+        <v>129702610</v>
       </c>
       <c r="B53" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7068,45 +7073,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>457300</v>
+        <v>457417</v>
       </c>
       <c r="R53" t="n">
-        <v>6678044</v>
+        <v>6677423</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7133,14 +7130,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Barkflagning</t>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7155,19 +7157,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129700821</v>
+        <v>129711613</v>
       </c>
       <c r="B54" t="n">
         <v>57736</v>
@@ -7196,24 +7198,27 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>457486</v>
+        <v>457300</v>
       </c>
       <c r="R54" t="n">
-        <v>6677569</v>
+        <v>6678044</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7240,24 +7245,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>11:49</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>11:49</t>
-        </is>
-      </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Barkflagning</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7272,22 +7267,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129699502</v>
+        <v>129700821</v>
       </c>
       <c r="B55" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7295,34 +7290,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>457280</v>
+        <v>457486</v>
       </c>
       <c r="R55" t="n">
-        <v>6678039</v>
+        <v>6677569</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7354,7 +7354,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7513,32 +7513,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129700360</v>
+        <v>129701074</v>
       </c>
       <c r="B57" t="n">
-        <v>91557</v>
+        <v>79081</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7548,10 +7548,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>457345</v>
+        <v>457397</v>
       </c>
       <c r="R57" t="n">
-        <v>6677677</v>
+        <v>6677548</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7593,7 +7593,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7620,10 +7625,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129711614</v>
+        <v>129701963</v>
       </c>
       <c r="B58" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7631,16 +7636,16 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -7649,19 +7654,24 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>457280</v>
+        <v>457294</v>
       </c>
       <c r="R58" t="n">
-        <v>6678029</v>
+        <v>6677481</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7688,14 +7698,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Färskt födosök av spillkråka i björk stubbe.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7710,22 +7730,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129701074</v>
+        <v>129711612</v>
       </c>
       <c r="B59" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7733,37 +7753,45 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>457397</v>
+        <v>457358</v>
       </c>
       <c r="R59" t="n">
-        <v>6677548</v>
+        <v>6677489</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7790,24 +7818,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Möjligt början på bohål i år/fjolåret.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7822,62 +7840,57 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129701963</v>
+        <v>129700360</v>
       </c>
       <c r="B60" t="n">
-        <v>57736</v>
+        <v>91557</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>457294</v>
+        <v>457345</v>
       </c>
       <c r="R60" t="n">
-        <v>6677481</v>
+        <v>6677677</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7909,7 +7922,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7919,12 +7932,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:43</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7951,7 +7959,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129711612</v>
+        <v>129699824</v>
       </c>
       <c r="B61" t="n">
         <v>57736</v>
@@ -7980,27 +7988,24 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>457358</v>
+        <v>457346</v>
       </c>
       <c r="R61" t="n">
-        <v>6677489</v>
+        <v>6677881</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8027,14 +8032,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Möjligt början på bohål i år/fjolåret.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8049,22 +8064,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129699824</v>
+        <v>129711614</v>
       </c>
       <c r="B62" t="n">
-        <v>57736</v>
+        <v>57733</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8072,16 +8087,16 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -8090,24 +8105,19 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>457346</v>
+        <v>457280</v>
       </c>
       <c r="R62" t="n">
-        <v>6677881</v>
+        <v>6678029</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8134,24 +8144,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Färskt födosök av spillkråka i björk stubbe.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8166,12 +8166,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -8412,59 +8412,48 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129711615</v>
+        <v>129704842</v>
       </c>
       <c r="B65" t="n">
-        <v>91577</v>
+        <v>78839</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4660</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>457423</v>
+        <v>457230</v>
       </c>
       <c r="R65" t="n">
-        <v>6677421</v>
+        <v>6677594</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8491,14 +8480,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>10-15 fk på stående mindre asp.</t>
+          <t>Lite osäker men rätt säker.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8507,26 +8506,25 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129703525</v>
+        <v>129702120</v>
       </c>
       <c r="B66" t="n">
         <v>57736</v>
@@ -8557,19 +8555,19 @@
       <c r="I66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>457433</v>
+        <v>457299</v>
       </c>
       <c r="R66" t="n">
-        <v>6677123</v>
+        <v>6677464</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8601,7 +8599,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8611,12 +8609,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:41</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Rikligt på tall.</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8643,7 +8636,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129702120</v>
+        <v>129703525</v>
       </c>
       <c r="B67" t="n">
         <v>57736</v>
@@ -8674,19 +8667,19 @@
       <c r="I67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>457299</v>
+        <v>457433</v>
       </c>
       <c r="R67" t="n">
-        <v>6677464</v>
+        <v>6677123</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8718,7 +8711,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8728,7 +8721,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Rikligt på tall.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8867,45 +8865,56 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129711616</v>
+        <v>129711615</v>
       </c>
       <c r="B69" t="n">
-        <v>78838</v>
+        <v>91577</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>4660</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>457305</v>
+        <v>457423</v>
       </c>
       <c r="R69" t="n">
-        <v>6677449</v>
+        <v>6677421</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -8940,12 +8949,18 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>10-15 fk på stående mindre asp.</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8964,10 +8979,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129704842</v>
+        <v>129711616</v>
       </c>
       <c r="B70" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8975,37 +8990,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>457230</v>
+        <v>457305</v>
       </c>
       <c r="R70" t="n">
-        <v>6677594</v>
+        <v>6677449</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9032,24 +9047,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Lite osäker men rätt säker.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9064,22 +9064,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129704395</v>
+        <v>129702970</v>
       </c>
       <c r="B71" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9087,39 +9087,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>457267</v>
+        <v>457390</v>
       </c>
       <c r="R71" t="n">
-        <v>6677342</v>
+        <v>6677240</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9151,7 +9146,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9161,12 +9156,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9193,10 +9188,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129702970</v>
+        <v>129704395</v>
       </c>
       <c r="B72" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9204,34 +9199,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>457390</v>
+        <v>457267</v>
       </c>
       <c r="R72" t="n">
-        <v>6677240</v>
+        <v>6677342</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9263,7 +9263,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9273,12 +9273,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9305,10 +9305,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129704249</v>
+        <v>129711617</v>
       </c>
       <c r="B73" t="n">
-        <v>97020</v>
+        <v>79081</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9316,37 +9316,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>457311</v>
+        <v>457423</v>
       </c>
       <c r="R73" t="n">
-        <v>6677235</v>
+        <v>6677206</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9373,19 +9373,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>14:11</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>14:11</t>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>På tallstam</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9400,22 +9395,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129711617</v>
+        <v>129704249</v>
       </c>
       <c r="B74" t="n">
-        <v>79081</v>
+        <v>97020</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9423,37 +9418,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>457423</v>
+        <v>457311</v>
       </c>
       <c r="R74" t="n">
-        <v>6677206</v>
+        <v>6677235</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9480,14 +9475,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>På tallstam</t>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9502,12 +9502,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -9738,10 +9738,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129699484</v>
+        <v>129700400</v>
       </c>
       <c r="B77" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9749,39 +9749,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>457246</v>
+        <v>457345</v>
       </c>
       <c r="R77" t="n">
-        <v>6678032</v>
+        <v>6677660</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9813,7 +9808,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9823,12 +9818,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9855,10 +9850,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129700400</v>
+        <v>129699484</v>
       </c>
       <c r="B78" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9866,34 +9861,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>457345</v>
+        <v>457246</v>
       </c>
       <c r="R78" t="n">
-        <v>6677660</v>
+        <v>6678032</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9925,7 +9925,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10415,7 +10415,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129701018</v>
+        <v>129702050</v>
       </c>
       <c r="B83" t="n">
         <v>57736</v>
@@ -10446,7 +10446,7 @@
       <c r="I83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -10455,10 +10455,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>457426</v>
+        <v>457274</v>
       </c>
       <c r="R83" t="n">
-        <v>6677541</v>
+        <v>6677446</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10490,7 +10490,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
@@ -10532,7 +10532,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129702050</v>
+        <v>129701018</v>
       </c>
       <c r="B84" t="n">
         <v>57736</v>
@@ -10563,7 +10563,7 @@
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -10572,10 +10572,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>457274</v>
+        <v>457426</v>
       </c>
       <c r="R84" t="n">
-        <v>6677446</v>
+        <v>6677541</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10607,7 +10607,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10617,7 +10617,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
@@ -10766,7 +10766,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129700950</v>
+        <v>129703077</v>
       </c>
       <c r="B86" t="n">
         <v>79081</v>
@@ -10797,14 +10797,14 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>457431</v>
+        <v>457393</v>
       </c>
       <c r="R86" t="n">
-        <v>6677513</v>
+        <v>6677229</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10836,7 +10836,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10846,7 +10846,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
@@ -10878,10 +10878,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129703077</v>
+        <v>129700968</v>
       </c>
       <c r="B87" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10889,34 +10889,39 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>457393</v>
+        <v>457428</v>
       </c>
       <c r="R87" t="n">
-        <v>6677229</v>
+        <v>6677512</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10948,7 +10953,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10958,12 +10963,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10990,10 +10995,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129704366</v>
+        <v>129702495</v>
       </c>
       <c r="B88" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11001,34 +11006,39 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>457288</v>
+        <v>457432</v>
       </c>
       <c r="R88" t="n">
-        <v>6677333</v>
+        <v>6677419</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11060,7 +11070,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11070,12 +11080,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11102,7 +11112,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129711618</v>
+        <v>129700950</v>
       </c>
       <c r="B89" t="n">
         <v>79081</v>
@@ -11133,17 +11143,17 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>457392</v>
+        <v>457431</v>
       </c>
       <c r="R89" t="n">
-        <v>6677547</v>
+        <v>6677513</v>
       </c>
       <c r="S89" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11170,9 +11180,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11187,22 +11212,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129702495</v>
+        <v>129704366</v>
       </c>
       <c r="B90" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11210,39 +11235,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>457432</v>
+        <v>457288</v>
       </c>
       <c r="R90" t="n">
-        <v>6677419</v>
+        <v>6677333</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11274,7 +11294,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11284,12 +11304,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11316,10 +11336,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129700968</v>
+        <v>129711618</v>
       </c>
       <c r="B91" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11327,42 +11347,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>457428</v>
+        <v>457392</v>
       </c>
       <c r="R91" t="n">
-        <v>6677512</v>
+        <v>6677547</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11389,24 +11404,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>11:56</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>11:56</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11421,12 +11421,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -12457,56 +12457,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129704065</v>
+        <v>129722043</v>
       </c>
       <c r="B101" t="n">
-        <v>92875</v>
+        <v>79081</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>457293</v>
+        <v>457469</v>
       </c>
       <c r="R101" t="n">
-        <v>6677157</v>
+        <v>6676536</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12533,22 +12522,22 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12557,7 +12546,6 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -12576,45 +12564,56 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129722043</v>
+        <v>129704065</v>
       </c>
       <c r="B102" t="n">
-        <v>79081</v>
+        <v>92875</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>457469</v>
+        <v>457293</v>
       </c>
       <c r="R102" t="n">
-        <v>6676536</v>
+        <v>6677157</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12641,22 +12640,22 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12665,6 +12664,7 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -12683,10 +12683,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129721585</v>
+        <v>129722392</v>
       </c>
       <c r="B103" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12694,37 +12694,42 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Lagalamm, Lagalamm, Dlr</t>
+          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>457426</v>
+        <v>457336</v>
       </c>
       <c r="R103" t="n">
-        <v>6676070</v>
+        <v>6676787</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12753,7 +12758,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12763,7 +12768,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Rikligt.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12790,10 +12800,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129722392</v>
+        <v>129721585</v>
       </c>
       <c r="B104" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12801,42 +12811,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
+          <t>Lagalamm, Lagalamm, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>457336</v>
+        <v>457426</v>
       </c>
       <c r="R104" t="n">
-        <v>6676787</v>
+        <v>6676070</v>
       </c>
       <c r="S104" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12865,7 +12870,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12875,12 +12880,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:36</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Rikligt.</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13713,7 +13713,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129721616</v>
+        <v>129722486</v>
       </c>
       <c r="B112" t="n">
         <v>79081</v>
@@ -13744,17 +13744,17 @@
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Lagalamm, Lagalamm, Dlr</t>
+          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>457429</v>
+        <v>457247</v>
       </c>
       <c r="R112" t="n">
-        <v>6676074</v>
+        <v>6676846</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -13783,7 +13783,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -13793,7 +13793,12 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>På flera tallar.</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13820,7 +13825,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129722486</v>
+        <v>129717654</v>
       </c>
       <c r="B113" t="n">
         <v>79081</v>
@@ -13851,14 +13856,14 @@
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>457247</v>
+        <v>457556</v>
       </c>
       <c r="R113" t="n">
-        <v>6676846</v>
+        <v>6676911</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -13890,7 +13895,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -13900,12 +13905,12 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>På flera tallar.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13932,7 +13937,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129717654</v>
+        <v>129721616</v>
       </c>
       <c r="B114" t="n">
         <v>79081</v>
@@ -13963,17 +13968,17 @@
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Lagalamm, Lagalamm, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>457556</v>
+        <v>457429</v>
       </c>
       <c r="R114" t="n">
-        <v>6676911</v>
+        <v>6676074</v>
       </c>
       <c r="S114" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -14002,7 +14007,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -14012,12 +14017,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>12:03</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD114" t="b">

--- a/artfynd/A 49804-2025 artfynd.xlsx
+++ b/artfynd/A 49804-2025 artfynd.xlsx
@@ -6950,7 +6950,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129699502</v>
+        <v>129702610</v>
       </c>
       <c r="B52" t="n">
         <v>79081</v>
@@ -6981,14 +6981,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>457280</v>
+        <v>457417</v>
       </c>
       <c r="R52" t="n">
-        <v>6678039</v>
+        <v>6677423</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7030,12 +7030,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:48</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7062,7 +7057,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129702610</v>
+        <v>129699502</v>
       </c>
       <c r="B53" t="n">
         <v>79081</v>
@@ -7093,14 +7088,14 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>457417</v>
+        <v>457280</v>
       </c>
       <c r="R53" t="n">
-        <v>6677423</v>
+        <v>6678039</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7132,7 +7127,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7142,7 +7137,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7513,10 +7513,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129701074</v>
+        <v>129699824</v>
       </c>
       <c r="B57" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7524,34 +7524,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>457397</v>
+        <v>457346</v>
       </c>
       <c r="R57" t="n">
-        <v>6677548</v>
+        <v>6677881</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7583,7 +7588,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7593,12 +7598,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7625,10 +7630,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129701963</v>
+        <v>129711614</v>
       </c>
       <c r="B58" t="n">
-        <v>57736</v>
+        <v>57733</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7636,16 +7641,16 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -7654,24 +7659,19 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>457294</v>
+        <v>457280</v>
       </c>
       <c r="R58" t="n">
-        <v>6677481</v>
+        <v>6678029</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7698,24 +7698,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>12:43</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>12:43</t>
-        </is>
-      </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Färskt födosök av spillkråka i björk stubbe.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7730,22 +7720,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129711612</v>
+        <v>129701074</v>
       </c>
       <c r="B59" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7753,45 +7743,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>457358</v>
+        <v>457397</v>
       </c>
       <c r="R59" t="n">
-        <v>6677489</v>
+        <v>6677548</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7818,14 +7800,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Möjligt början på bohål i år/fjolåret.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7840,12 +7832,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -7959,7 +7951,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129699824</v>
+        <v>129701963</v>
       </c>
       <c r="B61" t="n">
         <v>57736</v>
@@ -7990,7 +7982,7 @@
       <c r="I61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7999,10 +7991,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>457346</v>
+        <v>457294</v>
       </c>
       <c r="R61" t="n">
-        <v>6677881</v>
+        <v>6677481</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8034,7 +8026,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8044,7 +8036,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
@@ -8076,10 +8068,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129711614</v>
+        <v>129711612</v>
       </c>
       <c r="B62" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8087,16 +8079,16 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -8105,16 +8097,24 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>457280</v>
+        <v>457358</v>
       </c>
       <c r="R62" t="n">
-        <v>6678029</v>
+        <v>6677489</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -8151,7 +8151,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Färskt födosök av spillkråka i björk stubbe.</t>
+          <t>Möjligt början på bohål i år/fjolåret.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8412,10 +8412,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129704842</v>
+        <v>129711616</v>
       </c>
       <c r="B65" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8423,37 +8423,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>457230</v>
+        <v>457305</v>
       </c>
       <c r="R65" t="n">
-        <v>6677594</v>
+        <v>6677449</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8480,24 +8480,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Lite osäker men rätt säker.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8512,19 +8497,19 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129702120</v>
+        <v>129703525</v>
       </c>
       <c r="B66" t="n">
         <v>57736</v>
@@ -8555,19 +8540,19 @@
       <c r="I66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>457299</v>
+        <v>457433</v>
       </c>
       <c r="R66" t="n">
-        <v>6677464</v>
+        <v>6677123</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8599,7 +8584,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8609,7 +8594,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Rikligt på tall.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8636,7 +8626,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129703525</v>
+        <v>129702120</v>
       </c>
       <c r="B67" t="n">
         <v>57736</v>
@@ -8667,19 +8657,19 @@
       <c r="I67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>457433</v>
+        <v>457299</v>
       </c>
       <c r="R67" t="n">
-        <v>6677123</v>
+        <v>6677464</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8711,7 +8701,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8721,12 +8711,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:41</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Rikligt på tall.</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8979,10 +8964,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129711616</v>
+        <v>129704842</v>
       </c>
       <c r="B70" t="n">
-        <v>78838</v>
+        <v>78839</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8990,37 +8975,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>457305</v>
+        <v>457230</v>
       </c>
       <c r="R70" t="n">
-        <v>6677449</v>
+        <v>6677594</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9047,9 +9032,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Lite osäker men rätt säker.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9064,22 +9064,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129702970</v>
+        <v>129704395</v>
       </c>
       <c r="B71" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9087,34 +9087,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>457390</v>
+        <v>457267</v>
       </c>
       <c r="R71" t="n">
-        <v>6677240</v>
+        <v>6677342</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9146,7 +9151,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9156,12 +9161,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9188,10 +9193,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129704395</v>
+        <v>129702970</v>
       </c>
       <c r="B72" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9199,39 +9204,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>457267</v>
+        <v>457390</v>
       </c>
       <c r="R72" t="n">
-        <v>6677342</v>
+        <v>6677240</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9263,7 +9263,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9273,12 +9273,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9305,10 +9305,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129711617</v>
+        <v>129704249</v>
       </c>
       <c r="B73" t="n">
-        <v>79081</v>
+        <v>97020</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9316,37 +9316,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>457423</v>
+        <v>457311</v>
       </c>
       <c r="R73" t="n">
-        <v>6677206</v>
+        <v>6677235</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9373,14 +9373,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>På tallstam</t>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9395,22 +9400,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129704249</v>
+        <v>129711617</v>
       </c>
       <c r="B74" t="n">
-        <v>97020</v>
+        <v>79081</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9418,37 +9423,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>457311</v>
+        <v>457423</v>
       </c>
       <c r="R74" t="n">
-        <v>6677235</v>
+        <v>6677206</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9475,19 +9480,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>14:11</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>14:11</t>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>På tallstam</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9502,12 +9502,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -9738,10 +9738,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129700400</v>
+        <v>129699484</v>
       </c>
       <c r="B77" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9749,34 +9749,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>457345</v>
+        <v>457246</v>
       </c>
       <c r="R77" t="n">
-        <v>6677660</v>
+        <v>6678032</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9808,7 +9813,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9818,12 +9823,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9850,10 +9855,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129699484</v>
+        <v>129700400</v>
       </c>
       <c r="B78" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9861,39 +9866,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>457246</v>
+        <v>457345</v>
       </c>
       <c r="R78" t="n">
-        <v>6678032</v>
+        <v>6677660</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9925,7 +9925,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10415,7 +10415,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129702050</v>
+        <v>129701018</v>
       </c>
       <c r="B83" t="n">
         <v>57736</v>
@@ -10446,7 +10446,7 @@
       <c r="I83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -10455,10 +10455,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>457274</v>
+        <v>457426</v>
       </c>
       <c r="R83" t="n">
-        <v>6677446</v>
+        <v>6677541</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10490,7 +10490,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
@@ -10532,7 +10532,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129701018</v>
+        <v>129702050</v>
       </c>
       <c r="B84" t="n">
         <v>57736</v>
@@ -10563,7 +10563,7 @@
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -10572,10 +10572,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>457426</v>
+        <v>457274</v>
       </c>
       <c r="R84" t="n">
-        <v>6677541</v>
+        <v>6677446</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10607,7 +10607,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10617,7 +10617,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
@@ -10766,7 +10766,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129703077</v>
+        <v>129700950</v>
       </c>
       <c r="B86" t="n">
         <v>79081</v>
@@ -10797,14 +10797,14 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>457393</v>
+        <v>457431</v>
       </c>
       <c r="R86" t="n">
-        <v>6677229</v>
+        <v>6677513</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10836,7 +10836,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10846,7 +10846,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
@@ -10878,10 +10878,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129700968</v>
+        <v>129703077</v>
       </c>
       <c r="B87" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10889,39 +10889,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>457428</v>
+        <v>457393</v>
       </c>
       <c r="R87" t="n">
-        <v>6677512</v>
+        <v>6677229</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10953,7 +10948,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10963,12 +10958,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10995,10 +10990,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129702495</v>
+        <v>129704366</v>
       </c>
       <c r="B88" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11006,39 +11001,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>457432</v>
+        <v>457288</v>
       </c>
       <c r="R88" t="n">
-        <v>6677419</v>
+        <v>6677333</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11070,7 +11060,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11080,12 +11070,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11112,7 +11102,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129700950</v>
+        <v>129711618</v>
       </c>
       <c r="B89" t="n">
         <v>79081</v>
@@ -11143,17 +11133,17 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>457431</v>
+        <v>457392</v>
       </c>
       <c r="R89" t="n">
-        <v>6677513</v>
+        <v>6677547</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11180,24 +11170,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>På gran.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11212,22 +11187,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129704366</v>
+        <v>129702495</v>
       </c>
       <c r="B90" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11235,34 +11210,39 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>457288</v>
+        <v>457432</v>
       </c>
       <c r="R90" t="n">
-        <v>6677333</v>
+        <v>6677419</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11294,7 +11274,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11304,12 +11284,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11336,10 +11316,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129711618</v>
+        <v>129700968</v>
       </c>
       <c r="B91" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11347,37 +11327,42 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>457392</v>
+        <v>457428</v>
       </c>
       <c r="R91" t="n">
-        <v>6677547</v>
+        <v>6677512</v>
       </c>
       <c r="S91" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11404,9 +11389,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11421,22 +11421,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129703817</v>
+        <v>129701101</v>
       </c>
       <c r="B92" t="n">
-        <v>78838</v>
+        <v>57736</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11444,34 +11444,39 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>457337</v>
+        <v>457396</v>
       </c>
       <c r="R92" t="n">
-        <v>6677076</v>
+        <v>6677546</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11503,7 +11508,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11513,7 +11518,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Inte super färska.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11657,10 +11667,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129701101</v>
+        <v>129703817</v>
       </c>
       <c r="B94" t="n">
-        <v>57736</v>
+        <v>78838</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11668,39 +11678,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>457396</v>
+        <v>457337</v>
       </c>
       <c r="R94" t="n">
-        <v>6677546</v>
+        <v>6677076</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11732,7 +11737,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11742,12 +11747,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:03</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Inte super färska.</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -13248,59 +13248,48 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129699541</v>
+        <v>129722095</v>
       </c>
       <c r="B108" t="n">
-        <v>92875</v>
+        <v>79081</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
+          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>457267</v>
+        <v>457440</v>
       </c>
       <c r="R108" t="n">
-        <v>6678042</v>
+        <v>6676555</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -13324,22 +13313,27 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Ganska hänlavs rikt.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13348,7 +13342,6 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -13367,48 +13360,59 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129722095</v>
+        <v>129699541</v>
       </c>
       <c r="B109" t="n">
-        <v>79081</v>
+        <v>92875</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
+          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>457440</v>
+        <v>457267</v>
       </c>
       <c r="R109" t="n">
-        <v>6676555</v>
+        <v>6678042</v>
       </c>
       <c r="S109" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -13432,27 +13436,22 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>15:19</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Ganska hänlavs rikt.</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13461,6 +13460,7 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
@@ -13713,7 +13713,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129722486</v>
+        <v>129721616</v>
       </c>
       <c r="B112" t="n">
         <v>79081</v>
@@ -13744,17 +13744,17 @@
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
+          <t>Lagalamm, Lagalamm, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>457247</v>
+        <v>457429</v>
       </c>
       <c r="R112" t="n">
-        <v>6676846</v>
+        <v>6676074</v>
       </c>
       <c r="S112" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -13783,7 +13783,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -13793,12 +13793,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>På flera tallar.</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13825,7 +13820,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129717654</v>
+        <v>129722486</v>
       </c>
       <c r="B113" t="n">
         <v>79081</v>
@@ -13856,14 +13851,14 @@
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>457556</v>
+        <v>457247</v>
       </c>
       <c r="R113" t="n">
-        <v>6676911</v>
+        <v>6676846</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -13895,7 +13890,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -13905,12 +13900,12 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>På flera tallar.</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13937,7 +13932,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129721616</v>
+        <v>129717654</v>
       </c>
       <c r="B114" t="n">
         <v>79081</v>
@@ -13968,17 +13963,17 @@
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Lagalamm, Lagalamm, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>457429</v>
+        <v>457556</v>
       </c>
       <c r="R114" t="n">
-        <v>6676074</v>
+        <v>6676911</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -14007,7 +14002,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -14017,7 +14012,12 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD114" t="b">

--- a/artfynd/A 49804-2025 artfynd.xlsx
+++ b/artfynd/A 49804-2025 artfynd.xlsx
@@ -6950,10 +6950,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129702610</v>
+        <v>129700821</v>
       </c>
       <c r="B52" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6961,34 +6961,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>457417</v>
+        <v>457486</v>
       </c>
       <c r="R52" t="n">
-        <v>6677423</v>
+        <v>6677569</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7020,7 +7025,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7030,7 +7035,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7057,10 +7067,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129699502</v>
+        <v>129711613</v>
       </c>
       <c r="B53" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7068,37 +7078,45 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>457280</v>
+        <v>457300</v>
       </c>
       <c r="R53" t="n">
-        <v>6678039</v>
+        <v>6678044</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7125,24 +7143,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Barkflagning</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7157,22 +7165,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129711613</v>
+        <v>129702610</v>
       </c>
       <c r="B54" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7180,45 +7188,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>457300</v>
+        <v>457417</v>
       </c>
       <c r="R54" t="n">
-        <v>6678044</v>
+        <v>6677423</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7245,14 +7245,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Barkflagning</t>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7267,22 +7272,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129700821</v>
+        <v>129699502</v>
       </c>
       <c r="B55" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7290,39 +7295,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>457486</v>
+        <v>457280</v>
       </c>
       <c r="R55" t="n">
-        <v>6677569</v>
+        <v>6678039</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7354,7 +7354,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7513,7 +7513,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129699824</v>
+        <v>129711612</v>
       </c>
       <c r="B57" t="n">
         <v>57736</v>
@@ -7542,24 +7542,27 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>457346</v>
+        <v>457358</v>
       </c>
       <c r="R57" t="n">
-        <v>6677881</v>
+        <v>6677489</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7586,24 +7589,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Möjligt början på bohål i år/fjolåret.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7618,22 +7611,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129711614</v>
+        <v>129701963</v>
       </c>
       <c r="B58" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7641,16 +7634,16 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -7659,19 +7652,24 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>457280</v>
+        <v>457294</v>
       </c>
       <c r="R58" t="n">
-        <v>6678029</v>
+        <v>6677481</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7698,14 +7696,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Färskt födosök av spillkråka i björk stubbe.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7720,22 +7728,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129701074</v>
+        <v>129699824</v>
       </c>
       <c r="B59" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7743,34 +7751,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>457397</v>
+        <v>457346</v>
       </c>
       <c r="R59" t="n">
-        <v>6677548</v>
+        <v>6677881</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7802,7 +7815,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7812,12 +7825,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7844,32 +7857,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129700360</v>
+        <v>129701074</v>
       </c>
       <c r="B60" t="n">
-        <v>91557</v>
+        <v>79081</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7879,10 +7892,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>457345</v>
+        <v>457397</v>
       </c>
       <c r="R60" t="n">
-        <v>6677677</v>
+        <v>6677548</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7914,7 +7927,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7924,7 +7937,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7951,50 +7969,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129701963</v>
+        <v>129700360</v>
       </c>
       <c r="B61" t="n">
-        <v>57736</v>
+        <v>91561</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>457294</v>
+        <v>457345</v>
       </c>
       <c r="R61" t="n">
-        <v>6677481</v>
+        <v>6677677</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8026,7 +8039,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8036,12 +8049,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:43</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8068,10 +8076,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129711612</v>
+        <v>129711614</v>
       </c>
       <c r="B62" t="n">
-        <v>57736</v>
+        <v>57733</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8079,16 +8087,16 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -8097,24 +8105,16 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>457358</v>
+        <v>457280</v>
       </c>
       <c r="R62" t="n">
-        <v>6677489</v>
+        <v>6678029</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -8151,7 +8151,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Möjligt början på bohål i år/fjolåret.</t>
+          <t>Färskt födosök av spillkråka i björk stubbe.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8412,45 +8412,56 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129711616</v>
+        <v>129711615</v>
       </c>
       <c r="B65" t="n">
-        <v>78838</v>
+        <v>91581</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>4660</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>457305</v>
+        <v>457423</v>
       </c>
       <c r="R65" t="n">
-        <v>6677449</v>
+        <v>6677421</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -8485,12 +8496,18 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>10-15 fk på stående mindre asp.</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -8509,10 +8526,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129703525</v>
+        <v>129711616</v>
       </c>
       <c r="B66" t="n">
-        <v>57736</v>
+        <v>78838</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8520,42 +8537,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>457433</v>
+        <v>457305</v>
       </c>
       <c r="R66" t="n">
-        <v>6677123</v>
+        <v>6677449</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8582,24 +8594,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>13:41</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>13:41</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Rikligt på tall.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8614,22 +8611,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129702120</v>
+        <v>129703378</v>
       </c>
       <c r="B67" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8637,39 +8634,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>457299</v>
+        <v>457407</v>
       </c>
       <c r="R67" t="n">
-        <v>6677464</v>
+        <v>6677144</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8701,7 +8693,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8711,7 +8703,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8738,10 +8735,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129703378</v>
+        <v>129703525</v>
       </c>
       <c r="B68" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8749,34 +8746,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>457407</v>
+        <v>457433</v>
       </c>
       <c r="R68" t="n">
-        <v>6677144</v>
+        <v>6677123</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8808,7 +8810,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8818,12 +8820,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Rikligt på tall.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8850,59 +8852,53 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129711615</v>
+        <v>129702120</v>
       </c>
       <c r="B69" t="n">
-        <v>91577</v>
+        <v>57736</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4660</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>457423</v>
+        <v>457299</v>
       </c>
       <c r="R69" t="n">
-        <v>6677421</v>
+        <v>6677464</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8929,14 +8925,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>10-15 fk på stående mindre asp.</t>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8945,19 +8946,18 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -9076,10 +9076,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129704395</v>
+        <v>129702970</v>
       </c>
       <c r="B71" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9087,39 +9087,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>457267</v>
+        <v>457390</v>
       </c>
       <c r="R71" t="n">
-        <v>6677342</v>
+        <v>6677240</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9151,7 +9146,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9161,12 +9156,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9193,10 +9188,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129702970</v>
+        <v>129704395</v>
       </c>
       <c r="B72" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9204,34 +9199,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>457390</v>
+        <v>457267</v>
       </c>
       <c r="R72" t="n">
-        <v>6677240</v>
+        <v>6677342</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9263,7 +9263,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9273,12 +9273,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9305,10 +9305,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129704249</v>
+        <v>129711617</v>
       </c>
       <c r="B73" t="n">
-        <v>97020</v>
+        <v>79081</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9316,37 +9316,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>457311</v>
+        <v>457423</v>
       </c>
       <c r="R73" t="n">
-        <v>6677235</v>
+        <v>6677206</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9373,19 +9373,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>14:11</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>14:11</t>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>På tallstam</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9400,22 +9395,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129711617</v>
+        <v>129704249</v>
       </c>
       <c r="B74" t="n">
-        <v>79081</v>
+        <v>97024</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9423,37 +9418,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>457423</v>
+        <v>457311</v>
       </c>
       <c r="R74" t="n">
-        <v>6677206</v>
+        <v>6677235</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9480,14 +9475,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>På tallstam</t>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9502,12 +9502,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -9517,7 +9517,7 @@
         <v>129702657</v>
       </c>
       <c r="B75" t="n">
-        <v>91557</v>
+        <v>91561</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129701018</v>
+        <v>129702050</v>
       </c>
       <c r="B83" t="n">
         <v>57736</v>
@@ -10446,7 +10446,7 @@
       <c r="I83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -10455,10 +10455,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>457426</v>
+        <v>457274</v>
       </c>
       <c r="R83" t="n">
-        <v>6677541</v>
+        <v>6677446</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10490,7 +10490,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
@@ -10532,7 +10532,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129702050</v>
+        <v>129701018</v>
       </c>
       <c r="B84" t="n">
         <v>57736</v>
@@ -10563,7 +10563,7 @@
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -10572,10 +10572,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>457274</v>
+        <v>457426</v>
       </c>
       <c r="R84" t="n">
-        <v>6677446</v>
+        <v>6677541</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10607,7 +10607,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10617,7 +10617,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
@@ -10878,10 +10878,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129703077</v>
+        <v>129702495</v>
       </c>
       <c r="B87" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10889,34 +10889,39 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>457393</v>
+        <v>457432</v>
       </c>
       <c r="R87" t="n">
-        <v>6677229</v>
+        <v>6677419</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10948,7 +10953,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10958,12 +10963,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10990,10 +10995,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129704366</v>
+        <v>129700968</v>
       </c>
       <c r="B88" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11001,34 +11006,39 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>457288</v>
+        <v>457428</v>
       </c>
       <c r="R88" t="n">
-        <v>6677333</v>
+        <v>6677512</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11060,7 +11070,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11070,12 +11080,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11102,7 +11112,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129711618</v>
+        <v>129703077</v>
       </c>
       <c r="B89" t="n">
         <v>79081</v>
@@ -11133,17 +11143,17 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>457392</v>
+        <v>457393</v>
       </c>
       <c r="R89" t="n">
-        <v>6677547</v>
+        <v>6677229</v>
       </c>
       <c r="S89" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11170,9 +11180,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11187,22 +11212,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129702495</v>
+        <v>129704366</v>
       </c>
       <c r="B90" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11210,39 +11235,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>457432</v>
+        <v>457288</v>
       </c>
       <c r="R90" t="n">
-        <v>6677419</v>
+        <v>6677333</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11274,7 +11294,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11284,12 +11304,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11316,10 +11336,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129700968</v>
+        <v>129711618</v>
       </c>
       <c r="B91" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11327,42 +11347,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>457428</v>
+        <v>457392</v>
       </c>
       <c r="R91" t="n">
-        <v>6677512</v>
+        <v>6677547</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11389,24 +11404,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>11:56</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>11:56</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11421,19 +11421,19 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129701101</v>
+        <v>129699765</v>
       </c>
       <c r="B92" t="n">
         <v>57736</v>
@@ -11464,7 +11464,7 @@
       <c r="I92" t="inlineStr"/>
       <c r="M92" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -11473,10 +11473,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>457396</v>
+        <v>457317</v>
       </c>
       <c r="R92" t="n">
-        <v>6677546</v>
+        <v>6677895</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11508,7 +11508,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11518,12 +11518,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Inte super färska.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11550,10 +11550,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129699765</v>
+        <v>129703817</v>
       </c>
       <c r="B93" t="n">
-        <v>57736</v>
+        <v>78838</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11561,39 +11561,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>457317</v>
+        <v>457337</v>
       </c>
       <c r="R93" t="n">
-        <v>6677895</v>
+        <v>6677076</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11625,7 +11620,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11635,12 +11630,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11667,10 +11657,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129703817</v>
+        <v>129701101</v>
       </c>
       <c r="B94" t="n">
-        <v>78838</v>
+        <v>57736</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11678,34 +11668,39 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>457337</v>
+        <v>457396</v>
       </c>
       <c r="R94" t="n">
-        <v>6677076</v>
+        <v>6677546</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11737,7 +11732,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11747,7 +11742,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Inte super färska.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11998,10 +11998,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129722077</v>
+        <v>129717970</v>
       </c>
       <c r="B97" t="n">
-        <v>91613</v>
+        <v>57736</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12009,33 +12009,42 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>457452</v>
+        <v>457534</v>
       </c>
       <c r="R97" t="n">
-        <v>6676554</v>
+        <v>6676132</v>
       </c>
       <c r="S97" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -12064,7 +12073,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12074,12 +12083,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Fler fruktkroppar.</t>
+          <t>Ringhack på tall, hyfsat färska.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12106,10 +12115,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129717970</v>
+        <v>129722077</v>
       </c>
       <c r="B98" t="n">
-        <v>57736</v>
+        <v>91617</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12117,42 +12126,33 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>457534</v>
+        <v>457452</v>
       </c>
       <c r="R98" t="n">
-        <v>6676132</v>
+        <v>6676554</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -12181,7 +12181,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12191,12 +12191,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Ringhack på tall, hyfsat färska.</t>
+          <t>Fler fruktkroppar.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12567,7 +12567,7 @@
         <v>129704065</v>
       </c>
       <c r="B102" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12683,10 +12683,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129722392</v>
+        <v>129721585</v>
       </c>
       <c r="B103" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12694,42 +12694,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
+          <t>Lagalamm, Lagalamm, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>457336</v>
+        <v>457426</v>
       </c>
       <c r="R103" t="n">
-        <v>6676787</v>
+        <v>6676070</v>
       </c>
       <c r="S103" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12758,7 +12753,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12768,12 +12763,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:36</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Rikligt.</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12800,10 +12790,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129721585</v>
+        <v>129722392</v>
       </c>
       <c r="B104" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12811,37 +12801,42 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Lagalamm, Lagalamm, Dlr</t>
+          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>457426</v>
+        <v>457336</v>
       </c>
       <c r="R104" t="n">
-        <v>6676070</v>
+        <v>6676787</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12870,7 +12865,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12880,7 +12875,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Rikligt.</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13363,7 +13363,7 @@
         <v>129699541</v>
       </c>
       <c r="B109" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13479,7 +13479,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129722523</v>
+        <v>129717610</v>
       </c>
       <c r="B110" t="n">
         <v>57736</v>
@@ -13510,7 +13510,7 @@
       <c r="I110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -13519,13 +13519,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>457223</v>
+        <v>457387</v>
       </c>
       <c r="R110" t="n">
-        <v>6676922</v>
+        <v>6677155</v>
       </c>
       <c r="S110" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -13554,7 +13554,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -13564,12 +13564,12 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Ringhack på tall, mycket färska.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13596,7 +13596,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129717610</v>
+        <v>129722523</v>
       </c>
       <c r="B111" t="n">
         <v>57736</v>
@@ -13627,7 +13627,7 @@
       <c r="I111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -13636,13 +13636,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>457387</v>
+        <v>457223</v>
       </c>
       <c r="R111" t="n">
-        <v>6677155</v>
+        <v>6676922</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13671,7 +13671,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -13681,12 +13681,12 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack på tall, mycket färska.</t>
         </is>
       </c>
       <c r="AD111" t="b">

--- a/artfynd/A 49804-2025 artfynd.xlsx
+++ b/artfynd/A 49804-2025 artfynd.xlsx
@@ -6950,10 +6950,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129700821</v>
+        <v>129702610</v>
       </c>
       <c r="B52" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6961,39 +6961,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>457486</v>
+        <v>457417</v>
       </c>
       <c r="R52" t="n">
-        <v>6677569</v>
+        <v>6677423</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7025,7 +7020,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7035,12 +7030,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:49</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7067,10 +7057,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129711613</v>
+        <v>129699502</v>
       </c>
       <c r="B53" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7078,45 +7068,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>457300</v>
+        <v>457280</v>
       </c>
       <c r="R53" t="n">
-        <v>6678044</v>
+        <v>6678039</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7143,14 +7125,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Barkflagning</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7165,22 +7157,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129702610</v>
+        <v>129711613</v>
       </c>
       <c r="B54" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7188,37 +7180,45 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>457417</v>
+        <v>457300</v>
       </c>
       <c r="R54" t="n">
-        <v>6677423</v>
+        <v>6678044</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7245,19 +7245,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>13:10</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>13:10</t>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Barkflagning</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7272,22 +7267,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129699502</v>
+        <v>129700821</v>
       </c>
       <c r="B55" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7295,34 +7290,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>457280</v>
+        <v>457486</v>
       </c>
       <c r="R55" t="n">
-        <v>6678039</v>
+        <v>6677569</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7354,7 +7354,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7513,7 +7513,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129711612</v>
+        <v>129699824</v>
       </c>
       <c r="B57" t="n">
         <v>57736</v>
@@ -7542,27 +7542,24 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>457358</v>
+        <v>457346</v>
       </c>
       <c r="R57" t="n">
-        <v>6677489</v>
+        <v>6677881</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7589,14 +7586,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Möjligt början på bohål i år/fjolåret.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7611,22 +7618,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129701963</v>
+        <v>129701074</v>
       </c>
       <c r="B58" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7634,39 +7641,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>457294</v>
+        <v>457397</v>
       </c>
       <c r="R58" t="n">
-        <v>6677481</v>
+        <v>6677548</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7698,7 +7700,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7708,12 +7710,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7740,50 +7742,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129699824</v>
+        <v>129700360</v>
       </c>
       <c r="B59" t="n">
-        <v>57736</v>
+        <v>91563</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>457346</v>
+        <v>457345</v>
       </c>
       <c r="R59" t="n">
-        <v>6677881</v>
+        <v>6677677</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7815,7 +7812,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7825,12 +7822,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:04</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7857,10 +7849,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129701074</v>
+        <v>129711614</v>
       </c>
       <c r="B60" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7868,37 +7860,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>457397</v>
+        <v>457280</v>
       </c>
       <c r="R60" t="n">
-        <v>6677548</v>
+        <v>6678029</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7925,24 +7917,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Färskt födosök av spillkråka i björk stubbe.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7957,57 +7939,62 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129700360</v>
+        <v>129701963</v>
       </c>
       <c r="B61" t="n">
-        <v>91561</v>
+        <v>57736</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>457345</v>
+        <v>457294</v>
       </c>
       <c r="R61" t="n">
-        <v>6677677</v>
+        <v>6677481</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8039,7 +8026,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8049,7 +8036,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8076,10 +8068,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129711614</v>
+        <v>129711612</v>
       </c>
       <c r="B62" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8087,16 +8079,16 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -8105,16 +8097,24 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>457280</v>
+        <v>457358</v>
       </c>
       <c r="R62" t="n">
-        <v>6678029</v>
+        <v>6677489</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -8151,7 +8151,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Färskt födosök av spillkråka i björk stubbe.</t>
+          <t>Möjligt början på bohål i år/fjolåret.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8412,59 +8412,48 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129711615</v>
+        <v>129703378</v>
       </c>
       <c r="B65" t="n">
-        <v>91581</v>
+        <v>79081</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4660</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>457423</v>
+        <v>457407</v>
       </c>
       <c r="R65" t="n">
-        <v>6677421</v>
+        <v>6677144</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8491,14 +8480,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>10-15 fk på stående mindre asp.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8507,19 +8506,18 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -8623,10 +8621,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129703378</v>
+        <v>129703525</v>
       </c>
       <c r="B67" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8634,34 +8632,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>457407</v>
+        <v>457433</v>
       </c>
       <c r="R67" t="n">
-        <v>6677144</v>
+        <v>6677123</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8693,7 +8696,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8703,12 +8706,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Rikligt på tall.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8735,7 +8738,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129703525</v>
+        <v>129702120</v>
       </c>
       <c r="B68" t="n">
         <v>57736</v>
@@ -8766,19 +8769,19 @@
       <c r="I68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>457433</v>
+        <v>457299</v>
       </c>
       <c r="R68" t="n">
-        <v>6677123</v>
+        <v>6677464</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8810,7 +8813,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8820,12 +8823,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:41</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Rikligt på tall.</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8852,10 +8850,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129702120</v>
+        <v>129704842</v>
       </c>
       <c r="B69" t="n">
-        <v>57736</v>
+        <v>78839</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8863,39 +8861,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>457299</v>
+        <v>457230</v>
       </c>
       <c r="R69" t="n">
-        <v>6677464</v>
+        <v>6677594</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8927,7 +8920,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8937,7 +8930,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Lite osäker men rätt säker.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8964,48 +8962,59 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129704842</v>
+        <v>129711615</v>
       </c>
       <c r="B70" t="n">
-        <v>78839</v>
+        <v>91583</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>4660</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>457230</v>
+        <v>457423</v>
       </c>
       <c r="R70" t="n">
-        <v>6677594</v>
+        <v>6677421</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9032,24 +9041,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Lite osäker men rätt säker.</t>
+          <t>10-15 fk på stående mindre asp.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9058,18 +9057,19 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -9305,10 +9305,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129711617</v>
+        <v>129704249</v>
       </c>
       <c r="B73" t="n">
-        <v>79081</v>
+        <v>97026</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9316,37 +9316,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>457423</v>
+        <v>457311</v>
       </c>
       <c r="R73" t="n">
-        <v>6677206</v>
+        <v>6677235</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9373,14 +9373,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>På tallstam</t>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9395,22 +9400,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129704249</v>
+        <v>129711617</v>
       </c>
       <c r="B74" t="n">
-        <v>97024</v>
+        <v>79081</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9418,37 +9423,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>457311</v>
+        <v>457423</v>
       </c>
       <c r="R74" t="n">
-        <v>6677235</v>
+        <v>6677206</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9475,19 +9480,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>14:11</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>14:11</t>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>På tallstam</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9502,12 +9502,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -9517,7 +9517,7 @@
         <v>129702657</v>
       </c>
       <c r="B75" t="n">
-        <v>91561</v>
+        <v>91563</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129702050</v>
+        <v>129701018</v>
       </c>
       <c r="B83" t="n">
         <v>57736</v>
@@ -10446,7 +10446,7 @@
       <c r="I83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -10455,10 +10455,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>457274</v>
+        <v>457426</v>
       </c>
       <c r="R83" t="n">
-        <v>6677446</v>
+        <v>6677541</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10490,7 +10490,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
@@ -10532,7 +10532,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129701018</v>
+        <v>129702050</v>
       </c>
       <c r="B84" t="n">
         <v>57736</v>
@@ -10563,7 +10563,7 @@
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -10572,10 +10572,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>457426</v>
+        <v>457274</v>
       </c>
       <c r="R84" t="n">
-        <v>6677541</v>
+        <v>6677446</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10607,7 +10607,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10617,7 +10617,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
@@ -10766,7 +10766,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129700950</v>
+        <v>129711618</v>
       </c>
       <c r="B86" t="n">
         <v>79081</v>
@@ -10797,17 +10797,17 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>457431</v>
+        <v>457392</v>
       </c>
       <c r="R86" t="n">
-        <v>6677513</v>
+        <v>6677547</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10834,24 +10834,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>På gran.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10866,22 +10851,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129702495</v>
+        <v>129700950</v>
       </c>
       <c r="B87" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10889,39 +10874,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>457432</v>
+        <v>457431</v>
       </c>
       <c r="R87" t="n">
-        <v>6677419</v>
+        <v>6677513</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10953,7 +10933,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10963,12 +10943,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10995,10 +10975,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129700968</v>
+        <v>129703077</v>
       </c>
       <c r="B88" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11006,39 +10986,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>457428</v>
+        <v>457393</v>
       </c>
       <c r="R88" t="n">
-        <v>6677512</v>
+        <v>6677229</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11070,7 +11045,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11080,12 +11055,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11112,7 +11087,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129703077</v>
+        <v>129704366</v>
       </c>
       <c r="B89" t="n">
         <v>79081</v>
@@ -11147,10 +11122,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>457393</v>
+        <v>457288</v>
       </c>
       <c r="R89" t="n">
-        <v>6677229</v>
+        <v>6677333</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11182,7 +11157,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11192,12 +11167,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11224,10 +11199,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129704366</v>
+        <v>129702495</v>
       </c>
       <c r="B90" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11235,34 +11210,39 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>457288</v>
+        <v>457432</v>
       </c>
       <c r="R90" t="n">
-        <v>6677333</v>
+        <v>6677419</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11294,7 +11274,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11304,12 +11284,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11336,10 +11316,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129711618</v>
+        <v>129700968</v>
       </c>
       <c r="B91" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11347,37 +11327,42 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>457392</v>
+        <v>457428</v>
       </c>
       <c r="R91" t="n">
-        <v>6677547</v>
+        <v>6677512</v>
       </c>
       <c r="S91" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11404,9 +11389,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11421,22 +11421,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129699765</v>
+        <v>129703817</v>
       </c>
       <c r="B92" t="n">
-        <v>57736</v>
+        <v>78838</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11444,39 +11444,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>457317</v>
+        <v>457337</v>
       </c>
       <c r="R92" t="n">
-        <v>6677895</v>
+        <v>6677076</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11508,7 +11503,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11518,12 +11513,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11550,10 +11540,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129703817</v>
+        <v>129699765</v>
       </c>
       <c r="B93" t="n">
-        <v>78838</v>
+        <v>57736</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11561,34 +11551,39 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>457337</v>
+        <v>457317</v>
       </c>
       <c r="R93" t="n">
-        <v>6677076</v>
+        <v>6677895</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11620,7 +11615,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11630,7 +11625,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11998,10 +11998,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129717970</v>
+        <v>129722077</v>
       </c>
       <c r="B97" t="n">
-        <v>57736</v>
+        <v>91619</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12009,42 +12009,33 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>457534</v>
+        <v>457452</v>
       </c>
       <c r="R97" t="n">
-        <v>6676132</v>
+        <v>6676554</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -12073,7 +12064,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12083,12 +12074,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Ringhack på tall, hyfsat färska.</t>
+          <t>Fler fruktkroppar.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12115,10 +12106,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129722077</v>
+        <v>129717970</v>
       </c>
       <c r="B98" t="n">
-        <v>91617</v>
+        <v>57736</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12126,33 +12117,42 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>457452</v>
+        <v>457534</v>
       </c>
       <c r="R98" t="n">
-        <v>6676554</v>
+        <v>6676132</v>
       </c>
       <c r="S98" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -12181,7 +12181,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12191,12 +12191,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Fler fruktkroppar.</t>
+          <t>Ringhack på tall, hyfsat färska.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12567,7 +12567,7 @@
         <v>129704065</v>
       </c>
       <c r="B102" t="n">
-        <v>92879</v>
+        <v>92881</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13248,48 +13248,59 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129722095</v>
+        <v>129699541</v>
       </c>
       <c r="B108" t="n">
-        <v>79081</v>
+        <v>92881</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
+          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>457440</v>
+        <v>457267</v>
       </c>
       <c r="R108" t="n">
-        <v>6676555</v>
+        <v>6678042</v>
       </c>
       <c r="S108" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -13313,27 +13324,22 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>15:19</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Ganska hänlavs rikt.</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13342,6 +13348,7 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -13360,59 +13367,48 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129699541</v>
+        <v>129722095</v>
       </c>
       <c r="B109" t="n">
-        <v>92879</v>
+        <v>79081</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
+          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>457267</v>
+        <v>457440</v>
       </c>
       <c r="R109" t="n">
-        <v>6678042</v>
+        <v>6676555</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -13436,22 +13432,27 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Ganska hänlavs rikt.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13460,7 +13461,6 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
@@ -13479,7 +13479,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129717610</v>
+        <v>129722523</v>
       </c>
       <c r="B110" t="n">
         <v>57736</v>
@@ -13510,7 +13510,7 @@
       <c r="I110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -13519,13 +13519,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>457387</v>
+        <v>457223</v>
       </c>
       <c r="R110" t="n">
-        <v>6677155</v>
+        <v>6676922</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -13554,7 +13554,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -13564,12 +13564,12 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack på tall, mycket färska.</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13596,7 +13596,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129722523</v>
+        <v>129717610</v>
       </c>
       <c r="B111" t="n">
         <v>57736</v>
@@ -13627,7 +13627,7 @@
       <c r="I111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -13636,13 +13636,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>457223</v>
+        <v>457387</v>
       </c>
       <c r="R111" t="n">
-        <v>6676922</v>
+        <v>6677155</v>
       </c>
       <c r="S111" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13671,7 +13671,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -13681,12 +13681,12 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Ringhack på tall, mycket färska.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD111" t="b">

--- a/artfynd/A 49804-2025 artfynd.xlsx
+++ b/artfynd/A 49804-2025 artfynd.xlsx
@@ -7513,10 +7513,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129699824</v>
+        <v>129711614</v>
       </c>
       <c r="B57" t="n">
-        <v>57736</v>
+        <v>57733</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7524,16 +7524,16 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -7542,24 +7542,19 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>457346</v>
+        <v>457280</v>
       </c>
       <c r="R57" t="n">
-        <v>6677881</v>
+        <v>6678029</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7586,24 +7581,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Färskt födosök av spillkråka i björk stubbe.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7618,22 +7603,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129701074</v>
+        <v>129701963</v>
       </c>
       <c r="B58" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7641,34 +7626,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>457397</v>
+        <v>457294</v>
       </c>
       <c r="R58" t="n">
-        <v>6677548</v>
+        <v>6677481</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7700,7 +7690,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7710,12 +7700,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7742,48 +7732,56 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129700360</v>
+        <v>129711612</v>
       </c>
       <c r="B59" t="n">
-        <v>91563</v>
+        <v>57736</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>457345</v>
+        <v>457358</v>
       </c>
       <c r="R59" t="n">
-        <v>6677677</v>
+        <v>6677489</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7810,19 +7808,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>11:26</t>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Möjligt början på bohål i år/fjolåret.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7837,22 +7830,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129711614</v>
+        <v>129699824</v>
       </c>
       <c r="B60" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7860,16 +7853,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -7878,19 +7871,24 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>457280</v>
+        <v>457346</v>
       </c>
       <c r="R60" t="n">
-        <v>6678029</v>
+        <v>6677881</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7917,14 +7915,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Färskt födosök av spillkråka i björk stubbe.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7939,22 +7947,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129701963</v>
+        <v>129701074</v>
       </c>
       <c r="B61" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7962,39 +7970,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>457294</v>
+        <v>457397</v>
       </c>
       <c r="R61" t="n">
-        <v>6677481</v>
+        <v>6677548</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8026,7 +8029,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8036,12 +8039,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8068,56 +8071,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129711612</v>
+        <v>129700360</v>
       </c>
       <c r="B62" t="n">
-        <v>57736</v>
+        <v>91563</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>457358</v>
+        <v>457345</v>
       </c>
       <c r="R62" t="n">
-        <v>6677489</v>
+        <v>6677677</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8144,14 +8139,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Möjligt början på bohål i år/fjolåret.</t>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8166,12 +8166,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -9514,45 +9514,50 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129702657</v>
+        <v>129704181</v>
       </c>
       <c r="B75" t="n">
-        <v>91563</v>
+        <v>57736</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>457420</v>
+        <v>457325</v>
       </c>
       <c r="R75" t="n">
-        <v>6677417</v>
+        <v>6677219</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9584,7 +9589,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9594,7 +9599,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9621,50 +9631,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129704181</v>
+        <v>129702657</v>
       </c>
       <c r="B76" t="n">
-        <v>57736</v>
+        <v>91563</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>457325</v>
+        <v>457420</v>
       </c>
       <c r="R76" t="n">
-        <v>6677219</v>
+        <v>6677417</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9696,7 +9701,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9706,12 +9711,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10196,10 +10196,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129703164</v>
+        <v>129701018</v>
       </c>
       <c r="B81" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10207,34 +10207,39 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>457394</v>
+        <v>457426</v>
       </c>
       <c r="R81" t="n">
-        <v>6677203</v>
+        <v>6677541</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10266,7 +10271,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10276,7 +10281,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10303,10 +10313,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129700616</v>
+        <v>129702050</v>
       </c>
       <c r="B82" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10314,34 +10324,39 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>457384</v>
+        <v>457274</v>
       </c>
       <c r="R82" t="n">
-        <v>6677586</v>
+        <v>6677446</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10373,7 +10388,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10383,12 +10398,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10415,10 +10430,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129701018</v>
+        <v>129703164</v>
       </c>
       <c r="B83" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10426,39 +10441,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>457426</v>
+        <v>457394</v>
       </c>
       <c r="R83" t="n">
-        <v>6677541</v>
+        <v>6677203</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10490,7 +10500,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10500,12 +10510,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:59</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10532,10 +10537,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129702050</v>
+        <v>129700616</v>
       </c>
       <c r="B84" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10543,39 +10548,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>457274</v>
+        <v>457384</v>
       </c>
       <c r="R84" t="n">
-        <v>6677446</v>
+        <v>6677586</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10607,7 +10607,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11433,10 +11433,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129703817</v>
+        <v>129699765</v>
       </c>
       <c r="B92" t="n">
-        <v>78838</v>
+        <v>57736</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11444,34 +11444,39 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>457337</v>
+        <v>457317</v>
       </c>
       <c r="R92" t="n">
-        <v>6677076</v>
+        <v>6677895</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11503,7 +11508,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11513,7 +11518,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11540,10 +11550,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129699765</v>
+        <v>129703817</v>
       </c>
       <c r="B93" t="n">
-        <v>57736</v>
+        <v>78838</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11551,39 +11561,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>457317</v>
+        <v>457337</v>
       </c>
       <c r="R93" t="n">
-        <v>6677895</v>
+        <v>6677076</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11615,7 +11620,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11625,12 +11630,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11774,10 +11774,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129703127</v>
+        <v>129700098</v>
       </c>
       <c r="B95" t="n">
-        <v>78838</v>
+        <v>57736</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11785,34 +11785,39 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>457391</v>
+        <v>457355</v>
       </c>
       <c r="R95" t="n">
-        <v>6677213</v>
+        <v>6677771</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11844,7 +11849,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11854,7 +11859,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Inte jätte färska med syns sav fortfarande.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11881,10 +11891,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129700098</v>
+        <v>129703127</v>
       </c>
       <c r="B96" t="n">
-        <v>57736</v>
+        <v>78838</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11892,39 +11902,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>457355</v>
+        <v>457391</v>
       </c>
       <c r="R96" t="n">
-        <v>6677771</v>
+        <v>6677213</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11956,7 +11961,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11966,12 +11971,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Inte jätte färska med syns sav fortfarande.</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD96" t="b">

--- a/artfynd/A 49804-2025 artfynd.xlsx
+++ b/artfynd/A 49804-2025 artfynd.xlsx
@@ -6950,10 +6950,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129702610</v>
+        <v>129711613</v>
       </c>
       <c r="B52" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6961,37 +6961,45 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>457417</v>
+        <v>457300</v>
       </c>
       <c r="R52" t="n">
-        <v>6677423</v>
+        <v>6678044</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7018,19 +7026,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>13:10</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>13:10</t>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Barkflagning</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7045,22 +7048,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129699502</v>
+        <v>129700821</v>
       </c>
       <c r="B53" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7068,34 +7071,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>457280</v>
+        <v>457486</v>
       </c>
       <c r="R53" t="n">
-        <v>6678039</v>
+        <v>6677569</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7127,7 +7135,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7137,12 +7145,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7169,10 +7177,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129711613</v>
+        <v>129699502</v>
       </c>
       <c r="B54" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7180,45 +7188,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>457300</v>
+        <v>457280</v>
       </c>
       <c r="R54" t="n">
-        <v>6678044</v>
+        <v>6678039</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7245,14 +7245,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Barkflagning</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7267,22 +7277,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129700821</v>
+        <v>129702610</v>
       </c>
       <c r="B55" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7290,39 +7300,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>457486</v>
+        <v>457417</v>
       </c>
       <c r="R55" t="n">
-        <v>6677569</v>
+        <v>6677423</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7354,7 +7359,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7364,12 +7369,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:49</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -9076,10 +9076,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129702970</v>
+        <v>129704395</v>
       </c>
       <c r="B71" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9087,34 +9087,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>457390</v>
+        <v>457267</v>
       </c>
       <c r="R71" t="n">
-        <v>6677240</v>
+        <v>6677342</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9146,7 +9151,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9156,12 +9161,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9188,10 +9193,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129704395</v>
+        <v>129702970</v>
       </c>
       <c r="B72" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9199,39 +9204,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>457267</v>
+        <v>457390</v>
       </c>
       <c r="R72" t="n">
-        <v>6677342</v>
+        <v>6677240</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9263,7 +9263,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9273,12 +9273,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9514,50 +9514,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129704181</v>
+        <v>129702657</v>
       </c>
       <c r="B75" t="n">
-        <v>57736</v>
+        <v>91563</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>457325</v>
+        <v>457420</v>
       </c>
       <c r="R75" t="n">
-        <v>6677219</v>
+        <v>6677417</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9589,7 +9584,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9599,12 +9594,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9631,45 +9621,50 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129702657</v>
+        <v>129704181</v>
       </c>
       <c r="B76" t="n">
-        <v>91563</v>
+        <v>57736</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>457420</v>
+        <v>457325</v>
       </c>
       <c r="R76" t="n">
-        <v>6677417</v>
+        <v>6677219</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9701,7 +9696,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9711,7 +9706,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10196,10 +10196,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129701018</v>
+        <v>129703164</v>
       </c>
       <c r="B81" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10207,39 +10207,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>457426</v>
+        <v>457394</v>
       </c>
       <c r="R81" t="n">
-        <v>6677541</v>
+        <v>6677203</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10271,7 +10266,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10281,12 +10276,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:59</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10313,10 +10303,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129702050</v>
+        <v>129700616</v>
       </c>
       <c r="B82" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10324,39 +10314,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>457274</v>
+        <v>457384</v>
       </c>
       <c r="R82" t="n">
-        <v>6677446</v>
+        <v>6677586</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10388,7 +10373,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10398,12 +10383,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10430,10 +10415,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129703164</v>
+        <v>129701018</v>
       </c>
       <c r="B83" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10441,34 +10426,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>457394</v>
+        <v>457426</v>
       </c>
       <c r="R83" t="n">
-        <v>6677203</v>
+        <v>6677541</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10500,7 +10490,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10510,7 +10500,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10537,10 +10532,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129700616</v>
+        <v>129702050</v>
       </c>
       <c r="B84" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10548,34 +10543,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>457384</v>
+        <v>457274</v>
       </c>
       <c r="R84" t="n">
-        <v>6677586</v>
+        <v>6677446</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10607,7 +10607,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11774,10 +11774,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129700098</v>
+        <v>129703127</v>
       </c>
       <c r="B95" t="n">
-        <v>57736</v>
+        <v>78838</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11785,39 +11785,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>457355</v>
+        <v>457391</v>
       </c>
       <c r="R95" t="n">
-        <v>6677771</v>
+        <v>6677213</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11849,7 +11844,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11859,12 +11854,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Inte jätte färska med syns sav fortfarande.</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11891,10 +11881,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129703127</v>
+        <v>129700098</v>
       </c>
       <c r="B96" t="n">
-        <v>78838</v>
+        <v>57736</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11902,34 +11892,39 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>457391</v>
+        <v>457355</v>
       </c>
       <c r="R96" t="n">
-        <v>6677213</v>
+        <v>6677771</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11961,7 +11956,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11971,7 +11966,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Inte jätte färska med syns sav fortfarande.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11998,10 +11998,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129722077</v>
+        <v>129717970</v>
       </c>
       <c r="B97" t="n">
-        <v>91619</v>
+        <v>57736</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12009,33 +12009,42 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>457452</v>
+        <v>457534</v>
       </c>
       <c r="R97" t="n">
-        <v>6676554</v>
+        <v>6676132</v>
       </c>
       <c r="S97" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -12064,7 +12073,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12074,12 +12083,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Fler fruktkroppar.</t>
+          <t>Ringhack på tall, hyfsat färska.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12106,10 +12115,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129717970</v>
+        <v>129722077</v>
       </c>
       <c r="B98" t="n">
-        <v>57736</v>
+        <v>91619</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12117,42 +12126,33 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>457534</v>
+        <v>457452</v>
       </c>
       <c r="R98" t="n">
-        <v>6676132</v>
+        <v>6676554</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -12181,7 +12181,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12191,12 +12191,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Ringhack på tall, hyfsat färska.</t>
+          <t>Fler fruktkroppar.</t>
         </is>
       </c>
       <c r="AD98" t="b">

--- a/artfynd/A 49804-2025 artfynd.xlsx
+++ b/artfynd/A 49804-2025 artfynd.xlsx
@@ -6950,10 +6950,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129711613</v>
+        <v>129699502</v>
       </c>
       <c r="B52" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6961,45 +6961,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>457300</v>
+        <v>457280</v>
       </c>
       <c r="R52" t="n">
-        <v>6678044</v>
+        <v>6678039</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7026,14 +7018,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Barkflagning</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7048,22 +7050,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129700821</v>
+        <v>129702610</v>
       </c>
       <c r="B53" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7071,39 +7073,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>457486</v>
+        <v>457417</v>
       </c>
       <c r="R53" t="n">
-        <v>6677569</v>
+        <v>6677423</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7135,7 +7132,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7145,12 +7142,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:49</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7177,10 +7169,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129699502</v>
+        <v>129711613</v>
       </c>
       <c r="B54" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7188,37 +7180,45 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>457280</v>
+        <v>457300</v>
       </c>
       <c r="R54" t="n">
-        <v>6678039</v>
+        <v>6678044</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7245,24 +7245,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Barkflagning</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7277,22 +7267,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129702610</v>
+        <v>129700821</v>
       </c>
       <c r="B55" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7300,34 +7290,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>457417</v>
+        <v>457486</v>
       </c>
       <c r="R55" t="n">
-        <v>6677423</v>
+        <v>6677569</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7359,7 +7354,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7369,7 +7364,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7513,10 +7513,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129711614</v>
+        <v>129699824</v>
       </c>
       <c r="B57" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7524,16 +7524,16 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -7542,19 +7542,24 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>457280</v>
+        <v>457346</v>
       </c>
       <c r="R57" t="n">
-        <v>6678029</v>
+        <v>6677881</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7581,14 +7586,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Färskt födosök av spillkråka i björk stubbe.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7603,22 +7618,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129701963</v>
+        <v>129701074</v>
       </c>
       <c r="B58" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7626,39 +7641,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>457294</v>
+        <v>457397</v>
       </c>
       <c r="R58" t="n">
-        <v>6677481</v>
+        <v>6677548</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7690,7 +7700,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7700,12 +7710,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7732,56 +7742,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129711612</v>
+        <v>129700360</v>
       </c>
       <c r="B59" t="n">
-        <v>57736</v>
+        <v>91563</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>457358</v>
+        <v>457345</v>
       </c>
       <c r="R59" t="n">
-        <v>6677489</v>
+        <v>6677677</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7808,14 +7810,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Möjligt början på bohål i år/fjolåret.</t>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7830,22 +7837,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129699824</v>
+        <v>129711614</v>
       </c>
       <c r="B60" t="n">
-        <v>57736</v>
+        <v>57733</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7853,16 +7860,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -7871,24 +7878,19 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>457346</v>
+        <v>457280</v>
       </c>
       <c r="R60" t="n">
-        <v>6677881</v>
+        <v>6678029</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7915,24 +7917,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Färskt födosök av spillkråka i björk stubbe.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7947,22 +7939,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129701074</v>
+        <v>129701963</v>
       </c>
       <c r="B61" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7970,34 +7962,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>457397</v>
+        <v>457294</v>
       </c>
       <c r="R61" t="n">
-        <v>6677548</v>
+        <v>6677481</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8029,7 +8026,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8039,12 +8036,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8071,48 +8068,56 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129700360</v>
+        <v>129711612</v>
       </c>
       <c r="B62" t="n">
-        <v>91563</v>
+        <v>57736</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>457345</v>
+        <v>457358</v>
       </c>
       <c r="R62" t="n">
-        <v>6677677</v>
+        <v>6677489</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8139,19 +8144,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>11:26</t>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Möjligt början på bohål i år/fjolåret.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8166,12 +8166,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -8412,48 +8412,59 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129703378</v>
+        <v>129711615</v>
       </c>
       <c r="B65" t="n">
-        <v>79081</v>
+        <v>91583</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>4660</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>457407</v>
+        <v>457423</v>
       </c>
       <c r="R65" t="n">
-        <v>6677144</v>
+        <v>6677421</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8480,24 +8491,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>10-15 fk på stående mindre asp.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8506,28 +8507,29 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129711616</v>
+        <v>129703525</v>
       </c>
       <c r="B66" t="n">
-        <v>78838</v>
+        <v>57736</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8535,37 +8537,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>457305</v>
+        <v>457433</v>
       </c>
       <c r="R66" t="n">
-        <v>6677449</v>
+        <v>6677123</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8592,9 +8599,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Rikligt på tall.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8609,19 +8631,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129703525</v>
+        <v>129702120</v>
       </c>
       <c r="B67" t="n">
         <v>57736</v>
@@ -8652,19 +8674,19 @@
       <c r="I67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>457433</v>
+        <v>457299</v>
       </c>
       <c r="R67" t="n">
-        <v>6677123</v>
+        <v>6677464</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8696,7 +8718,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8706,12 +8728,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:41</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Rikligt på tall.</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8738,10 +8755,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129702120</v>
+        <v>129704842</v>
       </c>
       <c r="B68" t="n">
-        <v>57736</v>
+        <v>78839</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8749,39 +8766,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>457299</v>
+        <v>457230</v>
       </c>
       <c r="R68" t="n">
-        <v>6677464</v>
+        <v>6677594</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8813,7 +8825,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8823,7 +8835,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Lite osäker men rätt säker.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8850,10 +8867,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129704842</v>
+        <v>129703378</v>
       </c>
       <c r="B69" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8861,34 +8878,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>457230</v>
+        <v>457407</v>
       </c>
       <c r="R69" t="n">
-        <v>6677594</v>
+        <v>6677144</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8920,7 +8937,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8930,12 +8947,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Lite osäker men rätt säker.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8962,56 +8979,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129711615</v>
+        <v>129711616</v>
       </c>
       <c r="B70" t="n">
-        <v>91583</v>
+        <v>78838</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4660</v>
+        <v>6446</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>457423</v>
+        <v>457305</v>
       </c>
       <c r="R70" t="n">
-        <v>6677421</v>
+        <v>6677449</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -9046,18 +9052,12 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>10-15 fk på stående mindre asp.</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -9305,10 +9305,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129704249</v>
+        <v>129711617</v>
       </c>
       <c r="B73" t="n">
-        <v>97026</v>
+        <v>79081</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9316,37 +9316,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>457311</v>
+        <v>457423</v>
       </c>
       <c r="R73" t="n">
-        <v>6677235</v>
+        <v>6677206</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9373,19 +9373,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>14:11</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>14:11</t>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>På tallstam</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9400,22 +9395,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129711617</v>
+        <v>129704249</v>
       </c>
       <c r="B74" t="n">
-        <v>79081</v>
+        <v>97036</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9423,37 +9418,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>457423</v>
+        <v>457311</v>
       </c>
       <c r="R74" t="n">
-        <v>6677206</v>
+        <v>6677235</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9480,14 +9475,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>På tallstam</t>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9502,12 +9502,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -9738,10 +9738,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129699484</v>
+        <v>129700400</v>
       </c>
       <c r="B77" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9749,39 +9749,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>457246</v>
+        <v>457345</v>
       </c>
       <c r="R77" t="n">
-        <v>6678032</v>
+        <v>6677660</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9813,7 +9808,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9823,12 +9818,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9855,10 +9850,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129700400</v>
+        <v>129699484</v>
       </c>
       <c r="B78" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9866,34 +9861,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>457345</v>
+        <v>457246</v>
       </c>
       <c r="R78" t="n">
-        <v>6677660</v>
+        <v>6678032</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9925,7 +9925,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10415,7 +10415,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129701018</v>
+        <v>129702050</v>
       </c>
       <c r="B83" t="n">
         <v>57736</v>
@@ -10446,7 +10446,7 @@
       <c r="I83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -10455,10 +10455,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>457426</v>
+        <v>457274</v>
       </c>
       <c r="R83" t="n">
-        <v>6677541</v>
+        <v>6677446</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10490,7 +10490,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
@@ -10532,7 +10532,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129702050</v>
+        <v>129701018</v>
       </c>
       <c r="B84" t="n">
         <v>57736</v>
@@ -10563,7 +10563,7 @@
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -10572,10 +10572,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>457274</v>
+        <v>457426</v>
       </c>
       <c r="R84" t="n">
-        <v>6677446</v>
+        <v>6677541</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10607,7 +10607,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10617,7 +10617,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
@@ -10766,7 +10766,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129711618</v>
+        <v>129700950</v>
       </c>
       <c r="B86" t="n">
         <v>79081</v>
@@ -10797,17 +10797,17 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>457392</v>
+        <v>457431</v>
       </c>
       <c r="R86" t="n">
-        <v>6677547</v>
+        <v>6677513</v>
       </c>
       <c r="S86" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10834,9 +10834,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10851,19 +10866,19 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129700950</v>
+        <v>129703077</v>
       </c>
       <c r="B87" t="n">
         <v>79081</v>
@@ -10894,14 +10909,14 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>457431</v>
+        <v>457393</v>
       </c>
       <c r="R87" t="n">
-        <v>6677513</v>
+        <v>6677229</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10933,7 +10948,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10943,7 +10958,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
@@ -10975,7 +10990,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129703077</v>
+        <v>129704366</v>
       </c>
       <c r="B88" t="n">
         <v>79081</v>
@@ -11010,10 +11025,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>457393</v>
+        <v>457288</v>
       </c>
       <c r="R88" t="n">
-        <v>6677229</v>
+        <v>6677333</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11045,7 +11060,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11055,12 +11070,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11087,7 +11102,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129704366</v>
+        <v>129711618</v>
       </c>
       <c r="B89" t="n">
         <v>79081</v>
@@ -11118,17 +11133,17 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>457288</v>
+        <v>457392</v>
       </c>
       <c r="R89" t="n">
-        <v>6677333</v>
+        <v>6677547</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11155,24 +11170,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>14:16</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>14:16</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>På tall.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11187,12 +11187,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
@@ -11433,10 +11433,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129699765</v>
+        <v>129703817</v>
       </c>
       <c r="B92" t="n">
-        <v>57736</v>
+        <v>78838</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11444,39 +11444,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>457317</v>
+        <v>457337</v>
       </c>
       <c r="R92" t="n">
-        <v>6677895</v>
+        <v>6677076</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11508,7 +11503,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11518,12 +11513,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11550,10 +11540,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129703817</v>
+        <v>129699765</v>
       </c>
       <c r="B93" t="n">
-        <v>78838</v>
+        <v>57736</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11561,34 +11551,39 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>457337</v>
+        <v>457317</v>
       </c>
       <c r="R93" t="n">
-        <v>6677076</v>
+        <v>6677895</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11620,7 +11615,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11630,7 +11625,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12457,45 +12457,56 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129722043</v>
+        <v>129704065</v>
       </c>
       <c r="B101" t="n">
-        <v>79081</v>
+        <v>92881</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>457469</v>
+        <v>457293</v>
       </c>
       <c r="R101" t="n">
-        <v>6676536</v>
+        <v>6677157</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12522,22 +12533,22 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12546,6 +12557,7 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -12564,56 +12576,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129704065</v>
+        <v>129722043</v>
       </c>
       <c r="B102" t="n">
-        <v>92881</v>
+        <v>79081</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>457293</v>
+        <v>457469</v>
       </c>
       <c r="R102" t="n">
-        <v>6677157</v>
+        <v>6676536</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12640,22 +12641,22 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12664,7 +12665,6 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -12683,10 +12683,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129721585</v>
+        <v>129722392</v>
       </c>
       <c r="B103" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12694,37 +12694,42 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Lagalamm, Lagalamm, Dlr</t>
+          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>457426</v>
+        <v>457336</v>
       </c>
       <c r="R103" t="n">
-        <v>6676070</v>
+        <v>6676787</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12753,7 +12758,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12763,7 +12768,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Rikligt.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12790,10 +12800,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129722392</v>
+        <v>129721585</v>
       </c>
       <c r="B104" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12801,42 +12811,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
+          <t>Lagalamm, Lagalamm, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>457336</v>
+        <v>457426</v>
       </c>
       <c r="R104" t="n">
-        <v>6676787</v>
+        <v>6676070</v>
       </c>
       <c r="S104" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12865,7 +12870,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12875,12 +12880,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:36</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Rikligt.</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13479,7 +13479,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129722523</v>
+        <v>129717610</v>
       </c>
       <c r="B110" t="n">
         <v>57736</v>
@@ -13510,7 +13510,7 @@
       <c r="I110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -13519,13 +13519,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>457223</v>
+        <v>457387</v>
       </c>
       <c r="R110" t="n">
-        <v>6676922</v>
+        <v>6677155</v>
       </c>
       <c r="S110" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -13554,7 +13554,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -13564,12 +13564,12 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Ringhack på tall, mycket färska.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13596,7 +13596,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129717610</v>
+        <v>129722523</v>
       </c>
       <c r="B111" t="n">
         <v>57736</v>
@@ -13627,7 +13627,7 @@
       <c r="I111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -13636,13 +13636,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>457387</v>
+        <v>457223</v>
       </c>
       <c r="R111" t="n">
-        <v>6677155</v>
+        <v>6676922</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13671,7 +13671,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -13681,12 +13681,12 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack på tall, mycket färska.</t>
         </is>
       </c>
       <c r="AD111" t="b">

--- a/artfynd/A 49804-2025 artfynd.xlsx
+++ b/artfynd/A 49804-2025 artfynd.xlsx
@@ -7062,10 +7062,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129702610</v>
+        <v>129711613</v>
       </c>
       <c r="B53" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7073,37 +7073,45 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>457417</v>
+        <v>457300</v>
       </c>
       <c r="R53" t="n">
-        <v>6677423</v>
+        <v>6678044</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7130,19 +7138,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>13:10</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>13:10</t>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Barkflagning</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7157,19 +7160,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129711613</v>
+        <v>129700821</v>
       </c>
       <c r="B54" t="n">
         <v>57736</v>
@@ -7198,27 +7201,24 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>457300</v>
+        <v>457486</v>
       </c>
       <c r="R54" t="n">
-        <v>6678044</v>
+        <v>6677569</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7245,14 +7245,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Barkflagning</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7267,22 +7277,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129700821</v>
+        <v>129702610</v>
       </c>
       <c r="B55" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7290,39 +7300,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>457486</v>
+        <v>457417</v>
       </c>
       <c r="R55" t="n">
-        <v>6677569</v>
+        <v>6677423</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7354,7 +7359,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7364,12 +7369,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:49</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7513,10 +7513,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129699824</v>
+        <v>129701074</v>
       </c>
       <c r="B57" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7524,39 +7524,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>457346</v>
+        <v>457397</v>
       </c>
       <c r="R57" t="n">
-        <v>6677881</v>
+        <v>6677548</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7588,7 +7583,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7598,12 +7593,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7630,10 +7625,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129701074</v>
+        <v>129701963</v>
       </c>
       <c r="B58" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7641,34 +7636,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>457397</v>
+        <v>457294</v>
       </c>
       <c r="R58" t="n">
-        <v>6677548</v>
+        <v>6677481</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7700,7 +7700,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7710,12 +7710,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7742,48 +7742,56 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129700360</v>
+        <v>129711612</v>
       </c>
       <c r="B59" t="n">
-        <v>91563</v>
+        <v>57736</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>457345</v>
+        <v>457358</v>
       </c>
       <c r="R59" t="n">
-        <v>6677677</v>
+        <v>6677489</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7810,19 +7818,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>11:26</t>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Möjligt början på bohål i år/fjolåret.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7837,22 +7840,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129711614</v>
+        <v>129699824</v>
       </c>
       <c r="B60" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7860,16 +7863,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -7878,19 +7881,24 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>457280</v>
+        <v>457346</v>
       </c>
       <c r="R60" t="n">
-        <v>6678029</v>
+        <v>6677881</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7917,14 +7925,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Färskt födosök av spillkråka i björk stubbe.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7939,62 +7957,57 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129701963</v>
+        <v>129700360</v>
       </c>
       <c r="B61" t="n">
-        <v>57736</v>
+        <v>91563</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>457294</v>
+        <v>457345</v>
       </c>
       <c r="R61" t="n">
-        <v>6677481</v>
+        <v>6677677</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8026,7 +8039,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8036,12 +8049,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:43</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8068,10 +8076,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129711612</v>
+        <v>129711614</v>
       </c>
       <c r="B62" t="n">
-        <v>57736</v>
+        <v>57733</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8079,16 +8087,16 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -8097,24 +8105,16 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>457358</v>
+        <v>457280</v>
       </c>
       <c r="R62" t="n">
-        <v>6677489</v>
+        <v>6678029</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -8151,7 +8151,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Möjligt början på bohål i år/fjolåret.</t>
+          <t>Färskt födosök av spillkråka i björk stubbe.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8526,10 +8526,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129703525</v>
+        <v>129703378</v>
       </c>
       <c r="B66" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8537,39 +8537,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>457433</v>
+        <v>457407</v>
       </c>
       <c r="R66" t="n">
-        <v>6677123</v>
+        <v>6677144</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8601,7 +8596,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8611,12 +8606,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Rikligt på tall.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8643,10 +8638,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129702120</v>
+        <v>129711616</v>
       </c>
       <c r="B67" t="n">
-        <v>57736</v>
+        <v>78838</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8654,42 +8649,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>457299</v>
+        <v>457305</v>
       </c>
       <c r="R67" t="n">
-        <v>6677464</v>
+        <v>6677449</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8716,19 +8706,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>12:47</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8743,22 +8723,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129704842</v>
+        <v>129703525</v>
       </c>
       <c r="B68" t="n">
-        <v>78839</v>
+        <v>57736</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8766,34 +8746,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>457230</v>
+        <v>457433</v>
       </c>
       <c r="R68" t="n">
-        <v>6677594</v>
+        <v>6677123</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8825,7 +8810,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8835,12 +8820,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Lite osäker men rätt säker.</t>
+          <t>Rikligt på tall.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8867,10 +8852,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129703378</v>
+        <v>129704842</v>
       </c>
       <c r="B69" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8878,34 +8863,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>457407</v>
+        <v>457230</v>
       </c>
       <c r="R69" t="n">
-        <v>6677144</v>
+        <v>6677594</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8937,7 +8922,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8947,12 +8932,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Lite osäker men rätt säker.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8979,10 +8964,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129711616</v>
+        <v>129702120</v>
       </c>
       <c r="B70" t="n">
-        <v>78838</v>
+        <v>57736</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8990,37 +8975,42 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>457305</v>
+        <v>457299</v>
       </c>
       <c r="R70" t="n">
-        <v>6677449</v>
+        <v>6677464</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9047,9 +9037,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9064,12 +9064,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -9305,10 +9305,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129711617</v>
+        <v>129704249</v>
       </c>
       <c r="B73" t="n">
-        <v>79081</v>
+        <v>97036</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9316,37 +9316,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>457423</v>
+        <v>457311</v>
       </c>
       <c r="R73" t="n">
-        <v>6677206</v>
+        <v>6677235</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9373,14 +9373,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>På tallstam</t>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9395,22 +9400,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129704249</v>
+        <v>129711617</v>
       </c>
       <c r="B74" t="n">
-        <v>97036</v>
+        <v>79081</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9418,37 +9423,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>457311</v>
+        <v>457423</v>
       </c>
       <c r="R74" t="n">
-        <v>6677235</v>
+        <v>6677206</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9475,19 +9480,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>14:11</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>14:11</t>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>På tallstam</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9502,12 +9502,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -10196,10 +10196,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129703164</v>
+        <v>129702050</v>
       </c>
       <c r="B81" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10207,34 +10207,39 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>457394</v>
+        <v>457274</v>
       </c>
       <c r="R81" t="n">
-        <v>6677203</v>
+        <v>6677446</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10266,7 +10271,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10276,7 +10281,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10303,10 +10313,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129700616</v>
+        <v>129701018</v>
       </c>
       <c r="B82" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10314,34 +10324,39 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>457384</v>
+        <v>457426</v>
       </c>
       <c r="R82" t="n">
-        <v>6677586</v>
+        <v>6677541</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10373,7 +10388,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10383,12 +10398,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10415,10 +10430,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129702050</v>
+        <v>129703164</v>
       </c>
       <c r="B83" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10426,39 +10441,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>457274</v>
+        <v>457394</v>
       </c>
       <c r="R83" t="n">
-        <v>6677446</v>
+        <v>6677203</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10490,7 +10500,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10500,12 +10510,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:46</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10532,10 +10537,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129701018</v>
+        <v>129700616</v>
       </c>
       <c r="B84" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10543,39 +10548,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>457426</v>
+        <v>457384</v>
       </c>
       <c r="R84" t="n">
-        <v>6677541</v>
+        <v>6677586</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10607,7 +10607,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -12457,56 +12457,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129704065</v>
+        <v>129722043</v>
       </c>
       <c r="B101" t="n">
-        <v>92881</v>
+        <v>79081</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>457293</v>
+        <v>457469</v>
       </c>
       <c r="R101" t="n">
-        <v>6677157</v>
+        <v>6676536</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12533,22 +12522,22 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12557,7 +12546,6 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -12576,45 +12564,56 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129722043</v>
+        <v>129704065</v>
       </c>
       <c r="B102" t="n">
-        <v>79081</v>
+        <v>92881</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>457469</v>
+        <v>457293</v>
       </c>
       <c r="R102" t="n">
-        <v>6676536</v>
+        <v>6677157</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12641,22 +12640,22 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12665,6 +12664,7 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -12683,10 +12683,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129722392</v>
+        <v>129721585</v>
       </c>
       <c r="B103" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12694,42 +12694,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
+          <t>Lagalamm, Lagalamm, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>457336</v>
+        <v>457426</v>
       </c>
       <c r="R103" t="n">
-        <v>6676787</v>
+        <v>6676070</v>
       </c>
       <c r="S103" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12758,7 +12753,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12768,12 +12763,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:36</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Rikligt.</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12800,10 +12790,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129721585</v>
+        <v>129722392</v>
       </c>
       <c r="B104" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12811,37 +12801,42 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Lagalamm, Lagalamm, Dlr</t>
+          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>457426</v>
+        <v>457336</v>
       </c>
       <c r="R104" t="n">
-        <v>6676070</v>
+        <v>6676787</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12870,7 +12865,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12880,7 +12875,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Rikligt.</t>
         </is>
       </c>
       <c r="AD104" t="b">

--- a/artfynd/A 49804-2025 artfynd.xlsx
+++ b/artfynd/A 49804-2025 artfynd.xlsx
@@ -7513,10 +7513,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129701074</v>
+        <v>129699824</v>
       </c>
       <c r="B57" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7524,34 +7524,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>457397</v>
+        <v>457346</v>
       </c>
       <c r="R57" t="n">
-        <v>6677548</v>
+        <v>6677881</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7583,7 +7588,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7593,12 +7598,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7625,10 +7630,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129701963</v>
+        <v>129701074</v>
       </c>
       <c r="B58" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7636,39 +7641,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>457294</v>
+        <v>457397</v>
       </c>
       <c r="R58" t="n">
-        <v>6677481</v>
+        <v>6677548</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7700,7 +7700,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7710,12 +7710,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7742,56 +7742,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129711612</v>
+        <v>129700360</v>
       </c>
       <c r="B59" t="n">
-        <v>57736</v>
+        <v>91563</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>457358</v>
+        <v>457345</v>
       </c>
       <c r="R59" t="n">
-        <v>6677489</v>
+        <v>6677677</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7818,14 +7810,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Möjligt början på bohål i år/fjolåret.</t>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7840,22 +7837,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129699824</v>
+        <v>129711614</v>
       </c>
       <c r="B60" t="n">
-        <v>57736</v>
+        <v>57733</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7863,16 +7860,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -7881,24 +7878,19 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>457346</v>
+        <v>457280</v>
       </c>
       <c r="R60" t="n">
-        <v>6677881</v>
+        <v>6678029</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7925,24 +7917,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Färskt födosök av spillkråka i björk stubbe.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7957,57 +7939,62 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129700360</v>
+        <v>129701963</v>
       </c>
       <c r="B61" t="n">
-        <v>91563</v>
+        <v>57736</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>457345</v>
+        <v>457294</v>
       </c>
       <c r="R61" t="n">
-        <v>6677677</v>
+        <v>6677481</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8039,7 +8026,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8049,7 +8036,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8076,10 +8068,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129711614</v>
+        <v>129711612</v>
       </c>
       <c r="B62" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8087,16 +8079,16 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -8105,16 +8097,24 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>457280</v>
+        <v>457358</v>
       </c>
       <c r="R62" t="n">
-        <v>6678029</v>
+        <v>6677489</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -8151,7 +8151,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Färskt födosök av spillkråka i björk stubbe.</t>
+          <t>Möjligt början på bohål i år/fjolåret.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8526,10 +8526,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129703378</v>
+        <v>129703525</v>
       </c>
       <c r="B66" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8537,34 +8537,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>457407</v>
+        <v>457433</v>
       </c>
       <c r="R66" t="n">
-        <v>6677144</v>
+        <v>6677123</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8596,7 +8601,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8606,12 +8611,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Rikligt på tall.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8638,10 +8643,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129711616</v>
+        <v>129702120</v>
       </c>
       <c r="B67" t="n">
-        <v>78838</v>
+        <v>57736</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8649,37 +8654,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>457305</v>
+        <v>457299</v>
       </c>
       <c r="R67" t="n">
-        <v>6677449</v>
+        <v>6677464</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8706,9 +8716,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8723,22 +8743,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129703525</v>
+        <v>129704842</v>
       </c>
       <c r="B68" t="n">
-        <v>57736</v>
+        <v>78839</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8746,39 +8766,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>457433</v>
+        <v>457230</v>
       </c>
       <c r="R68" t="n">
-        <v>6677123</v>
+        <v>6677594</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8810,7 +8825,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8820,12 +8835,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Rikligt på tall.</t>
+          <t>Lite osäker men rätt säker.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8852,10 +8867,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129704842</v>
+        <v>129703378</v>
       </c>
       <c r="B69" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8863,34 +8878,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>457230</v>
+        <v>457407</v>
       </c>
       <c r="R69" t="n">
-        <v>6677594</v>
+        <v>6677144</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8922,7 +8937,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8932,12 +8947,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Lite osäker men rätt säker.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8964,10 +8979,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129702120</v>
+        <v>129711616</v>
       </c>
       <c r="B70" t="n">
-        <v>57736</v>
+        <v>78838</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8975,42 +8990,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>457299</v>
+        <v>457305</v>
       </c>
       <c r="R70" t="n">
-        <v>6677464</v>
+        <v>6677449</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9037,19 +9047,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>12:47</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9064,12 +9064,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -9305,10 +9305,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129704249</v>
+        <v>129711617</v>
       </c>
       <c r="B73" t="n">
-        <v>97036</v>
+        <v>79081</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9316,37 +9316,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>457311</v>
+        <v>457423</v>
       </c>
       <c r="R73" t="n">
-        <v>6677235</v>
+        <v>6677206</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9373,19 +9373,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>14:11</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>14:11</t>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>På tallstam</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9400,22 +9395,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129711617</v>
+        <v>129704249</v>
       </c>
       <c r="B74" t="n">
-        <v>79081</v>
+        <v>97036</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9423,37 +9418,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>457423</v>
+        <v>457311</v>
       </c>
       <c r="R74" t="n">
-        <v>6677206</v>
+        <v>6677235</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9480,14 +9475,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>På tallstam</t>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9502,12 +9502,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -11433,10 +11433,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129703817</v>
+        <v>129701101</v>
       </c>
       <c r="B92" t="n">
-        <v>78838</v>
+        <v>57736</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11444,34 +11444,39 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>457337</v>
+        <v>457396</v>
       </c>
       <c r="R92" t="n">
-        <v>6677076</v>
+        <v>6677546</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11503,7 +11508,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11513,7 +11518,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Inte super färska.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11657,10 +11667,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129701101</v>
+        <v>129703817</v>
       </c>
       <c r="B94" t="n">
-        <v>57736</v>
+        <v>78838</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11668,39 +11678,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>457396</v>
+        <v>457337</v>
       </c>
       <c r="R94" t="n">
-        <v>6677546</v>
+        <v>6677076</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11732,7 +11737,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11742,12 +11747,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:03</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Inte super färska.</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12223,7 +12223,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129722173</v>
+        <v>129722296</v>
       </c>
       <c r="B99" t="n">
         <v>57736</v>
@@ -12254,7 +12254,7 @@
       <c r="I99" t="inlineStr"/>
       <c r="M99" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -12263,10 +12263,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>457418</v>
+        <v>457348</v>
       </c>
       <c r="R99" t="n">
-        <v>6676575</v>
+        <v>6676704</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -12298,7 +12298,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12308,12 +12308,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Lite färskare och äldre.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12340,7 +12340,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129722296</v>
+        <v>129722173</v>
       </c>
       <c r="B100" t="n">
         <v>57736</v>
@@ -12371,7 +12371,7 @@
       <c r="I100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -12380,10 +12380,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>457348</v>
+        <v>457418</v>
       </c>
       <c r="R100" t="n">
-        <v>6676704</v>
+        <v>6676575</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -12415,7 +12415,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12425,12 +12425,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Lite färskare och äldre.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12457,45 +12457,56 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129722043</v>
+        <v>129704065</v>
       </c>
       <c r="B101" t="n">
-        <v>79081</v>
+        <v>92881</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>457469</v>
+        <v>457293</v>
       </c>
       <c r="R101" t="n">
-        <v>6676536</v>
+        <v>6677157</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12522,22 +12533,22 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12546,6 +12557,7 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -12564,56 +12576,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129704065</v>
+        <v>129722043</v>
       </c>
       <c r="B102" t="n">
-        <v>92881</v>
+        <v>79081</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>457293</v>
+        <v>457469</v>
       </c>
       <c r="R102" t="n">
-        <v>6677157</v>
+        <v>6676536</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12640,22 +12641,22 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12664,7 +12665,6 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -13248,59 +13248,48 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129699541</v>
+        <v>129722095</v>
       </c>
       <c r="B108" t="n">
-        <v>92881</v>
+        <v>79081</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
+          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>457267</v>
+        <v>457440</v>
       </c>
       <c r="R108" t="n">
-        <v>6678042</v>
+        <v>6676555</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -13324,22 +13313,27 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Ganska hänlavs rikt.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13348,7 +13342,6 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -13367,48 +13360,59 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129722095</v>
+        <v>129699541</v>
       </c>
       <c r="B109" t="n">
-        <v>79081</v>
+        <v>92881</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
+          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>457440</v>
+        <v>457267</v>
       </c>
       <c r="R109" t="n">
-        <v>6676555</v>
+        <v>6678042</v>
       </c>
       <c r="S109" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -13432,27 +13436,22 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>15:19</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Ganska hänlavs rikt.</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13461,6 +13460,7 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49804-2025 artfynd.xlsx
+++ b/artfynd/A 49804-2025 artfynd.xlsx
@@ -6953,7 +6953,7 @@
         <v>129699502</v>
       </c>
       <c r="B52" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129711613</v>
+        <v>129702610</v>
       </c>
       <c r="B53" t="n">
-        <v>57736</v>
+        <v>79084</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7073,45 +7073,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>457300</v>
+        <v>457417</v>
       </c>
       <c r="R53" t="n">
-        <v>6678044</v>
+        <v>6677423</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7138,14 +7130,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Barkflagning</t>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7160,12 +7157,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -7175,7 +7172,7 @@
         <v>129700821</v>
       </c>
       <c r="B54" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7289,10 +7286,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129702610</v>
+        <v>129711613</v>
       </c>
       <c r="B55" t="n">
-        <v>79081</v>
+        <v>57737</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7300,37 +7297,45 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>457417</v>
+        <v>457300</v>
       </c>
       <c r="R55" t="n">
-        <v>6677423</v>
+        <v>6678044</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7357,19 +7362,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>13:10</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>13:10</t>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Barkflagning</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7384,12 +7384,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -7399,7 +7399,7 @@
         <v>129703897</v>
       </c>
       <c r="B56" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7516,7 +7516,7 @@
         <v>129699824</v>
       </c>
       <c r="B57" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7630,32 +7630,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129701074</v>
+        <v>129700360</v>
       </c>
       <c r="B58" t="n">
-        <v>79081</v>
+        <v>91566</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7665,10 +7665,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>457397</v>
+        <v>457345</v>
       </c>
       <c r="R58" t="n">
-        <v>6677548</v>
+        <v>6677677</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7700,7 +7700,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7710,12 +7710,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:02</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7742,32 +7737,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129700360</v>
+        <v>129701074</v>
       </c>
       <c r="B59" t="n">
-        <v>91563</v>
+        <v>79084</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7777,10 +7772,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>457345</v>
+        <v>457397</v>
       </c>
       <c r="R59" t="n">
-        <v>6677677</v>
+        <v>6677548</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7812,7 +7807,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7822,7 +7817,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7852,7 +7852,7 @@
         <v>129711614</v>
       </c>
       <c r="B60" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7951,10 +7951,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129701963</v>
+        <v>129711612</v>
       </c>
       <c r="B61" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7980,24 +7980,27 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>457294</v>
+        <v>457358</v>
       </c>
       <c r="R61" t="n">
-        <v>6677481</v>
+        <v>6677489</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8024,24 +8027,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>12:43</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>12:43</t>
-        </is>
-      </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Möjligt början på bohål i år/fjolåret.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8056,22 +8049,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129711612</v>
+        <v>129701963</v>
       </c>
       <c r="B62" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8097,27 +8090,24 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>457358</v>
+        <v>457294</v>
       </c>
       <c r="R62" t="n">
-        <v>6677489</v>
+        <v>6677481</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8144,14 +8134,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Möjligt början på bohål i år/fjolåret.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8166,12 +8166,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -8181,7 +8181,7 @@
         <v>129700848</v>
       </c>
       <c r="B63" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>129703670</v>
       </c>
       <c r="B64" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>129711615</v>
       </c>
       <c r="B65" t="n">
-        <v>91583</v>
+        <v>91586</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8526,10 +8526,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129703525</v>
+        <v>129703378</v>
       </c>
       <c r="B66" t="n">
-        <v>57736</v>
+        <v>79084</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8537,39 +8537,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>457433</v>
+        <v>457407</v>
       </c>
       <c r="R66" t="n">
-        <v>6677123</v>
+        <v>6677144</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8601,7 +8596,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8611,12 +8606,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Rikligt på tall.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8643,10 +8638,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129702120</v>
+        <v>129711616</v>
       </c>
       <c r="B67" t="n">
-        <v>57736</v>
+        <v>78841</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8654,42 +8649,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>457299</v>
+        <v>457305</v>
       </c>
       <c r="R67" t="n">
-        <v>6677464</v>
+        <v>6677449</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8716,19 +8706,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>12:47</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8743,22 +8723,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129704842</v>
+        <v>129703525</v>
       </c>
       <c r="B68" t="n">
-        <v>78839</v>
+        <v>57737</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8766,34 +8746,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>457230</v>
+        <v>457433</v>
       </c>
       <c r="R68" t="n">
-        <v>6677594</v>
+        <v>6677123</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8825,7 +8810,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8835,12 +8820,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Lite osäker men rätt säker.</t>
+          <t>Rikligt på tall.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8867,10 +8852,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129703378</v>
+        <v>129702120</v>
       </c>
       <c r="B69" t="n">
-        <v>79081</v>
+        <v>57737</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8878,34 +8863,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>457407</v>
+        <v>457299</v>
       </c>
       <c r="R69" t="n">
-        <v>6677144</v>
+        <v>6677464</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8937,7 +8927,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8947,12 +8937,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:36</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8979,10 +8964,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129711616</v>
+        <v>129704842</v>
       </c>
       <c r="B70" t="n">
-        <v>78838</v>
+        <v>78842</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8990,37 +8975,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>457305</v>
+        <v>457230</v>
       </c>
       <c r="R70" t="n">
-        <v>6677449</v>
+        <v>6677594</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9047,9 +9032,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Lite osäker men rätt säker.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9064,22 +9064,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129704395</v>
+        <v>129702970</v>
       </c>
       <c r="B71" t="n">
-        <v>57736</v>
+        <v>79084</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9087,39 +9087,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>457267</v>
+        <v>457390</v>
       </c>
       <c r="R71" t="n">
-        <v>6677342</v>
+        <v>6677240</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9151,7 +9146,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9161,12 +9156,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9193,10 +9188,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129702970</v>
+        <v>129704395</v>
       </c>
       <c r="B72" t="n">
-        <v>79081</v>
+        <v>57737</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9204,34 +9199,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>457390</v>
+        <v>457267</v>
       </c>
       <c r="R72" t="n">
-        <v>6677240</v>
+        <v>6677342</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9263,7 +9263,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9273,12 +9273,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9305,10 +9305,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129711617</v>
+        <v>129704249</v>
       </c>
       <c r="B73" t="n">
-        <v>79081</v>
+        <v>97040</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9316,37 +9316,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>457423</v>
+        <v>457311</v>
       </c>
       <c r="R73" t="n">
-        <v>6677206</v>
+        <v>6677235</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9373,14 +9373,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>På tallstam</t>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9395,22 +9400,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129704249</v>
+        <v>129711617</v>
       </c>
       <c r="B74" t="n">
-        <v>97036</v>
+        <v>79084</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9418,37 +9423,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>457311</v>
+        <v>457423</v>
       </c>
       <c r="R74" t="n">
-        <v>6677235</v>
+        <v>6677206</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9475,19 +9480,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>14:11</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>14:11</t>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>På tallstam</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9502,12 +9502,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -9517,7 +9517,7 @@
         <v>129702657</v>
       </c>
       <c r="B75" t="n">
-        <v>91563</v>
+        <v>91566</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9624,7 +9624,7 @@
         <v>129704181</v>
       </c>
       <c r="B76" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9741,7 +9741,7 @@
         <v>129700400</v>
       </c>
       <c r="B77" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
         <v>129699484</v>
       </c>
       <c r="B78" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>129702998</v>
       </c>
       <c r="B79" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10082,7 +10082,7 @@
         <v>129703222</v>
       </c>
       <c r="B80" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10196,10 +10196,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129702050</v>
+        <v>129701018</v>
       </c>
       <c r="B81" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10227,7 +10227,7 @@
       <c r="I81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -10236,10 +10236,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>457274</v>
+        <v>457426</v>
       </c>
       <c r="R81" t="n">
-        <v>6677446</v>
+        <v>6677541</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10271,7 +10271,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10281,7 +10281,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
@@ -10313,10 +10313,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129701018</v>
+        <v>129703164</v>
       </c>
       <c r="B82" t="n">
-        <v>57736</v>
+        <v>79084</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10324,39 +10324,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>457426</v>
+        <v>457394</v>
       </c>
       <c r="R82" t="n">
-        <v>6677541</v>
+        <v>6677203</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10388,7 +10383,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10398,12 +10393,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:59</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10430,10 +10420,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129703164</v>
+        <v>129700616</v>
       </c>
       <c r="B83" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10461,14 +10451,14 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>457394</v>
+        <v>457384</v>
       </c>
       <c r="R83" t="n">
-        <v>6677203</v>
+        <v>6677586</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10500,7 +10490,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10510,7 +10500,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10537,10 +10532,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129700616</v>
+        <v>129702050</v>
       </c>
       <c r="B84" t="n">
-        <v>79081</v>
+        <v>57737</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10548,34 +10543,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>457384</v>
+        <v>457274</v>
       </c>
       <c r="R84" t="n">
-        <v>6677586</v>
+        <v>6677446</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10607,7 +10607,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10652,7 +10652,7 @@
         <v>129700434</v>
       </c>
       <c r="B85" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10766,10 +10766,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129700950</v>
+        <v>129711618</v>
       </c>
       <c r="B86" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10797,17 +10797,17 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>457431</v>
+        <v>457392</v>
       </c>
       <c r="R86" t="n">
-        <v>6677513</v>
+        <v>6677547</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10834,24 +10834,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>På gran.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10866,22 +10851,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129703077</v>
+        <v>129700950</v>
       </c>
       <c r="B87" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10909,14 +10894,14 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>457393</v>
+        <v>457431</v>
       </c>
       <c r="R87" t="n">
-        <v>6677229</v>
+        <v>6677513</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10948,7 +10933,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10958,7 +10943,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
@@ -10990,10 +10975,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129704366</v>
+        <v>129703077</v>
       </c>
       <c r="B88" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11025,10 +11010,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>457288</v>
+        <v>457393</v>
       </c>
       <c r="R88" t="n">
-        <v>6677333</v>
+        <v>6677229</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11060,7 +11045,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11070,12 +11055,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11102,10 +11087,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129711618</v>
+        <v>129704366</v>
       </c>
       <c r="B89" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11133,17 +11118,17 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>457392</v>
+        <v>457288</v>
       </c>
       <c r="R89" t="n">
-        <v>6677547</v>
+        <v>6677333</v>
       </c>
       <c r="S89" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11170,9 +11155,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11187,12 +11187,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
@@ -11202,7 +11202,7 @@
         <v>129702495</v>
       </c>
       <c r="B90" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11319,7 +11319,7 @@
         <v>129700968</v>
       </c>
       <c r="B91" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11436,7 +11436,7 @@
         <v>129701101</v>
       </c>
       <c r="B92" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11553,7 +11553,7 @@
         <v>129699765</v>
       </c>
       <c r="B93" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11670,7 +11670,7 @@
         <v>129703817</v>
       </c>
       <c r="B94" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11777,7 +11777,7 @@
         <v>129703127</v>
       </c>
       <c r="B95" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11884,7 +11884,7 @@
         <v>129700098</v>
       </c>
       <c r="B96" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12001,7 +12001,7 @@
         <v>129717970</v>
       </c>
       <c r="B97" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>129722077</v>
       </c>
       <c r="B98" t="n">
-        <v>91619</v>
+        <v>91622</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12223,10 +12223,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129722296</v>
+        <v>129722173</v>
       </c>
       <c r="B99" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12254,7 +12254,7 @@
       <c r="I99" t="inlineStr"/>
       <c r="M99" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -12263,10 +12263,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>457348</v>
+        <v>457418</v>
       </c>
       <c r="R99" t="n">
-        <v>6676704</v>
+        <v>6676575</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -12298,7 +12298,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12308,12 +12308,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Lite färskare och äldre.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12340,10 +12340,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129722173</v>
+        <v>129722296</v>
       </c>
       <c r="B100" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12371,7 +12371,7 @@
       <c r="I100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -12380,10 +12380,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>457418</v>
+        <v>457348</v>
       </c>
       <c r="R100" t="n">
-        <v>6676575</v>
+        <v>6676704</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -12415,7 +12415,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12425,12 +12425,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Lite färskare och äldre.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12460,7 +12460,7 @@
         <v>129704065</v>
       </c>
       <c r="B101" t="n">
-        <v>92881</v>
+        <v>92884</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12579,7 +12579,7 @@
         <v>129722043</v>
       </c>
       <c r="B102" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12686,7 +12686,7 @@
         <v>129721585</v>
       </c>
       <c r="B103" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12793,7 +12793,7 @@
         <v>129722392</v>
       </c>
       <c r="B104" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         <v>129722198</v>
       </c>
       <c r="B105" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13027,7 +13027,7 @@
         <v>129717396</v>
       </c>
       <c r="B106" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13144,7 +13144,7 @@
         <v>129721773</v>
       </c>
       <c r="B107" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13248,48 +13248,59 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129722095</v>
+        <v>129699541</v>
       </c>
       <c r="B108" t="n">
-        <v>79081</v>
+        <v>92884</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
+          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>457440</v>
+        <v>457267</v>
       </c>
       <c r="R108" t="n">
-        <v>6676555</v>
+        <v>6678042</v>
       </c>
       <c r="S108" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -13313,27 +13324,22 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>15:19</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Ganska hänlavs rikt.</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13342,6 +13348,7 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -13360,59 +13367,48 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129699541</v>
+        <v>129722095</v>
       </c>
       <c r="B109" t="n">
-        <v>92881</v>
+        <v>79084</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
+          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>457267</v>
+        <v>457440</v>
       </c>
       <c r="R109" t="n">
-        <v>6678042</v>
+        <v>6676555</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -13436,22 +13432,27 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Ganska hänlavs rikt.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13460,7 +13461,6 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
@@ -13482,7 +13482,7 @@
         <v>129717610</v>
       </c>
       <c r="B110" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13599,7 +13599,7 @@
         <v>129722523</v>
       </c>
       <c r="B111" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13716,7 +13716,7 @@
         <v>129721616</v>
       </c>
       <c r="B112" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>129722486</v>
       </c>
       <c r="B113" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13935,7 +13935,7 @@
         <v>129717654</v>
       </c>
       <c r="B114" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14047,7 +14047,7 @@
         <v>129722420</v>
       </c>
       <c r="B115" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14154,7 +14154,7 @@
         <v>129722346</v>
       </c>
       <c r="B116" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>

--- a/artfynd/A 49804-2025 artfynd.xlsx
+++ b/artfynd/A 49804-2025 artfynd.xlsx
@@ -7630,48 +7630,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129700360</v>
+        <v>129711614</v>
       </c>
       <c r="B58" t="n">
-        <v>91566</v>
+        <v>57734</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>457345</v>
+        <v>457280</v>
       </c>
       <c r="R58" t="n">
-        <v>6677677</v>
+        <v>6678029</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7698,19 +7698,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>11:26</t>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Färskt födosök av spillkråka i björk stubbe.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7725,44 +7720,44 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129701074</v>
+        <v>129700360</v>
       </c>
       <c r="B59" t="n">
-        <v>79084</v>
+        <v>91566</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7772,10 +7767,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>457397</v>
+        <v>457345</v>
       </c>
       <c r="R59" t="n">
-        <v>6677548</v>
+        <v>6677677</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7807,7 +7802,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7817,12 +7812,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:02</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7849,10 +7839,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129711614</v>
+        <v>129701074</v>
       </c>
       <c r="B60" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7860,37 +7850,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>457280</v>
+        <v>457397</v>
       </c>
       <c r="R60" t="n">
-        <v>6678029</v>
+        <v>6677548</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7917,14 +7907,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Färskt födosök av spillkråka i björk stubbe.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7939,12 +7939,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -9076,10 +9076,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129702970</v>
+        <v>129704395</v>
       </c>
       <c r="B71" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9087,34 +9087,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>457390</v>
+        <v>457267</v>
       </c>
       <c r="R71" t="n">
-        <v>6677240</v>
+        <v>6677342</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9146,7 +9151,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9156,12 +9161,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9188,10 +9193,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129704395</v>
+        <v>129702970</v>
       </c>
       <c r="B72" t="n">
-        <v>57737</v>
+        <v>79084</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9199,39 +9204,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>457267</v>
+        <v>457390</v>
       </c>
       <c r="R72" t="n">
-        <v>6677342</v>
+        <v>6677240</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9263,7 +9263,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9273,12 +9273,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9305,10 +9305,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129704249</v>
+        <v>129711617</v>
       </c>
       <c r="B73" t="n">
-        <v>97040</v>
+        <v>79084</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9316,37 +9316,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>457311</v>
+        <v>457423</v>
       </c>
       <c r="R73" t="n">
-        <v>6677235</v>
+        <v>6677206</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9373,19 +9373,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>14:11</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>14:11</t>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>På tallstam</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9400,22 +9395,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129711617</v>
+        <v>129704249</v>
       </c>
       <c r="B74" t="n">
-        <v>79084</v>
+        <v>97040</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9423,37 +9418,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>457423</v>
+        <v>457311</v>
       </c>
       <c r="R74" t="n">
-        <v>6677206</v>
+        <v>6677235</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9480,14 +9475,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>På tallstam</t>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9502,12 +9502,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -10766,10 +10766,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129711618</v>
+        <v>129702495</v>
       </c>
       <c r="B86" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10777,37 +10777,42 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>457392</v>
+        <v>457432</v>
       </c>
       <c r="R86" t="n">
-        <v>6677547</v>
+        <v>6677419</v>
       </c>
       <c r="S86" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10834,9 +10839,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10851,22 +10871,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129700950</v>
+        <v>129700968</v>
       </c>
       <c r="B87" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10874,34 +10894,39 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>457431</v>
+        <v>457428</v>
       </c>
       <c r="R87" t="n">
-        <v>6677513</v>
+        <v>6677512</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10933,7 +10958,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10943,12 +10968,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10975,7 +11000,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129703077</v>
+        <v>129711618</v>
       </c>
       <c r="B88" t="n">
         <v>79084</v>
@@ -11006,17 +11031,17 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>457393</v>
+        <v>457392</v>
       </c>
       <c r="R88" t="n">
-        <v>6677229</v>
+        <v>6677547</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -11043,24 +11068,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>På gran.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11075,19 +11085,19 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129704366</v>
+        <v>129700950</v>
       </c>
       <c r="B89" t="n">
         <v>79084</v>
@@ -11118,14 +11128,14 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>457288</v>
+        <v>457431</v>
       </c>
       <c r="R89" t="n">
-        <v>6677333</v>
+        <v>6677513</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11157,7 +11167,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11167,12 +11177,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11199,10 +11209,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129702495</v>
+        <v>129703077</v>
       </c>
       <c r="B90" t="n">
-        <v>57737</v>
+        <v>79084</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11210,39 +11220,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>457432</v>
+        <v>457393</v>
       </c>
       <c r="R90" t="n">
-        <v>6677419</v>
+        <v>6677229</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11274,7 +11279,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11284,12 +11289,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11316,10 +11321,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129700968</v>
+        <v>129704366</v>
       </c>
       <c r="B91" t="n">
-        <v>57737</v>
+        <v>79084</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11327,39 +11332,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>457428</v>
+        <v>457288</v>
       </c>
       <c r="R91" t="n">
-        <v>6677512</v>
+        <v>6677333</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD91" t="b">

--- a/artfynd/A 49804-2025 artfynd.xlsx
+++ b/artfynd/A 49804-2025 artfynd.xlsx
@@ -6953,7 +6953,7 @@
         <v>129699502</v>
       </c>
       <c r="B52" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>129702610</v>
       </c>
       <c r="B53" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
         <v>129700821</v>
       </c>
       <c r="B54" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>129711613</v>
       </c>
       <c r="B55" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         <v>129703897</v>
       </c>
       <c r="B56" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7513,50 +7513,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129699824</v>
+        <v>129700360</v>
       </c>
       <c r="B57" t="n">
-        <v>57737</v>
+        <v>91569</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>457346</v>
+        <v>457345</v>
       </c>
       <c r="R57" t="n">
-        <v>6677881</v>
+        <v>6677677</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7588,7 +7583,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7598,12 +7593,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:04</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7630,10 +7620,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129711614</v>
+        <v>129701074</v>
       </c>
       <c r="B58" t="n">
-        <v>57734</v>
+        <v>79087</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7641,37 +7631,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>457280</v>
+        <v>457397</v>
       </c>
       <c r="R58" t="n">
-        <v>6678029</v>
+        <v>6677548</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7698,14 +7688,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Färskt födosök av spillkråka i björk stubbe.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7720,60 +7720,60 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129700360</v>
+        <v>129711614</v>
       </c>
       <c r="B59" t="n">
-        <v>91566</v>
+        <v>57737</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>457345</v>
+        <v>457280</v>
       </c>
       <c r="R59" t="n">
-        <v>6677677</v>
+        <v>6678029</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7800,19 +7800,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>11:26</t>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Färskt födosök av spillkråka i björk stubbe.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7827,22 +7822,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129701074</v>
+        <v>129711612</v>
       </c>
       <c r="B60" t="n">
-        <v>79084</v>
+        <v>57740</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7850,37 +7845,45 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>457397</v>
+        <v>457358</v>
       </c>
       <c r="R60" t="n">
-        <v>6677548</v>
+        <v>6677489</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7907,24 +7910,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Möjligt början på bohål i år/fjolåret.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7939,22 +7932,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129711612</v>
+        <v>129701963</v>
       </c>
       <c r="B61" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7980,27 +7973,24 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>457358</v>
+        <v>457294</v>
       </c>
       <c r="R61" t="n">
-        <v>6677489</v>
+        <v>6677481</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8027,14 +8017,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Möjligt början på bohål i år/fjolåret.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8049,22 +8049,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129701963</v>
+        <v>129699824</v>
       </c>
       <c r="B62" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
       <c r="I62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -8101,10 +8101,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>457294</v>
+        <v>457346</v>
       </c>
       <c r="R62" t="n">
-        <v>6677481</v>
+        <v>6677881</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8136,7 +8136,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
@@ -8181,7 +8181,7 @@
         <v>129700848</v>
       </c>
       <c r="B63" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>129703670</v>
       </c>
       <c r="B64" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8412,59 +8412,48 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129711615</v>
+        <v>129703378</v>
       </c>
       <c r="B65" t="n">
-        <v>91586</v>
+        <v>79087</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4660</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>457423</v>
+        <v>457407</v>
       </c>
       <c r="R65" t="n">
-        <v>6677421</v>
+        <v>6677144</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8491,14 +8480,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>10-15 fk på stående mindre asp.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8507,29 +8506,28 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129703378</v>
+        <v>129711616</v>
       </c>
       <c r="B66" t="n">
-        <v>79084</v>
+        <v>78844</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8537,37 +8535,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>457407</v>
+        <v>457305</v>
       </c>
       <c r="R66" t="n">
-        <v>6677144</v>
+        <v>6677449</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8594,24 +8592,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>På tall.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8626,22 +8609,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129711616</v>
+        <v>129702120</v>
       </c>
       <c r="B67" t="n">
-        <v>78841</v>
+        <v>57740</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8649,37 +8632,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>457305</v>
+        <v>457299</v>
       </c>
       <c r="R67" t="n">
-        <v>6677449</v>
+        <v>6677464</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8706,9 +8694,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8723,65 +8721,71 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129703525</v>
+        <v>129711615</v>
       </c>
       <c r="B68" t="n">
-        <v>57737</v>
+        <v>91589</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>4660</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>457433</v>
+        <v>457423</v>
       </c>
       <c r="R68" t="n">
-        <v>6677123</v>
+        <v>6677421</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8808,24 +8812,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>13:41</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>13:41</t>
-        </is>
-      </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Rikligt på tall.</t>
+          <t>10-15 fk på stående mindre asp.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8834,28 +8828,29 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129702120</v>
+        <v>129703525</v>
       </c>
       <c r="B69" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8883,19 +8878,19 @@
       <c r="I69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>457299</v>
+        <v>457433</v>
       </c>
       <c r="R69" t="n">
-        <v>6677464</v>
+        <v>6677123</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8927,7 +8922,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8937,7 +8932,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Rikligt på tall.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8967,7 +8967,7 @@
         <v>129704842</v>
       </c>
       <c r="B70" t="n">
-        <v>78842</v>
+        <v>78845</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         <v>129704395</v>
       </c>
       <c r="B71" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>129702970</v>
       </c>
       <c r="B72" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9305,10 +9305,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129711617</v>
+        <v>129704249</v>
       </c>
       <c r="B73" t="n">
-        <v>79084</v>
+        <v>97043</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9316,37 +9316,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>457423</v>
+        <v>457311</v>
       </c>
       <c r="R73" t="n">
-        <v>6677206</v>
+        <v>6677235</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9373,14 +9373,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>På tallstam</t>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9395,22 +9400,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129704249</v>
+        <v>129711617</v>
       </c>
       <c r="B74" t="n">
-        <v>97040</v>
+        <v>79087</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9418,37 +9423,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>457311</v>
+        <v>457423</v>
       </c>
       <c r="R74" t="n">
-        <v>6677235</v>
+        <v>6677206</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9475,19 +9480,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>14:11</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>14:11</t>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>På tallstam</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9502,12 +9502,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -9517,7 +9517,7 @@
         <v>129702657</v>
       </c>
       <c r="B75" t="n">
-        <v>91566</v>
+        <v>91569</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9624,7 +9624,7 @@
         <v>129704181</v>
       </c>
       <c r="B76" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9741,7 +9741,7 @@
         <v>129700400</v>
       </c>
       <c r="B77" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
         <v>129699484</v>
       </c>
       <c r="B78" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>129702998</v>
       </c>
       <c r="B79" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10082,7 +10082,7 @@
         <v>129703222</v>
       </c>
       <c r="B80" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10196,10 +10196,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129701018</v>
+        <v>129703164</v>
       </c>
       <c r="B81" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10207,39 +10207,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>457426</v>
+        <v>457394</v>
       </c>
       <c r="R81" t="n">
-        <v>6677541</v>
+        <v>6677203</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10271,7 +10266,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10281,12 +10276,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:59</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10313,10 +10303,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129703164</v>
+        <v>129700616</v>
       </c>
       <c r="B82" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10344,14 +10334,14 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>457394</v>
+        <v>457384</v>
       </c>
       <c r="R82" t="n">
-        <v>6677203</v>
+        <v>6677586</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10383,7 +10373,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10393,7 +10383,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10420,10 +10415,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129700616</v>
+        <v>129701018</v>
       </c>
       <c r="B83" t="n">
-        <v>79084</v>
+        <v>57740</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10431,34 +10426,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>457384</v>
+        <v>457426</v>
       </c>
       <c r="R83" t="n">
-        <v>6677586</v>
+        <v>6677541</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10490,7 +10490,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10500,12 +10500,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10535,7 +10535,7 @@
         <v>129702050</v>
       </c>
       <c r="B84" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10652,7 +10652,7 @@
         <v>129700434</v>
       </c>
       <c r="B85" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10766,10 +10766,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129702495</v>
+        <v>129700950</v>
       </c>
       <c r="B86" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10777,39 +10777,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>457432</v>
+        <v>457431</v>
       </c>
       <c r="R86" t="n">
-        <v>6677419</v>
+        <v>6677513</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10841,7 +10836,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10851,12 +10846,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10883,10 +10878,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129700968</v>
+        <v>129703077</v>
       </c>
       <c r="B87" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10894,39 +10889,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>457428</v>
+        <v>457393</v>
       </c>
       <c r="R87" t="n">
-        <v>6677512</v>
+        <v>6677229</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10958,7 +10948,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10968,12 +10958,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11000,10 +10990,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129711618</v>
+        <v>129704366</v>
       </c>
       <c r="B88" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11031,17 +11021,17 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>457392</v>
+        <v>457288</v>
       </c>
       <c r="R88" t="n">
-        <v>6677547</v>
+        <v>6677333</v>
       </c>
       <c r="S88" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -11068,9 +11058,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11085,22 +11090,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129700950</v>
+        <v>129711618</v>
       </c>
       <c r="B89" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11128,17 +11133,17 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>457431</v>
+        <v>457392</v>
       </c>
       <c r="R89" t="n">
-        <v>6677513</v>
+        <v>6677547</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11165,24 +11170,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>På gran.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11197,22 +11187,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129703077</v>
+        <v>129702495</v>
       </c>
       <c r="B90" t="n">
-        <v>79084</v>
+        <v>57740</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11220,34 +11210,39 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>457393</v>
+        <v>457432</v>
       </c>
       <c r="R90" t="n">
-        <v>6677229</v>
+        <v>6677419</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11279,7 +11274,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11289,12 +11284,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11321,10 +11316,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129704366</v>
+        <v>129700968</v>
       </c>
       <c r="B91" t="n">
-        <v>79084</v>
+        <v>57740</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11332,34 +11327,39 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>457288</v>
+        <v>457428</v>
       </c>
       <c r="R91" t="n">
-        <v>6677333</v>
+        <v>6677512</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11433,10 +11433,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129701101</v>
+        <v>129699765</v>
       </c>
       <c r="B92" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11464,7 +11464,7 @@
       <c r="I92" t="inlineStr"/>
       <c r="M92" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -11473,10 +11473,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>457396</v>
+        <v>457317</v>
       </c>
       <c r="R92" t="n">
-        <v>6677546</v>
+        <v>6677895</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11508,7 +11508,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11518,12 +11518,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Inte super färska.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11550,10 +11550,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129699765</v>
+        <v>129701101</v>
       </c>
       <c r="B93" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11581,7 +11581,7 @@
       <c r="I93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -11590,10 +11590,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>457317</v>
+        <v>457396</v>
       </c>
       <c r="R93" t="n">
-        <v>6677895</v>
+        <v>6677546</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11625,7 +11625,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11635,12 +11635,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Inte super färska.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11670,7 +11670,7 @@
         <v>129703817</v>
       </c>
       <c r="B94" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11774,10 +11774,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129703127</v>
+        <v>129700098</v>
       </c>
       <c r="B95" t="n">
-        <v>78841</v>
+        <v>57740</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11785,34 +11785,39 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>457391</v>
+        <v>457355</v>
       </c>
       <c r="R95" t="n">
-        <v>6677213</v>
+        <v>6677771</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11844,7 +11849,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11854,7 +11859,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Inte jätte färska med syns sav fortfarande.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11881,10 +11891,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129700098</v>
+        <v>129703127</v>
       </c>
       <c r="B96" t="n">
-        <v>57737</v>
+        <v>78844</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11892,39 +11902,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>457355</v>
+        <v>457391</v>
       </c>
       <c r="R96" t="n">
-        <v>6677771</v>
+        <v>6677213</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11956,7 +11961,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11966,12 +11971,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Inte jätte färska med syns sav fortfarande.</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11998,10 +11998,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129717970</v>
+        <v>129722077</v>
       </c>
       <c r="B97" t="n">
-        <v>57737</v>
+        <v>91625</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12009,42 +12009,33 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>457534</v>
+        <v>457452</v>
       </c>
       <c r="R97" t="n">
-        <v>6676132</v>
+        <v>6676554</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -12073,7 +12064,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12083,12 +12074,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Ringhack på tall, hyfsat färska.</t>
+          <t>Fler fruktkroppar.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12115,10 +12106,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129722077</v>
+        <v>129717970</v>
       </c>
       <c r="B98" t="n">
-        <v>91622</v>
+        <v>57740</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12126,33 +12117,42 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>457452</v>
+        <v>457534</v>
       </c>
       <c r="R98" t="n">
-        <v>6676554</v>
+        <v>6676132</v>
       </c>
       <c r="S98" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -12181,7 +12181,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12191,12 +12191,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Fler fruktkroppar.</t>
+          <t>Ringhack på tall, hyfsat färska.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12223,10 +12223,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129722173</v>
+        <v>129722296</v>
       </c>
       <c r="B99" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12254,7 +12254,7 @@
       <c r="I99" t="inlineStr"/>
       <c r="M99" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -12263,10 +12263,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>457418</v>
+        <v>457348</v>
       </c>
       <c r="R99" t="n">
-        <v>6676575</v>
+        <v>6676704</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -12298,7 +12298,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12308,12 +12308,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Lite färskare och äldre.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12340,10 +12340,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129722296</v>
+        <v>129722173</v>
       </c>
       <c r="B100" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12371,7 +12371,7 @@
       <c r="I100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -12380,10 +12380,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>457348</v>
+        <v>457418</v>
       </c>
       <c r="R100" t="n">
-        <v>6676704</v>
+        <v>6676575</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -12415,7 +12415,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12425,12 +12425,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Lite färskare och äldre.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12460,7 +12460,7 @@
         <v>129704065</v>
       </c>
       <c r="B101" t="n">
-        <v>92884</v>
+        <v>92887</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12579,7 +12579,7 @@
         <v>129722043</v>
       </c>
       <c r="B102" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12683,10 +12683,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129721585</v>
+        <v>129722392</v>
       </c>
       <c r="B103" t="n">
-        <v>79084</v>
+        <v>57740</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12694,37 +12694,42 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Lagalamm, Lagalamm, Dlr</t>
+          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>457426</v>
+        <v>457336</v>
       </c>
       <c r="R103" t="n">
-        <v>6676070</v>
+        <v>6676787</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12753,7 +12758,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12763,7 +12768,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Rikligt.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12790,10 +12800,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129722392</v>
+        <v>129721585</v>
       </c>
       <c r="B104" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12801,42 +12811,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
+          <t>Lagalamm, Lagalamm, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>457336</v>
+        <v>457426</v>
       </c>
       <c r="R104" t="n">
-        <v>6676787</v>
+        <v>6676070</v>
       </c>
       <c r="S104" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12865,7 +12870,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12875,12 +12880,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:36</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Rikligt.</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12910,7 +12910,7 @@
         <v>129722198</v>
       </c>
       <c r="B105" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13027,7 +13027,7 @@
         <v>129717396</v>
       </c>
       <c r="B106" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13144,7 +13144,7 @@
         <v>129721773</v>
       </c>
       <c r="B107" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13251,7 +13251,7 @@
         <v>129699541</v>
       </c>
       <c r="B108" t="n">
-        <v>92884</v>
+        <v>92887</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13370,7 +13370,7 @@
         <v>129722095</v>
       </c>
       <c r="B109" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13479,10 +13479,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129717610</v>
+        <v>129722523</v>
       </c>
       <c r="B110" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
       <c r="I110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -13519,13 +13519,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>457387</v>
+        <v>457223</v>
       </c>
       <c r="R110" t="n">
-        <v>6677155</v>
+        <v>6676922</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -13554,7 +13554,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -13564,12 +13564,12 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack på tall, mycket färska.</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13596,10 +13596,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129722523</v>
+        <v>129717610</v>
       </c>
       <c r="B111" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13627,7 +13627,7 @@
       <c r="I111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -13636,13 +13636,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>457223</v>
+        <v>457387</v>
       </c>
       <c r="R111" t="n">
-        <v>6676922</v>
+        <v>6677155</v>
       </c>
       <c r="S111" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13671,7 +13671,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -13681,12 +13681,12 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Ringhack på tall, mycket färska.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13716,7 +13716,7 @@
         <v>129721616</v>
       </c>
       <c r="B112" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>129722486</v>
       </c>
       <c r="B113" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13935,7 +13935,7 @@
         <v>129717654</v>
       </c>
       <c r="B114" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14047,7 +14047,7 @@
         <v>129722420</v>
       </c>
       <c r="B115" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14154,7 +14154,7 @@
         <v>129722346</v>
       </c>
       <c r="B116" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>

--- a/artfynd/A 49804-2025 artfynd.xlsx
+++ b/artfynd/A 49804-2025 artfynd.xlsx
@@ -7513,45 +7513,50 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129700360</v>
+        <v>129699824</v>
       </c>
       <c r="B57" t="n">
-        <v>91569</v>
+        <v>57740</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>457345</v>
+        <v>457346</v>
       </c>
       <c r="R57" t="n">
-        <v>6677677</v>
+        <v>6677881</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7583,7 +7588,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7593,7 +7598,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7620,32 +7630,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129701074</v>
+        <v>129700360</v>
       </c>
       <c r="B58" t="n">
-        <v>79087</v>
+        <v>91569</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7655,10 +7665,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>457397</v>
+        <v>457345</v>
       </c>
       <c r="R58" t="n">
-        <v>6677548</v>
+        <v>6677677</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7690,7 +7700,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7700,12 +7710,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:02</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7732,10 +7737,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129711614</v>
+        <v>129701074</v>
       </c>
       <c r="B59" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7743,37 +7748,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>457280</v>
+        <v>457397</v>
       </c>
       <c r="R59" t="n">
-        <v>6678029</v>
+        <v>6677548</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7800,14 +7805,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Färskt födosök av spillkråka i björk stubbe.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7822,22 +7837,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129711612</v>
+        <v>129711614</v>
       </c>
       <c r="B60" t="n">
-        <v>57740</v>
+        <v>57737</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7845,16 +7860,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -7863,24 +7878,16 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>457358</v>
+        <v>457280</v>
       </c>
       <c r="R60" t="n">
-        <v>6677489</v>
+        <v>6678029</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7917,7 +7924,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Möjligt början på bohål i år/fjolåret.</t>
+          <t>Färskt födosök av spillkråka i björk stubbe.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7944,7 +7951,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129701963</v>
+        <v>129711612</v>
       </c>
       <c r="B61" t="n">
         <v>57740</v>
@@ -7973,24 +7980,27 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>457294</v>
+        <v>457358</v>
       </c>
       <c r="R61" t="n">
-        <v>6677481</v>
+        <v>6677489</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8017,24 +8027,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>12:43</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>12:43</t>
-        </is>
-      </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Möjligt början på bohål i år/fjolåret.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8049,19 +8049,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129699824</v>
+        <v>129701963</v>
       </c>
       <c r="B62" t="n">
         <v>57740</v>
@@ -8092,7 +8092,7 @@
       <c r="I62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -8101,10 +8101,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>457346</v>
+        <v>457294</v>
       </c>
       <c r="R62" t="n">
-        <v>6677881</v>
+        <v>6677481</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8136,7 +8136,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
@@ -9738,10 +9738,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129700400</v>
+        <v>129699484</v>
       </c>
       <c r="B77" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9749,34 +9749,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>457345</v>
+        <v>457246</v>
       </c>
       <c r="R77" t="n">
-        <v>6677660</v>
+        <v>6678032</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9808,7 +9813,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9818,12 +9823,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9850,10 +9855,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129699484</v>
+        <v>129700400</v>
       </c>
       <c r="B78" t="n">
-        <v>57740</v>
+        <v>79087</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9861,39 +9866,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>457246</v>
+        <v>457345</v>
       </c>
       <c r="R78" t="n">
-        <v>6678032</v>
+        <v>6677660</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9925,7 +9925,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -13248,59 +13248,48 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129699541</v>
+        <v>129722095</v>
       </c>
       <c r="B108" t="n">
-        <v>92887</v>
+        <v>79087</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
+          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>457267</v>
+        <v>457440</v>
       </c>
       <c r="R108" t="n">
-        <v>6678042</v>
+        <v>6676555</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -13324,22 +13313,27 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Ganska hänlavs rikt.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13348,7 +13342,6 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -13367,48 +13360,59 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129722095</v>
+        <v>129699541</v>
       </c>
       <c r="B109" t="n">
-        <v>79087</v>
+        <v>92887</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
+          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>457440</v>
+        <v>457267</v>
       </c>
       <c r="R109" t="n">
-        <v>6676555</v>
+        <v>6678042</v>
       </c>
       <c r="S109" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -13432,27 +13436,22 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>15:19</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Ganska hänlavs rikt.</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13461,6 +13460,7 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49804-2025 artfynd.xlsx
+++ b/artfynd/A 49804-2025 artfynd.xlsx
@@ -7062,10 +7062,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129702610</v>
+        <v>129700821</v>
       </c>
       <c r="B53" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7073,34 +7073,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>457417</v>
+        <v>457486</v>
       </c>
       <c r="R53" t="n">
-        <v>6677423</v>
+        <v>6677569</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7132,7 +7137,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7142,7 +7147,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7169,7 +7179,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129700821</v>
+        <v>129711613</v>
       </c>
       <c r="B54" t="n">
         <v>57740</v>
@@ -7198,24 +7208,27 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>457486</v>
+        <v>457300</v>
       </c>
       <c r="R54" t="n">
-        <v>6677569</v>
+        <v>6678044</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7242,24 +7255,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>11:49</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>11:49</t>
-        </is>
-      </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Barkflagning</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7274,22 +7277,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129711613</v>
+        <v>129702610</v>
       </c>
       <c r="B55" t="n">
-        <v>57740</v>
+        <v>79087</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7297,45 +7300,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>457300</v>
+        <v>457417</v>
       </c>
       <c r="R55" t="n">
-        <v>6678044</v>
+        <v>6677423</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7362,14 +7357,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Barkflagning</t>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7384,12 +7384,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -7513,50 +7513,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129699824</v>
+        <v>129700360</v>
       </c>
       <c r="B57" t="n">
-        <v>57740</v>
+        <v>91569</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>457346</v>
+        <v>457345</v>
       </c>
       <c r="R57" t="n">
-        <v>6677881</v>
+        <v>6677677</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7588,7 +7583,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7598,12 +7593,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:04</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7630,32 +7620,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129700360</v>
+        <v>129701074</v>
       </c>
       <c r="B58" t="n">
-        <v>91569</v>
+        <v>79087</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7665,10 +7655,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>457345</v>
+        <v>457397</v>
       </c>
       <c r="R58" t="n">
-        <v>6677677</v>
+        <v>6677548</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7700,7 +7690,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7710,7 +7700,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7737,10 +7732,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129701074</v>
+        <v>129711614</v>
       </c>
       <c r="B59" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7748,37 +7743,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>457397</v>
+        <v>457280</v>
       </c>
       <c r="R59" t="n">
-        <v>6677548</v>
+        <v>6678029</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7805,24 +7800,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Färskt födosök av spillkråka i björk stubbe.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7837,22 +7822,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129711614</v>
+        <v>129711612</v>
       </c>
       <c r="B60" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7860,16 +7845,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -7878,16 +7863,24 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>457280</v>
+        <v>457358</v>
       </c>
       <c r="R60" t="n">
-        <v>6678029</v>
+        <v>6677489</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7924,7 +7917,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Färskt födosök av spillkråka i björk stubbe.</t>
+          <t>Möjligt början på bohål i år/fjolåret.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7951,7 +7944,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129711612</v>
+        <v>129701963</v>
       </c>
       <c r="B61" t="n">
         <v>57740</v>
@@ -7980,27 +7973,24 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>457358</v>
+        <v>457294</v>
       </c>
       <c r="R61" t="n">
-        <v>6677489</v>
+        <v>6677481</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8027,14 +8017,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Möjligt början på bohål i år/fjolåret.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8049,19 +8049,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129701963</v>
+        <v>129699824</v>
       </c>
       <c r="B62" t="n">
         <v>57740</v>
@@ -8092,7 +8092,7 @@
       <c r="I62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -8101,10 +8101,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>457294</v>
+        <v>457346</v>
       </c>
       <c r="R62" t="n">
-        <v>6677481</v>
+        <v>6677881</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8136,7 +8136,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
@@ -8412,10 +8412,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129703378</v>
+        <v>129703525</v>
       </c>
       <c r="B65" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8423,34 +8423,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>457407</v>
+        <v>457433</v>
       </c>
       <c r="R65" t="n">
-        <v>6677144</v>
+        <v>6677123</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8482,7 +8487,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8492,12 +8497,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Rikligt på tall.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8524,10 +8529,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129711616</v>
+        <v>129702120</v>
       </c>
       <c r="B66" t="n">
-        <v>78844</v>
+        <v>57740</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8535,37 +8540,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>457305</v>
+        <v>457299</v>
       </c>
       <c r="R66" t="n">
-        <v>6677449</v>
+        <v>6677464</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8592,9 +8602,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8609,22 +8629,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129702120</v>
+        <v>129704842</v>
       </c>
       <c r="B67" t="n">
-        <v>57740</v>
+        <v>78845</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8632,39 +8652,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>457299</v>
+        <v>457230</v>
       </c>
       <c r="R67" t="n">
-        <v>6677464</v>
+        <v>6677594</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8696,7 +8711,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8706,7 +8721,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Lite osäker men rätt säker.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8733,59 +8753,48 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129711615</v>
+        <v>129703378</v>
       </c>
       <c r="B68" t="n">
-        <v>91589</v>
+        <v>79087</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4660</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>457423</v>
+        <v>457407</v>
       </c>
       <c r="R68" t="n">
-        <v>6677421</v>
+        <v>6677144</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8812,14 +8821,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>10-15 fk på stående mindre asp.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8828,72 +8847,77 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129703525</v>
+        <v>129711615</v>
       </c>
       <c r="B69" t="n">
-        <v>57740</v>
+        <v>91589</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>4660</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>457433</v>
+        <v>457423</v>
       </c>
       <c r="R69" t="n">
-        <v>6677123</v>
+        <v>6677421</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8920,24 +8944,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>13:41</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>13:41</t>
-        </is>
-      </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Rikligt på tall.</t>
+          <t>10-15 fk på stående mindre asp.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8946,28 +8960,29 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129704842</v>
+        <v>129711616</v>
       </c>
       <c r="B70" t="n">
-        <v>78845</v>
+        <v>78844</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8975,37 +8990,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>457230</v>
+        <v>457305</v>
       </c>
       <c r="R70" t="n">
-        <v>6677594</v>
+        <v>6677449</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9032,24 +9047,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Lite osäker men rätt säker.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9064,12 +9064,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -11774,10 +11774,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129700098</v>
+        <v>129703127</v>
       </c>
       <c r="B95" t="n">
-        <v>57740</v>
+        <v>78844</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11785,39 +11785,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>457355</v>
+        <v>457391</v>
       </c>
       <c r="R95" t="n">
-        <v>6677771</v>
+        <v>6677213</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11849,7 +11844,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11859,12 +11854,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Inte jätte färska med syns sav fortfarande.</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11891,10 +11881,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129703127</v>
+        <v>129700098</v>
       </c>
       <c r="B96" t="n">
-        <v>78844</v>
+        <v>57740</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11902,34 +11892,39 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>457391</v>
+        <v>457355</v>
       </c>
       <c r="R96" t="n">
-        <v>6677213</v>
+        <v>6677771</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11961,7 +11956,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11971,7 +11966,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Inte jätte färska med syns sav fortfarande.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -13248,48 +13248,59 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129722095</v>
+        <v>129699541</v>
       </c>
       <c r="B108" t="n">
-        <v>79087</v>
+        <v>92887</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
+          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>457440</v>
+        <v>457267</v>
       </c>
       <c r="R108" t="n">
-        <v>6676555</v>
+        <v>6678042</v>
       </c>
       <c r="S108" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -13313,27 +13324,22 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>15:19</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Ganska hänlavs rikt.</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13342,6 +13348,7 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -13360,59 +13367,48 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129699541</v>
+        <v>129722095</v>
       </c>
       <c r="B109" t="n">
-        <v>92887</v>
+        <v>79087</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
+          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>457267</v>
+        <v>457440</v>
       </c>
       <c r="R109" t="n">
-        <v>6678042</v>
+        <v>6676555</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -13436,22 +13432,27 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Ganska hänlavs rikt.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13460,7 +13461,6 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49804-2025 artfynd.xlsx
+++ b/artfynd/A 49804-2025 artfynd.xlsx
@@ -6950,10 +6950,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129699502</v>
+        <v>129702610</v>
       </c>
       <c r="B52" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6981,14 +6981,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>457280</v>
+        <v>457417</v>
       </c>
       <c r="R52" t="n">
-        <v>6678039</v>
+        <v>6677423</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7030,12 +7030,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:48</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7289,10 +7284,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129702610</v>
+        <v>129699502</v>
       </c>
       <c r="B55" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7320,14 +7315,14 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>457417</v>
+        <v>457280</v>
       </c>
       <c r="R55" t="n">
-        <v>6677423</v>
+        <v>6678039</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7359,7 +7354,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7369,7 +7364,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7513,45 +7513,50 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129700360</v>
+        <v>129699824</v>
       </c>
       <c r="B57" t="n">
-        <v>91569</v>
+        <v>57740</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>457345</v>
+        <v>457346</v>
       </c>
       <c r="R57" t="n">
-        <v>6677677</v>
+        <v>6677881</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7583,7 +7588,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7593,7 +7598,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7623,7 +7633,7 @@
         <v>129701074</v>
       </c>
       <c r="B58" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7732,48 +7742,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129711614</v>
+        <v>129700360</v>
       </c>
       <c r="B59" t="n">
-        <v>57737</v>
+        <v>91570</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>457280</v>
+        <v>457345</v>
       </c>
       <c r="R59" t="n">
-        <v>6678029</v>
+        <v>6677677</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7800,14 +7810,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Färskt födosök av spillkråka i björk stubbe.</t>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7822,22 +7837,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129711612</v>
+        <v>129711614</v>
       </c>
       <c r="B60" t="n">
-        <v>57740</v>
+        <v>57737</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7845,16 +7860,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -7863,24 +7878,16 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>457358</v>
+        <v>457280</v>
       </c>
       <c r="R60" t="n">
-        <v>6677489</v>
+        <v>6678029</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7917,7 +7924,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Möjligt början på bohål i år/fjolåret.</t>
+          <t>Färskt födosök av spillkråka i björk stubbe.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8061,7 +8068,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129699824</v>
+        <v>129711612</v>
       </c>
       <c r="B62" t="n">
         <v>57740</v>
@@ -8090,24 +8097,27 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>457346</v>
+        <v>457358</v>
       </c>
       <c r="R62" t="n">
-        <v>6677881</v>
+        <v>6677489</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8134,24 +8144,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Möjligt början på bohål i år/fjolåret.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8166,12 +8166,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -8412,10 +8412,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129703525</v>
+        <v>129703378</v>
       </c>
       <c r="B65" t="n">
-        <v>57740</v>
+        <v>79088</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8423,39 +8423,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>457433</v>
+        <v>457407</v>
       </c>
       <c r="R65" t="n">
-        <v>6677123</v>
+        <v>6677144</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8487,7 +8482,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8497,12 +8492,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Rikligt på tall.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8529,10 +8524,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129702120</v>
+        <v>129711616</v>
       </c>
       <c r="B66" t="n">
-        <v>57740</v>
+        <v>78845</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8540,42 +8535,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>457299</v>
+        <v>457305</v>
       </c>
       <c r="R66" t="n">
-        <v>6677464</v>
+        <v>6677449</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8602,19 +8592,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>12:47</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8629,60 +8609,71 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129704842</v>
+        <v>129711615</v>
       </c>
       <c r="B67" t="n">
-        <v>78845</v>
+        <v>91590</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>4660</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>457230</v>
+        <v>457423</v>
       </c>
       <c r="R67" t="n">
-        <v>6677594</v>
+        <v>6677421</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8709,24 +8700,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Lite osäker men rätt säker.</t>
+          <t>10-15 fk på stående mindre asp.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8735,28 +8716,29 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129703378</v>
+        <v>129703525</v>
       </c>
       <c r="B68" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8764,34 +8746,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>457407</v>
+        <v>457433</v>
       </c>
       <c r="R68" t="n">
-        <v>6677144</v>
+        <v>6677123</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8823,7 +8810,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8833,12 +8820,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Rikligt på tall.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8865,59 +8852,53 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129711615</v>
+        <v>129702120</v>
       </c>
       <c r="B69" t="n">
-        <v>91589</v>
+        <v>57740</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4660</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>457423</v>
+        <v>457299</v>
       </c>
       <c r="R69" t="n">
-        <v>6677421</v>
+        <v>6677464</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8944,14 +8925,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>10-15 fk på stående mindre asp.</t>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8960,29 +8946,28 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129711616</v>
+        <v>129704842</v>
       </c>
       <c r="B70" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8990,37 +8975,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>457305</v>
+        <v>457230</v>
       </c>
       <c r="R70" t="n">
-        <v>6677449</v>
+        <v>6677594</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9047,9 +9032,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Lite osäker men rätt säker.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9064,12 +9064,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -9196,7 +9196,7 @@
         <v>129702970</v>
       </c>
       <c r="B72" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9308,7 +9308,7 @@
         <v>129704249</v>
       </c>
       <c r="B73" t="n">
-        <v>97043</v>
+        <v>97044</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
         <v>129711617</v>
       </c>
       <c r="B74" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9517,7 +9517,7 @@
         <v>129702657</v>
       </c>
       <c r="B75" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9738,10 +9738,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129699484</v>
+        <v>129700400</v>
       </c>
       <c r="B77" t="n">
-        <v>57740</v>
+        <v>79088</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9749,39 +9749,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>457246</v>
+        <v>457345</v>
       </c>
       <c r="R77" t="n">
-        <v>6678032</v>
+        <v>6677660</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9813,7 +9808,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9823,12 +9818,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9855,10 +9850,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129700400</v>
+        <v>129699484</v>
       </c>
       <c r="B78" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9866,34 +9861,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>457345</v>
+        <v>457246</v>
       </c>
       <c r="R78" t="n">
-        <v>6677660</v>
+        <v>6678032</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9925,7 +9925,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9970,7 +9970,7 @@
         <v>129702998</v>
       </c>
       <c r="B79" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10199,7 +10199,7 @@
         <v>129703164</v>
       </c>
       <c r="B81" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10306,7 +10306,7 @@
         <v>129700616</v>
       </c>
       <c r="B82" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10766,10 +10766,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129700950</v>
+        <v>129702495</v>
       </c>
       <c r="B86" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10777,34 +10777,39 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>457431</v>
+        <v>457432</v>
       </c>
       <c r="R86" t="n">
-        <v>6677513</v>
+        <v>6677419</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10836,7 +10841,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10846,12 +10851,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10878,10 +10883,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129703077</v>
+        <v>129700968</v>
       </c>
       <c r="B87" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10889,34 +10894,39 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>457393</v>
+        <v>457428</v>
       </c>
       <c r="R87" t="n">
-        <v>6677229</v>
+        <v>6677512</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10948,7 +10958,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10958,12 +10968,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10990,10 +11000,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129704366</v>
+        <v>129700950</v>
       </c>
       <c r="B88" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11021,14 +11031,14 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>457288</v>
+        <v>457431</v>
       </c>
       <c r="R88" t="n">
-        <v>6677333</v>
+        <v>6677513</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11060,7 +11070,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11070,12 +11080,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11102,10 +11112,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129711618</v>
+        <v>129703077</v>
       </c>
       <c r="B89" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11133,17 +11143,17 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>457392</v>
+        <v>457393</v>
       </c>
       <c r="R89" t="n">
-        <v>6677547</v>
+        <v>6677229</v>
       </c>
       <c r="S89" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11170,9 +11180,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11187,22 +11212,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129702495</v>
+        <v>129704366</v>
       </c>
       <c r="B90" t="n">
-        <v>57740</v>
+        <v>79088</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11210,39 +11235,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>457432</v>
+        <v>457288</v>
       </c>
       <c r="R90" t="n">
-        <v>6677419</v>
+        <v>6677333</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11274,7 +11294,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11284,12 +11304,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11316,10 +11336,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129700968</v>
+        <v>129711618</v>
       </c>
       <c r="B91" t="n">
-        <v>57740</v>
+        <v>79088</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11327,42 +11347,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>457428</v>
+        <v>457392</v>
       </c>
       <c r="R91" t="n">
-        <v>6677512</v>
+        <v>6677547</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11389,24 +11404,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>11:56</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>11:56</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11421,12 +11421,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -11550,10 +11550,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129701101</v>
+        <v>129703817</v>
       </c>
       <c r="B93" t="n">
-        <v>57740</v>
+        <v>78845</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11561,39 +11561,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>457396</v>
+        <v>457337</v>
       </c>
       <c r="R93" t="n">
-        <v>6677546</v>
+        <v>6677076</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11625,7 +11620,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11635,12 +11630,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:03</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Inte super färska.</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11667,10 +11657,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129703817</v>
+        <v>129701101</v>
       </c>
       <c r="B94" t="n">
-        <v>78844</v>
+        <v>57740</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11678,34 +11668,39 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>457337</v>
+        <v>457396</v>
       </c>
       <c r="R94" t="n">
-        <v>6677076</v>
+        <v>6677546</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11737,7 +11732,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11747,7 +11742,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Inte super färska.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11774,10 +11774,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129703127</v>
+        <v>129700098</v>
       </c>
       <c r="B95" t="n">
-        <v>78844</v>
+        <v>57740</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11785,34 +11785,39 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>457391</v>
+        <v>457355</v>
       </c>
       <c r="R95" t="n">
-        <v>6677213</v>
+        <v>6677771</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11844,7 +11849,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11854,7 +11859,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Inte jätte färska med syns sav fortfarande.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11881,10 +11891,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129700098</v>
+        <v>129703127</v>
       </c>
       <c r="B96" t="n">
-        <v>57740</v>
+        <v>78845</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11892,39 +11902,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>457355</v>
+        <v>457391</v>
       </c>
       <c r="R96" t="n">
-        <v>6677771</v>
+        <v>6677213</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11956,7 +11961,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11966,12 +11971,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Inte jätte färska med syns sav fortfarande.</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12001,7 +12001,7 @@
         <v>129722077</v>
       </c>
       <c r="B97" t="n">
-        <v>91625</v>
+        <v>91626</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12457,56 +12457,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129704065</v>
+        <v>129722043</v>
       </c>
       <c r="B101" t="n">
-        <v>92887</v>
+        <v>79088</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>457293</v>
+        <v>457469</v>
       </c>
       <c r="R101" t="n">
-        <v>6677157</v>
+        <v>6676536</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12533,22 +12522,22 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12557,7 +12546,6 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -12576,45 +12564,56 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129722043</v>
+        <v>129704065</v>
       </c>
       <c r="B102" t="n">
-        <v>79087</v>
+        <v>92888</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>457469</v>
+        <v>457293</v>
       </c>
       <c r="R102" t="n">
-        <v>6676536</v>
+        <v>6677157</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12641,22 +12640,22 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12665,6 +12664,7 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -12683,10 +12683,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129722392</v>
+        <v>129721585</v>
       </c>
       <c r="B103" t="n">
-        <v>57740</v>
+        <v>79088</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12694,42 +12694,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
+          <t>Lagalamm, Lagalamm, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>457336</v>
+        <v>457426</v>
       </c>
       <c r="R103" t="n">
-        <v>6676787</v>
+        <v>6676070</v>
       </c>
       <c r="S103" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12758,7 +12753,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12768,12 +12763,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:36</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Rikligt.</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12800,10 +12790,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129721585</v>
+        <v>129722392</v>
       </c>
       <c r="B104" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12811,37 +12801,42 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Lagalamm, Lagalamm, Dlr</t>
+          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>457426</v>
+        <v>457336</v>
       </c>
       <c r="R104" t="n">
-        <v>6676070</v>
+        <v>6676787</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12870,7 +12865,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12880,7 +12875,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Rikligt.</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13144,7 +13144,7 @@
         <v>129721773</v>
       </c>
       <c r="B107" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13248,59 +13248,48 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129699541</v>
+        <v>129722095</v>
       </c>
       <c r="B108" t="n">
-        <v>92887</v>
+        <v>79088</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
+          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>457267</v>
+        <v>457440</v>
       </c>
       <c r="R108" t="n">
-        <v>6678042</v>
+        <v>6676555</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -13324,22 +13313,27 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Ganska hänlavs rikt.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13348,7 +13342,6 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -13367,48 +13360,59 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129722095</v>
+        <v>129699541</v>
       </c>
       <c r="B109" t="n">
-        <v>79087</v>
+        <v>92888</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
+          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>457440</v>
+        <v>457267</v>
       </c>
       <c r="R109" t="n">
-        <v>6676555</v>
+        <v>6678042</v>
       </c>
       <c r="S109" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -13432,27 +13436,22 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>15:19</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Ganska hänlavs rikt.</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13461,6 +13460,7 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
@@ -13716,7 +13716,7 @@
         <v>129721616</v>
       </c>
       <c r="B112" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>129722486</v>
       </c>
       <c r="B113" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13935,7 +13935,7 @@
         <v>129717654</v>
       </c>
       <c r="B114" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14047,7 +14047,7 @@
         <v>129722420</v>
       </c>
       <c r="B115" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>

--- a/artfynd/A 49804-2025 artfynd.xlsx
+++ b/artfynd/A 49804-2025 artfynd.xlsx
@@ -7513,10 +7513,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129699824</v>
+        <v>129711614</v>
       </c>
       <c r="B57" t="n">
-        <v>57740</v>
+        <v>57737</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7524,16 +7524,16 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -7542,24 +7542,19 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>457346</v>
+        <v>457280</v>
       </c>
       <c r="R57" t="n">
-        <v>6677881</v>
+        <v>6678029</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7586,24 +7581,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Färskt födosök av spillkråka i björk stubbe.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7618,12 +7603,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -7849,10 +7834,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129711614</v>
+        <v>129701963</v>
       </c>
       <c r="B60" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7860,16 +7845,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -7878,19 +7863,24 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>457280</v>
+        <v>457294</v>
       </c>
       <c r="R60" t="n">
-        <v>6678029</v>
+        <v>6677481</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7917,14 +7907,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Färskt födosök av spillkråka i björk stubbe.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7939,19 +7939,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129701963</v>
+        <v>129711612</v>
       </c>
       <c r="B61" t="n">
         <v>57740</v>
@@ -7980,24 +7980,27 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>457294</v>
+        <v>457358</v>
       </c>
       <c r="R61" t="n">
-        <v>6677481</v>
+        <v>6677489</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8024,24 +8027,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>12:43</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>12:43</t>
-        </is>
-      </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Möjligt början på bohål i år/fjolåret.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8056,19 +8049,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129711612</v>
+        <v>129699824</v>
       </c>
       <c r="B62" t="n">
         <v>57740</v>
@@ -8097,27 +8090,24 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>457358</v>
+        <v>457346</v>
       </c>
       <c r="R62" t="n">
-        <v>6677489</v>
+        <v>6677881</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8144,14 +8134,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Möjligt början på bohål i år/fjolåret.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8166,12 +8166,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -8735,10 +8735,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129703525</v>
+        <v>129704842</v>
       </c>
       <c r="B68" t="n">
-        <v>57740</v>
+        <v>78846</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8746,39 +8746,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>457433</v>
+        <v>457230</v>
       </c>
       <c r="R68" t="n">
-        <v>6677123</v>
+        <v>6677594</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8810,7 +8805,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8820,12 +8815,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Rikligt på tall.</t>
+          <t>Lite osäker men rätt säker.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8852,7 +8847,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129702120</v>
+        <v>129703525</v>
       </c>
       <c r="B69" t="n">
         <v>57740</v>
@@ -8883,19 +8878,19 @@
       <c r="I69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>457299</v>
+        <v>457433</v>
       </c>
       <c r="R69" t="n">
-        <v>6677464</v>
+        <v>6677123</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8927,7 +8922,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8937,7 +8932,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Rikligt på tall.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8964,10 +8964,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129704842</v>
+        <v>129702120</v>
       </c>
       <c r="B70" t="n">
-        <v>78846</v>
+        <v>57740</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8975,34 +8975,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>457230</v>
+        <v>457299</v>
       </c>
       <c r="R70" t="n">
-        <v>6677594</v>
+        <v>6677464</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9034,7 +9039,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9044,12 +9049,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:36</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Lite osäker men rätt säker.</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9076,10 +9076,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129704395</v>
+        <v>129702970</v>
       </c>
       <c r="B71" t="n">
-        <v>57740</v>
+        <v>79088</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9087,39 +9087,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>457267</v>
+        <v>457390</v>
       </c>
       <c r="R71" t="n">
-        <v>6677342</v>
+        <v>6677240</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9151,7 +9146,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9161,12 +9156,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9193,10 +9188,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129702970</v>
+        <v>129704395</v>
       </c>
       <c r="B72" t="n">
-        <v>79088</v>
+        <v>57740</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9204,34 +9199,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>457390</v>
+        <v>457267</v>
       </c>
       <c r="R72" t="n">
-        <v>6677240</v>
+        <v>6677342</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9263,7 +9263,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9273,12 +9273,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9738,10 +9738,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129700400</v>
+        <v>129699484</v>
       </c>
       <c r="B77" t="n">
-        <v>79088</v>
+        <v>57740</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9749,34 +9749,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>457345</v>
+        <v>457246</v>
       </c>
       <c r="R77" t="n">
-        <v>6677660</v>
+        <v>6678032</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9808,7 +9813,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9818,12 +9823,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9850,10 +9855,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129699484</v>
+        <v>129700400</v>
       </c>
       <c r="B78" t="n">
-        <v>57740</v>
+        <v>79088</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9861,39 +9866,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>457246</v>
+        <v>457345</v>
       </c>
       <c r="R78" t="n">
-        <v>6678032</v>
+        <v>6677660</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9925,7 +9925,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD78" t="b">

--- a/artfynd/A 49804-2025 artfynd.xlsx
+++ b/artfynd/A 49804-2025 artfynd.xlsx
@@ -7513,10 +7513,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129711614</v>
+        <v>129699824</v>
       </c>
       <c r="B57" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7524,16 +7524,16 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -7542,19 +7542,24 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>457280</v>
+        <v>457346</v>
       </c>
       <c r="R57" t="n">
-        <v>6678029</v>
+        <v>6677881</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7581,14 +7586,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Färskt födosök av spillkråka i björk stubbe.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7603,12 +7618,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -7834,10 +7849,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129701963</v>
+        <v>129711614</v>
       </c>
       <c r="B60" t="n">
-        <v>57740</v>
+        <v>57737</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7845,16 +7860,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -7863,24 +7878,19 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>457294</v>
+        <v>457280</v>
       </c>
       <c r="R60" t="n">
-        <v>6677481</v>
+        <v>6678029</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7907,24 +7917,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>12:43</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>12:43</t>
-        </is>
-      </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Färskt födosök av spillkråka i björk stubbe.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7939,19 +7939,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129711612</v>
+        <v>129701963</v>
       </c>
       <c r="B61" t="n">
         <v>57740</v>
@@ -7980,27 +7980,24 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>457358</v>
+        <v>457294</v>
       </c>
       <c r="R61" t="n">
-        <v>6677489</v>
+        <v>6677481</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8027,14 +8024,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Möjligt början på bohål i år/fjolåret.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8049,19 +8056,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129699824</v>
+        <v>129711612</v>
       </c>
       <c r="B62" t="n">
         <v>57740</v>
@@ -8090,24 +8097,27 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>457346</v>
+        <v>457358</v>
       </c>
       <c r="R62" t="n">
-        <v>6677881</v>
+        <v>6677489</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8134,24 +8144,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Möjligt början på bohål i år/fjolåret.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8166,12 +8166,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -8735,10 +8735,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129704842</v>
+        <v>129703525</v>
       </c>
       <c r="B68" t="n">
-        <v>78846</v>
+        <v>57740</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8746,34 +8746,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>457230</v>
+        <v>457433</v>
       </c>
       <c r="R68" t="n">
-        <v>6677594</v>
+        <v>6677123</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8805,7 +8810,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8815,12 +8820,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Lite osäker men rätt säker.</t>
+          <t>Rikligt på tall.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8847,7 +8852,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129703525</v>
+        <v>129702120</v>
       </c>
       <c r="B69" t="n">
         <v>57740</v>
@@ -8878,19 +8883,19 @@
       <c r="I69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>457433</v>
+        <v>457299</v>
       </c>
       <c r="R69" t="n">
-        <v>6677123</v>
+        <v>6677464</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8922,7 +8927,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8932,12 +8937,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:41</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Rikligt på tall.</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8964,10 +8964,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129702120</v>
+        <v>129704842</v>
       </c>
       <c r="B70" t="n">
-        <v>57740</v>
+        <v>78846</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8975,39 +8975,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>457299</v>
+        <v>457230</v>
       </c>
       <c r="R70" t="n">
-        <v>6677464</v>
+        <v>6677594</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9039,7 +9034,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9049,7 +9044,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Lite osäker men rätt säker.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9076,10 +9076,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129702970</v>
+        <v>129704395</v>
       </c>
       <c r="B71" t="n">
-        <v>79088</v>
+        <v>57740</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9087,34 +9087,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>457390</v>
+        <v>457267</v>
       </c>
       <c r="R71" t="n">
-        <v>6677240</v>
+        <v>6677342</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9146,7 +9151,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9156,12 +9161,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9188,10 +9193,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129704395</v>
+        <v>129702970</v>
       </c>
       <c r="B72" t="n">
-        <v>57740</v>
+        <v>79088</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9199,39 +9204,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>457267</v>
+        <v>457390</v>
       </c>
       <c r="R72" t="n">
-        <v>6677342</v>
+        <v>6677240</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9263,7 +9263,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9273,12 +9273,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD72" t="b">

--- a/artfynd/A 49804-2025 artfynd.xlsx
+++ b/artfynd/A 49804-2025 artfynd.xlsx
@@ -6950,10 +6950,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129702610</v>
+        <v>129699502</v>
       </c>
       <c r="B52" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6981,14 +6981,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>457417</v>
+        <v>457280</v>
       </c>
       <c r="R52" t="n">
-        <v>6677423</v>
+        <v>6678039</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7030,7 +7030,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7057,10 +7062,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129700821</v>
+        <v>129702610</v>
       </c>
       <c r="B53" t="n">
-        <v>57740</v>
+        <v>79089</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7068,39 +7073,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>457486</v>
+        <v>457417</v>
       </c>
       <c r="R53" t="n">
-        <v>6677569</v>
+        <v>6677423</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7132,7 +7132,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7142,12 +7142,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:49</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7284,10 +7279,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129699502</v>
+        <v>129700821</v>
       </c>
       <c r="B55" t="n">
-        <v>79088</v>
+        <v>57740</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7295,34 +7290,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>457280</v>
+        <v>457486</v>
       </c>
       <c r="R55" t="n">
-        <v>6678039</v>
+        <v>6677569</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7354,7 +7354,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7513,50 +7513,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129699824</v>
+        <v>129700360</v>
       </c>
       <c r="B57" t="n">
-        <v>57740</v>
+        <v>91587</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>457346</v>
+        <v>457345</v>
       </c>
       <c r="R57" t="n">
-        <v>6677881</v>
+        <v>6677677</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7588,7 +7583,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7598,12 +7593,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:04</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7633,7 +7623,7 @@
         <v>129701074</v>
       </c>
       <c r="B58" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7742,48 +7732,56 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129700360</v>
+        <v>129711612</v>
       </c>
       <c r="B59" t="n">
-        <v>91570</v>
+        <v>57740</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>457345</v>
+        <v>457358</v>
       </c>
       <c r="R59" t="n">
-        <v>6677677</v>
+        <v>6677489</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7810,19 +7808,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>11:26</t>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Möjligt början på bohål i år/fjolåret.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7837,12 +7830,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -8068,7 +8061,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129711612</v>
+        <v>129699824</v>
       </c>
       <c r="B62" t="n">
         <v>57740</v>
@@ -8097,27 +8090,24 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>457358</v>
+        <v>457346</v>
       </c>
       <c r="R62" t="n">
-        <v>6677489</v>
+        <v>6677881</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8144,14 +8134,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Möjligt början på bohål i år/fjolåret.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8166,12 +8166,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -8415,7 +8415,7 @@
         <v>129703378</v>
       </c>
       <c r="B65" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8524,10 +8524,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129711616</v>
+        <v>129703525</v>
       </c>
       <c r="B66" t="n">
-        <v>78845</v>
+        <v>57740</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8535,37 +8535,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>457305</v>
+        <v>457433</v>
       </c>
       <c r="R66" t="n">
-        <v>6677449</v>
+        <v>6677123</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8592,9 +8597,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Rikligt på tall.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8609,71 +8629,65 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129711615</v>
+        <v>129702120</v>
       </c>
       <c r="B67" t="n">
-        <v>91590</v>
+        <v>57740</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4660</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>457423</v>
+        <v>457299</v>
       </c>
       <c r="R67" t="n">
-        <v>6677421</v>
+        <v>6677464</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8700,14 +8714,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>10-15 fk på stående mindre asp.</t>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8716,72 +8735,77 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129703525</v>
+        <v>129711615</v>
       </c>
       <c r="B68" t="n">
-        <v>57740</v>
+        <v>91607</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>4660</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>457433</v>
+        <v>457423</v>
       </c>
       <c r="R68" t="n">
-        <v>6677123</v>
+        <v>6677421</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8808,24 +8832,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>13:41</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>13:41</t>
-        </is>
-      </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Rikligt på tall.</t>
+          <t>10-15 fk på stående mindre asp.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8834,28 +8848,29 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129702120</v>
+        <v>129711616</v>
       </c>
       <c r="B69" t="n">
-        <v>57740</v>
+        <v>78846</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8863,42 +8878,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>457299</v>
+        <v>457305</v>
       </c>
       <c r="R69" t="n">
-        <v>6677464</v>
+        <v>6677449</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8925,19 +8935,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>12:47</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8952,12 +8952,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -8967,7 +8967,7 @@
         <v>129704842</v>
       </c>
       <c r="B70" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9076,10 +9076,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129704395</v>
+        <v>129702970</v>
       </c>
       <c r="B71" t="n">
-        <v>57740</v>
+        <v>79089</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9087,39 +9087,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>457267</v>
+        <v>457390</v>
       </c>
       <c r="R71" t="n">
-        <v>6677342</v>
+        <v>6677240</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9151,7 +9146,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9161,12 +9156,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9193,10 +9188,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129702970</v>
+        <v>129704395</v>
       </c>
       <c r="B72" t="n">
-        <v>79088</v>
+        <v>57740</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9204,34 +9199,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>457390</v>
+        <v>457267</v>
       </c>
       <c r="R72" t="n">
-        <v>6677240</v>
+        <v>6677342</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9263,7 +9263,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9273,12 +9273,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9305,10 +9305,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129704249</v>
+        <v>129711617</v>
       </c>
       <c r="B73" t="n">
-        <v>97044</v>
+        <v>79089</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9316,37 +9316,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>457311</v>
+        <v>457423</v>
       </c>
       <c r="R73" t="n">
-        <v>6677235</v>
+        <v>6677206</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9373,19 +9373,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>14:11</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>14:11</t>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>På tallstam</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9400,22 +9395,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129711617</v>
+        <v>129704249</v>
       </c>
       <c r="B74" t="n">
-        <v>79088</v>
+        <v>97061</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9423,37 +9418,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>457423</v>
+        <v>457311</v>
       </c>
       <c r="R74" t="n">
-        <v>6677206</v>
+        <v>6677235</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9480,14 +9475,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>På tallstam</t>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9502,57 +9502,62 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129702657</v>
+        <v>129704181</v>
       </c>
       <c r="B75" t="n">
-        <v>91570</v>
+        <v>57740</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>457420</v>
+        <v>457325</v>
       </c>
       <c r="R75" t="n">
-        <v>6677417</v>
+        <v>6677219</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9584,7 +9589,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9594,7 +9599,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9621,50 +9631,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129704181</v>
+        <v>129702657</v>
       </c>
       <c r="B76" t="n">
-        <v>57740</v>
+        <v>91587</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>457325</v>
+        <v>457420</v>
       </c>
       <c r="R76" t="n">
-        <v>6677219</v>
+        <v>6677417</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9696,7 +9701,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9706,12 +9711,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9738,10 +9738,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129699484</v>
+        <v>129700400</v>
       </c>
       <c r="B77" t="n">
-        <v>57740</v>
+        <v>79089</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9749,39 +9749,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>457246</v>
+        <v>457345</v>
       </c>
       <c r="R77" t="n">
-        <v>6678032</v>
+        <v>6677660</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9813,7 +9808,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9823,12 +9818,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9855,10 +9850,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129700400</v>
+        <v>129699484</v>
       </c>
       <c r="B78" t="n">
-        <v>79088</v>
+        <v>57740</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9866,34 +9861,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>457345</v>
+        <v>457246</v>
       </c>
       <c r="R78" t="n">
-        <v>6677660</v>
+        <v>6678032</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9925,7 +9925,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9970,7 +9970,7 @@
         <v>129702998</v>
       </c>
       <c r="B79" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10196,10 +10196,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129703164</v>
+        <v>129700616</v>
       </c>
       <c r="B81" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10227,14 +10227,14 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>457394</v>
+        <v>457384</v>
       </c>
       <c r="R81" t="n">
-        <v>6677203</v>
+        <v>6677586</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10266,7 +10266,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10276,7 +10276,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10303,10 +10308,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129700616</v>
+        <v>129703164</v>
       </c>
       <c r="B82" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10334,14 +10339,14 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>457384</v>
+        <v>457394</v>
       </c>
       <c r="R82" t="n">
-        <v>6677586</v>
+        <v>6677203</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10373,7 +10378,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10383,12 +10388,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:40</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10766,10 +10766,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129702495</v>
+        <v>129703077</v>
       </c>
       <c r="B86" t="n">
-        <v>57740</v>
+        <v>79089</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10777,39 +10777,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>457432</v>
+        <v>457393</v>
       </c>
       <c r="R86" t="n">
-        <v>6677419</v>
+        <v>6677229</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10841,7 +10836,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10851,12 +10846,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10883,10 +10878,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129700968</v>
+        <v>129711618</v>
       </c>
       <c r="B87" t="n">
-        <v>57740</v>
+        <v>79089</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10894,42 +10889,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>St. Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>457428</v>
+        <v>457392</v>
       </c>
       <c r="R87" t="n">
-        <v>6677512</v>
+        <v>6677547</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10956,24 +10946,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>11:56</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>11:56</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10988,12 +10963,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -11003,7 +10978,7 @@
         <v>129700950</v>
       </c>
       <c r="B88" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11112,10 +11087,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129703077</v>
+        <v>129704366</v>
       </c>
       <c r="B89" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11147,10 +11122,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>457393</v>
+        <v>457288</v>
       </c>
       <c r="R89" t="n">
-        <v>6677229</v>
+        <v>6677333</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11182,7 +11157,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11192,12 +11167,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11224,10 +11199,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129704366</v>
+        <v>129702495</v>
       </c>
       <c r="B90" t="n">
-        <v>79088</v>
+        <v>57740</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11235,34 +11210,39 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>457288</v>
+        <v>457432</v>
       </c>
       <c r="R90" t="n">
-        <v>6677333</v>
+        <v>6677419</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11294,7 +11274,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11304,12 +11284,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11336,10 +11316,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129711618</v>
+        <v>129700968</v>
       </c>
       <c r="B91" t="n">
-        <v>79088</v>
+        <v>57740</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11347,37 +11327,42 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>St. Mörtsjön, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>457392</v>
+        <v>457428</v>
       </c>
       <c r="R91" t="n">
-        <v>6677547</v>
+        <v>6677512</v>
       </c>
       <c r="S91" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11404,9 +11389,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11421,12 +11421,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -11553,7 +11553,7 @@
         <v>129703817</v>
       </c>
       <c r="B93" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11774,10 +11774,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129700098</v>
+        <v>129703127</v>
       </c>
       <c r="B95" t="n">
-        <v>57740</v>
+        <v>78846</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11785,39 +11785,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>457355</v>
+        <v>457391</v>
       </c>
       <c r="R95" t="n">
-        <v>6677771</v>
+        <v>6677213</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11849,7 +11844,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11859,12 +11854,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Inte jätte färska med syns sav fortfarande.</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11891,10 +11881,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129703127</v>
+        <v>129700098</v>
       </c>
       <c r="B96" t="n">
-        <v>78845</v>
+        <v>57740</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11902,34 +11892,39 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Stora Mörttjärnen, Stora Mörttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>457391</v>
+        <v>457355</v>
       </c>
       <c r="R96" t="n">
-        <v>6677213</v>
+        <v>6677771</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11961,7 +11956,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11971,7 +11966,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Inte jätte färska med syns sav fortfarande.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12001,7 +12001,7 @@
         <v>129722077</v>
       </c>
       <c r="B97" t="n">
-        <v>91626</v>
+        <v>91643</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12223,7 +12223,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129722296</v>
+        <v>129722173</v>
       </c>
       <c r="B99" t="n">
         <v>57740</v>
@@ -12254,7 +12254,7 @@
       <c r="I99" t="inlineStr"/>
       <c r="M99" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -12263,10 +12263,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>457348</v>
+        <v>457418</v>
       </c>
       <c r="R99" t="n">
-        <v>6676704</v>
+        <v>6676575</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -12298,7 +12298,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12308,12 +12308,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Lite färskare och äldre.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12340,7 +12340,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129722173</v>
+        <v>129722296</v>
       </c>
       <c r="B100" t="n">
         <v>57740</v>
@@ -12371,7 +12371,7 @@
       <c r="I100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -12380,10 +12380,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>457418</v>
+        <v>457348</v>
       </c>
       <c r="R100" t="n">
-        <v>6676575</v>
+        <v>6676704</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -12415,7 +12415,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12425,12 +12425,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Lite färskare och äldre.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12460,7 +12460,7 @@
         <v>129722043</v>
       </c>
       <c r="B101" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12567,7 +12567,7 @@
         <v>129704065</v>
       </c>
       <c r="B102" t="n">
-        <v>92888</v>
+        <v>92905</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12683,10 +12683,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129721585</v>
+        <v>129722392</v>
       </c>
       <c r="B103" t="n">
-        <v>79088</v>
+        <v>57740</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12694,37 +12694,42 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Lagalamm, Lagalamm, Dlr</t>
+          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>457426</v>
+        <v>457336</v>
       </c>
       <c r="R103" t="n">
-        <v>6676070</v>
+        <v>6676787</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12753,7 +12758,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12763,7 +12768,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Rikligt.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12790,10 +12800,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129722392</v>
+        <v>129721585</v>
       </c>
       <c r="B104" t="n">
-        <v>57740</v>
+        <v>79089</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12801,42 +12811,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
+          <t>Lagalamm, Lagalamm, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>457336</v>
+        <v>457426</v>
       </c>
       <c r="R104" t="n">
-        <v>6676787</v>
+        <v>6676070</v>
       </c>
       <c r="S104" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12865,7 +12870,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12875,12 +12880,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:36</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Rikligt.</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13144,7 +13144,7 @@
         <v>129721773</v>
       </c>
       <c r="B107" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13248,48 +13248,59 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129722095</v>
+        <v>129699541</v>
       </c>
       <c r="B108" t="n">
-        <v>79088</v>
+        <v>92905</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
+          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>457440</v>
+        <v>457267</v>
       </c>
       <c r="R108" t="n">
-        <v>6676555</v>
+        <v>6678042</v>
       </c>
       <c r="S108" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -13313,27 +13324,22 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>15:19</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Ganska hänlavs rikt.</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13342,6 +13348,7 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -13360,59 +13367,48 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129699541</v>
+        <v>129722095</v>
       </c>
       <c r="B109" t="n">
-        <v>92888</v>
+        <v>79089</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
+          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>457267</v>
+        <v>457440</v>
       </c>
       <c r="R109" t="n">
-        <v>6678042</v>
+        <v>6676555</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -13436,22 +13432,27 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Ganska hänlavs rikt.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13460,7 +13461,6 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
@@ -13716,7 +13716,7 @@
         <v>129721616</v>
       </c>
       <c r="B112" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13820,10 +13820,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129722486</v>
+        <v>129717654</v>
       </c>
       <c r="B113" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13851,14 +13851,14 @@
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
+          <t>Korronsoppi, Korronsoppi, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>457247</v>
+        <v>457556</v>
       </c>
       <c r="R113" t="n">
-        <v>6676846</v>
+        <v>6676911</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -13890,7 +13890,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -13900,12 +13900,12 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>På flera tallar.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13932,10 +13932,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129717654</v>
+        <v>129722486</v>
       </c>
       <c r="B114" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13963,14 +13963,14 @@
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Korronsoppi, Korronsoppi, Dlr</t>
+          <t>Lagalammshöjden, Lagalammshöjden, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>457556</v>
+        <v>457247</v>
       </c>
       <c r="R114" t="n">
-        <v>6676911</v>
+        <v>6676846</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -14002,7 +14002,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -14012,12 +14012,12 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>På flera tallar.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -14047,7 +14047,7 @@
         <v>129722420</v>
       </c>
       <c r="B115" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>

--- a/artfynd/A 49804-2025 artfynd.xlsx
+++ b/artfynd/A 49804-2025 artfynd.xlsx
@@ -7152,7 +7152,7 @@
         <v>0</v>
       </c>
       <c r="AE53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG53" t="b">
         <v>0</v>
@@ -7939,7 +7939,7 @@
         <v>0</v>
       </c>
       <c r="AE60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG60" t="b">
         <v>0</v>
@@ -9392,7 +9392,7 @@
         <v>0</v>
       </c>
       <c r="AE73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG73" t="b">
         <v>0</v>
